--- a/research/traditional_assets/database/data/france/france_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/france/france_oil_gas_integrated.xlsx
@@ -650,10 +650,10 @@
         <v>0.1456805479972704</v>
       </c>
       <c r="X2">
-        <v>0.1114668167263384</v>
+        <v>0.1114361496755217</v>
       </c>
       <c r="Y2">
-        <v>0.034213731270932</v>
+        <v>0.03424439832174866</v>
       </c>
       <c r="Z2">
         <v>1.344685525994399</v>
@@ -662,10 +662,10 @@
         <v>0.09858451922176539</v>
       </c>
       <c r="AB2">
-        <v>0.08943252963885542</v>
+        <v>0.08941196474270305</v>
       </c>
       <c r="AC2">
-        <v>0.00915198958290997</v>
+        <v>0.009172554479062345</v>
       </c>
       <c r="AD2">
         <v>60091</v>
@@ -787,10 +787,10 @@
         <v>0.1456805479972704</v>
       </c>
       <c r="X3">
-        <v>0.1114668167263384</v>
+        <v>0.1114361496755217</v>
       </c>
       <c r="Y3">
-        <v>0.034213731270932</v>
+        <v>0.03424439832174866</v>
       </c>
       <c r="Z3">
         <v>1.344685525994399</v>
@@ -799,10 +799,10 @@
         <v>0.09858451922176539</v>
       </c>
       <c r="AB3">
-        <v>0.08943252963885542</v>
+        <v>0.08941196474270305</v>
       </c>
       <c r="AC3">
-        <v>0.00915198958290997</v>
+        <v>0.009172554479062345</v>
       </c>
       <c r="AD3">
         <v>60091</v>
@@ -1139,49 +1139,49 @@
         <v>11.7597840755735</v>
       </c>
       <c r="F2">
-        <v>3.02682750755665</v>
+        <v>3.02912767427362</v>
       </c>
       <c r="G2">
         <v>1.61239955161121</v>
       </c>
       <c r="H2">
-        <v>3.52422124319289</v>
+        <v>3.67106379499259</v>
       </c>
       <c r="I2">
         <v>0.329413960432372</v>
       </c>
       <c r="J2">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="K2">
         <v>126009.5</v>
       </c>
       <c r="L2">
-        <v>58001.8572873242</v>
+        <v>55949.9156078525</v>
       </c>
       <c r="M2">
         <v>162237.518786354</v>
       </c>
       <c r="N2">
-        <v>167624.710813499</v>
+        <v>171210.054697618</v>
       </c>
       <c r="O2">
         <v>61900.0187863542</v>
       </c>
       <c r="P2">
-        <v>135294.853526175</v>
+        <v>140932.139089766</v>
       </c>
       <c r="Q2">
-        <v>0.0894325296388554</v>
+        <v>0.08941196474270301</v>
       </c>
       <c r="R2">
-        <v>0.0866452447928137</v>
+        <v>0.0848669564495844</v>
       </c>
       <c r="S2">
         <v>0.0445774624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.111466816726338</v>
+        <v>0.111436149675522</v>
       </c>
       <c r="X2">
-        <v>0.186333827839448</v>
+        <v>0.201685438307636</v>
       </c>
       <c r="Y2">
         <v>1.27937072567706</v>
       </c>
       <c r="Z2">
-        <v>2.73798661589478</v>
+        <v>3.03849734202957</v>
       </c>
       <c r="AA2">
         <v>60091</v>
@@ -1236,7 +1236,7 @@
         <v>126009.5</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.0513034637718367</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09378716072566504</v>
+        <v>0.09376475024850341</v>
       </c>
       <c r="C2">
-        <v>180152.9548816363</v>
+        <v>180155.9457972118</v>
       </c>
       <c r="D2">
-        <v>154480.9548816363</v>
+        <v>154483.9457972118</v>
       </c>
       <c r="E2">
         <v>-61900.0187863542</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09378716072566504</v>
+        <v>0.09376475024850341</v>
       </c>
       <c r="T2">
         <v>0.9349222590860211</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09364146744881986</v>
+        <v>0.09360861299785116</v>
       </c>
       <c r="C3">
-        <v>178521.3603829117</v>
+        <v>178542.1390662081</v>
       </c>
       <c r="D3">
-        <v>154728.4555707752</v>
+        <v>154749.2342540716</v>
       </c>
       <c r="E3">
         <v>-60020.92359849066</v>
@@ -1539,37 +1539,37 @@
         <v>26142</v>
       </c>
       <c r="M3">
-        <v>108.3046890153035</v>
+        <v>105.6739557522945</v>
       </c>
       <c r="N3">
-        <v>26033.6953109847</v>
+        <v>26036.3260442477</v>
       </c>
       <c r="O3">
-        <v>6508.423827746175</v>
+        <v>6509.081511061926</v>
       </c>
       <c r="P3">
-        <v>19525.27148323852</v>
+        <v>19527.24453318578</v>
       </c>
       <c r="Q3">
-        <v>31773.27148323852</v>
+        <v>31775.24453318578</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09415069982207158</v>
+        <v>0.09412811956856783</v>
       </c>
       <c r="T3">
         <v>0.9420050034730364</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>241.3745908665703</v>
+        <v>247.3835659306468</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.0934957741719747</v>
+        <v>0.09345247574719891</v>
       </c>
       <c r="C4">
-        <v>176890.5602201688</v>
+        <v>176929.2450388494</v>
       </c>
       <c r="D4">
-        <v>154976.7505958958</v>
+        <v>155015.4354145765</v>
       </c>
       <c r="E4">
         <v>-58141.82841062712</v>
@@ -1621,37 +1621,37 @@
         <v>26142</v>
       </c>
       <c r="M4">
-        <v>216.6093780306069</v>
+        <v>211.347911504589</v>
       </c>
       <c r="N4">
-        <v>25925.39062196939</v>
+        <v>25930.65208849541</v>
       </c>
       <c r="O4">
-        <v>6481.347655492348</v>
+        <v>6482.663022123853</v>
       </c>
       <c r="P4">
-        <v>19444.04296647705</v>
+        <v>19447.98906637156</v>
       </c>
       <c r="Q4">
-        <v>31692.04296647705</v>
+        <v>31695.98906637156</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09452165808371092</v>
+        <v>0.09449890458904173</v>
       </c>
       <c r="T4">
         <v>0.9492322936638684</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>120.6872954332851</v>
+        <v>123.6917829653234</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09335008089512954</v>
+        <v>0.09329633849654664</v>
       </c>
       <c r="C5">
-        <v>175260.5582236018</v>
+        <v>175317.2684333776</v>
       </c>
       <c r="D5">
-        <v>155225.8437871924</v>
+        <v>155282.5539969682</v>
       </c>
       <c r="E5">
         <v>-56262.73322276358</v>
@@ -1703,37 +1703,37 @@
         <v>26142</v>
       </c>
       <c r="M5">
-        <v>324.9140670459104</v>
+        <v>317.0218672568835</v>
       </c>
       <c r="N5">
-        <v>25817.08593295409</v>
+        <v>25824.97813274312</v>
       </c>
       <c r="O5">
-        <v>6454.271483238523</v>
+        <v>6456.244533185779</v>
       </c>
       <c r="P5">
-        <v>19362.81444971557</v>
+        <v>19368.73359955734</v>
       </c>
       <c r="Q5">
-        <v>31610.81444971557</v>
+        <v>31616.73359955734</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09490026496930158</v>
+        <v>0.09487733466148415</v>
       </c>
       <c r="T5">
         <v>0.9566086001472948</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>80.45819695552343</v>
+        <v>82.46118864354894</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09320438761828441</v>
+        <v>0.09314020124589439</v>
       </c>
       <c r="C6">
-        <v>173631.3582480695</v>
+        <v>173706.214000612</v>
       </c>
       <c r="D6">
-        <v>155475.7389995237</v>
+        <v>155550.5947520662</v>
       </c>
       <c r="E6">
         <v>-54383.63803490003</v>
@@ -1785,37 +1785,37 @@
         <v>26142</v>
       </c>
       <c r="M6">
-        <v>433.2187560612139</v>
+        <v>422.695823009178</v>
       </c>
       <c r="N6">
-        <v>25708.78124393879</v>
+        <v>25719.30417699082</v>
       </c>
       <c r="O6">
-        <v>6427.195310984696</v>
+        <v>6429.826044247706</v>
       </c>
       <c r="P6">
-        <v>19281.58593295409</v>
+        <v>19289.47813274312</v>
       </c>
       <c r="Q6">
-        <v>31529.58593295409</v>
+        <v>31537.47813274312</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09528675949834206</v>
+        <v>0.09526364869376913</v>
       </c>
       <c r="T6">
         <v>0.9641385796824593</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.34364771664256</v>
+        <v>61.84589148266171</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09305869434143925</v>
+        <v>0.09298406399524213</v>
       </c>
       <c r="C7">
-        <v>172002.9641732944</v>
+        <v>172096.0865242312</v>
       </c>
       <c r="D7">
-        <v>155726.4401126121</v>
+        <v>155819.5624635489</v>
       </c>
       <c r="E7">
         <v>-52504.54284703649</v>
@@ -1867,37 +1867,37 @@
         <v>26142</v>
       </c>
       <c r="M7">
-        <v>541.5234450765173</v>
+        <v>528.3697787614726</v>
       </c>
       <c r="N7">
-        <v>25600.47655492348</v>
+        <v>25613.63022123853</v>
       </c>
       <c r="O7">
-        <v>6400.119138730871</v>
+        <v>6403.407555309632</v>
       </c>
       <c r="P7">
-        <v>19200.35741619261</v>
+        <v>19210.22266592889</v>
       </c>
       <c r="Q7">
-        <v>31448.35741619261</v>
+        <v>31458.22266592889</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0956813907543097</v>
+        <v>0.09565809565304959</v>
       </c>
       <c r="T7">
         <v>0.9718270851025745</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.27491817331406</v>
+        <v>49.47671318612935</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09291300106459408</v>
+        <v>0.09282792674458989</v>
       </c>
       <c r="C8">
-        <v>170375.3799040631</v>
+        <v>170486.8908210576</v>
       </c>
       <c r="D8">
-        <v>155977.9510312443</v>
+        <v>156089.4619482388</v>
       </c>
       <c r="E8">
         <v>-50625.44765917295</v>
@@ -1949,37 +1949,37 @@
         <v>26142</v>
       </c>
       <c r="M8">
-        <v>649.8281340918207</v>
+        <v>634.0437345137669</v>
       </c>
       <c r="N8">
-        <v>25492.17186590818</v>
+        <v>25507.95626548623</v>
       </c>
       <c r="O8">
-        <v>6373.042966477045</v>
+        <v>6376.989066371559</v>
       </c>
       <c r="P8">
-        <v>19119.12889943113</v>
+        <v>19130.96719911468</v>
       </c>
       <c r="Q8">
-        <v>31367.12889943113</v>
+        <v>31378.96719911468</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09608441841997878</v>
+        <v>0.09606093510082539</v>
       </c>
       <c r="T8">
         <v>0.9796791757443944</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.22909847776171</v>
+        <v>41.23059432177448</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09276730778774891</v>
+        <v>0.09267178949393762</v>
       </c>
       <c r="C9">
-        <v>168748.6093704291</v>
+        <v>168878.6317413448</v>
       </c>
       <c r="D9">
-        <v>156230.2756854739</v>
+        <v>156360.2980563896</v>
       </c>
       <c r="E9">
         <v>-48746.35247130941</v>
@@ -2031,37 +2031,37 @@
         <v>26142</v>
       </c>
       <c r="M9">
-        <v>758.1328231071243</v>
+        <v>739.7176902660616</v>
       </c>
       <c r="N9">
-        <v>25383.86717689288</v>
+        <v>25402.28230973394</v>
       </c>
       <c r="O9">
-        <v>6345.966794223219</v>
+        <v>6350.570577433485</v>
       </c>
       <c r="P9">
-        <v>19037.90038266966</v>
+        <v>19051.71173230045</v>
       </c>
       <c r="Q9">
-        <v>31285.90038266966</v>
+        <v>31299.71173230045</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09649611334727515</v>
+        <v>0.09647243776253182</v>
       </c>
       <c r="T9">
         <v>0.9877001285505546</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.48208440951004</v>
+        <v>35.34050941866383</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09262161451090378</v>
+        <v>0.0925156522432854</v>
       </c>
       <c r="C10">
-        <v>167122.6565279177</v>
+        <v>167271.3141690684</v>
       </c>
       <c r="D10">
-        <v>156483.4180308261</v>
+        <v>156632.0756719767</v>
       </c>
       <c r="E10">
         <v>-46867.25728344587</v>
@@ -2113,37 +2113,37 @@
         <v>26142</v>
       </c>
       <c r="M10">
-        <v>866.4375121224277</v>
+        <v>845.391646018356</v>
       </c>
       <c r="N10">
-        <v>25275.56248787757</v>
+        <v>25296.60835398164</v>
       </c>
       <c r="O10">
-        <v>6318.890621969393</v>
+        <v>6324.152088495411</v>
       </c>
       <c r="P10">
-        <v>18956.67186590818</v>
+        <v>18972.45626548623</v>
       </c>
       <c r="Q10">
-        <v>31204.67186590818</v>
+        <v>31220.45626548623</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09691675816429536</v>
+        <v>0.09689288613427538</v>
       </c>
       <c r="T10">
         <v>0.9958954498959791</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.17182385832128</v>
+        <v>30.92294574133085</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09247592123405861</v>
+        <v>0.09235951499263312</v>
       </c>
       <c r="C11">
-        <v>165497.5253577328</v>
+        <v>165664.9430222194</v>
       </c>
       <c r="D11">
-        <v>156737.3820485047</v>
+        <v>156904.7997129913</v>
       </c>
       <c r="E11">
         <v>-44988.16209558232</v>
@@ -2195,37 +2195,37 @@
         <v>26142</v>
       </c>
       <c r="M11">
-        <v>974.7422011377312</v>
+        <v>951.0656017706506</v>
       </c>
       <c r="N11">
-        <v>25167.25779886227</v>
+        <v>25190.93439822935</v>
       </c>
       <c r="O11">
-        <v>6291.814449715567</v>
+        <v>6297.733599557338</v>
       </c>
       <c r="P11">
-        <v>18875.4433491467</v>
+        <v>18893.20079867201</v>
       </c>
       <c r="Q11">
-        <v>31123.4433491467</v>
+        <v>31141.20079867201</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09734664792234897</v>
+        <v>0.09732257512957371</v>
       </c>
       <c r="T11">
         <v>1.00427088819405</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.81939898517447</v>
+        <v>27.48706288118298</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09233022795721348</v>
+        <v>0.09220337774198088</v>
       </c>
       <c r="C12">
-        <v>163873.2198669652</v>
+        <v>164059.5232531009</v>
       </c>
       <c r="D12">
-        <v>156992.1717456006</v>
+        <v>157178.4751317363</v>
       </c>
       <c r="E12">
         <v>-43109.06690771878</v>
@@ -2277,37 +2277,37 @@
         <v>26142</v>
       </c>
       <c r="M12">
-        <v>1083.046890153035</v>
+        <v>1056.739557522945</v>
       </c>
       <c r="N12">
-        <v>25058.95310984697</v>
+        <v>25085.26044247705</v>
       </c>
       <c r="O12">
-        <v>6264.738277461742</v>
+        <v>6271.315110619264</v>
       </c>
       <c r="P12">
-        <v>18794.21483238522</v>
+        <v>18813.94533185779</v>
       </c>
       <c r="Q12">
-        <v>31042.21483238522</v>
+        <v>31061.94533185779</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09778609078613712</v>
+        <v>0.09776181276921203</v>
       </c>
       <c r="T12">
         <v>1.01283244734319</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.13745908665703</v>
+        <v>24.73835659306468</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0921845346803683</v>
+        <v>0.09204724049132862</v>
       </c>
       <c r="C13">
-        <v>162249.7440888036</v>
+        <v>162455.0598486278</v>
       </c>
       <c r="D13">
-        <v>157247.7911553026</v>
+        <v>157453.1069151267</v>
       </c>
       <c r="E13">
         <v>-41229.97171985524</v>
@@ -2359,37 +2359,37 @@
         <v>26142</v>
       </c>
       <c r="M13">
-        <v>1191.351579168338</v>
+        <v>1162.41351327524</v>
       </c>
       <c r="N13">
-        <v>24950.64842083166</v>
+        <v>24979.58648672476</v>
       </c>
       <c r="O13">
-        <v>6237.662105207915</v>
+        <v>6244.89662168119</v>
       </c>
       <c r="P13">
-        <v>18712.98631562375</v>
+        <v>18734.68986504357</v>
       </c>
       <c r="Q13">
-        <v>30960.98631562375</v>
+        <v>30982.68986504357</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09823540877045982</v>
+        <v>0.09821092091760625</v>
       </c>
       <c r="T13">
         <v>1.02158640107995</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.94314462423366</v>
+        <v>22.48941508460425</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09203884140352314</v>
+        <v>0.09189110324067638</v>
       </c>
       <c r="C14">
-        <v>160627.1020827474</v>
+        <v>160851.5578306298</v>
       </c>
       <c r="D14">
-        <v>157504.2443371099</v>
+        <v>157728.7000849923</v>
       </c>
       <c r="E14">
         <v>-39350.8765319917</v>
@@ -2441,37 +2441,37 @@
         <v>26142</v>
       </c>
       <c r="M14">
-        <v>1299.656268183641</v>
+        <v>1268.087469027534</v>
       </c>
       <c r="N14">
-        <v>24842.34373181636</v>
+        <v>24873.91253097247</v>
       </c>
       <c r="O14">
-        <v>6210.58593295409</v>
+        <v>6218.478132743116</v>
       </c>
       <c r="P14">
-        <v>18631.75779886227</v>
+        <v>18655.43439822935</v>
       </c>
       <c r="Q14">
-        <v>30879.75779886227</v>
+        <v>30903.43439822935</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0986949385271535</v>
+        <v>0.09867023606937309</v>
       </c>
       <c r="T14">
         <v>1.030539308310728</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.11454923888086</v>
+        <v>20.61529716088724</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.091893148126678</v>
+        <v>0.09173496599002412</v>
       </c>
       <c r="C15">
-        <v>159005.2979348215</v>
+        <v>159249.0222561577</v>
       </c>
       <c r="D15">
-        <v>157761.5353770476</v>
+        <v>158005.2596983837</v>
       </c>
       <c r="E15">
         <v>-37471.78134412815</v>
@@ -2523,37 +2523,37 @@
         <v>26142</v>
       </c>
       <c r="M15">
-        <v>1407.960957198945</v>
+        <v>1373.761424779829</v>
       </c>
       <c r="N15">
-        <v>24734.03904280105</v>
+        <v>24768.23857522017</v>
       </c>
       <c r="O15">
-        <v>6183.509760700264</v>
+        <v>6192.059643805042</v>
       </c>
       <c r="P15">
-        <v>18550.52928210079</v>
+        <v>18576.17893141513</v>
       </c>
       <c r="Q15">
-        <v>30798.52928210079</v>
+        <v>30824.17893141513</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09916503218629991</v>
+        <v>0.09914011019014603</v>
       </c>
       <c r="T15">
         <v>1.039698029500834</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.5672762205054</v>
+        <v>19.02950507158821</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09174745484983284</v>
+        <v>0.09157882873937187</v>
       </c>
       <c r="C16">
-        <v>157384.3357577936</v>
+        <v>157647.458217792</v>
       </c>
       <c r="D16">
-        <v>158019.6683878832</v>
+        <v>158282.7908478816</v>
       </c>
       <c r="E16">
         <v>-35592.68615626461</v>
@@ -2605,37 +2605,37 @@
         <v>26142</v>
       </c>
       <c r="M16">
-        <v>1516.265646214249</v>
+        <v>1479.435380532123</v>
       </c>
       <c r="N16">
-        <v>24625.73435378575</v>
+        <v>24662.56461946788</v>
       </c>
       <c r="O16">
-        <v>6156.433588446438</v>
+        <v>6165.641154866969</v>
       </c>
       <c r="P16">
-        <v>18469.30076533931</v>
+        <v>18496.92346460091</v>
       </c>
       <c r="Q16">
-        <v>30717.30076533931</v>
+        <v>30744.92346460091</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09964605825612413</v>
+        <v>0.09962091161605324</v>
       </c>
       <c r="T16">
         <v>1.049069744206989</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.24104220475502</v>
+        <v>17.67025470933191</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09160176157298766</v>
+        <v>0.09142269148871961</v>
       </c>
       <c r="C17">
-        <v>155764.2196913929</v>
+        <v>156046.8708439565</v>
       </c>
       <c r="D17">
-        <v>158278.6475093461</v>
+        <v>158561.2986619096</v>
       </c>
       <c r="E17">
         <v>-33713.59096840107</v>
@@ -2687,37 +2687,37 @@
         <v>26142</v>
       </c>
       <c r="M17">
-        <v>1624.570335229552</v>
+        <v>1585.109336284418</v>
       </c>
       <c r="N17">
-        <v>24517.42966477045</v>
+        <v>24556.89066371558</v>
       </c>
       <c r="O17">
-        <v>6129.357416192612</v>
+        <v>6139.222665928895</v>
       </c>
       <c r="P17">
-        <v>18388.07224857784</v>
+        <v>18417.66799778669</v>
       </c>
       <c r="Q17">
-        <v>30636.07224857784</v>
+        <v>30665.66799778669</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1001384025864148</v>
+        <v>0.1001130260166877</v>
       </c>
       <c r="T17">
         <v>1.058661969847406</v>
       </c>
       <c r="U17">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.09163939110469</v>
+        <v>16.49223772870979</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09145606829614253</v>
+        <v>0.09126655423806737</v>
       </c>
       <c r="C18">
-        <v>154144.9539025317</v>
+        <v>154447.2652992332</v>
       </c>
       <c r="D18">
-        <v>158538.4769083484</v>
+        <v>158840.7883050498</v>
       </c>
       <c r="E18">
         <v>-31834.49578053753</v>
@@ -2769,37 +2769,37 @@
         <v>26142</v>
       </c>
       <c r="M18">
-        <v>1732.875024244855</v>
+        <v>1690.783292036712</v>
       </c>
       <c r="N18">
-        <v>24409.12497575514</v>
+        <v>24451.21670796329</v>
       </c>
       <c r="O18">
-        <v>6102.281243938786</v>
+        <v>6112.804176990822</v>
       </c>
       <c r="P18">
-        <v>18306.84373181636</v>
+        <v>18338.41253097247</v>
       </c>
       <c r="Q18">
-        <v>30554.84373181636</v>
+        <v>30586.41253097247</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.10064246940076</v>
+        <v>0.1006168574268611</v>
       </c>
       <c r="T18">
         <v>1.068482581812596</v>
       </c>
       <c r="U18">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.08591192916064</v>
+        <v>15.46147287066543</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09131037501929735</v>
+        <v>0.09111041698741511</v>
       </c>
       <c r="C19">
-        <v>152526.542585529</v>
+        <v>152848.6467846823</v>
       </c>
       <c r="D19">
-        <v>158799.1607792092</v>
+        <v>159121.2649783625</v>
       </c>
       <c r="E19">
         <v>-29955.40059267398</v>
@@ -2851,37 +2851,37 @@
         <v>26142</v>
       </c>
       <c r="M19">
-        <v>1841.179713260159</v>
+        <v>1796.457247789007</v>
       </c>
       <c r="N19">
-        <v>24300.82028673984</v>
+        <v>24345.54275221099</v>
       </c>
       <c r="O19">
-        <v>6075.20507168496</v>
+        <v>6086.385688052748</v>
       </c>
       <c r="P19">
-        <v>18225.61521505488</v>
+        <v>18259.15706415824</v>
       </c>
       <c r="Q19">
-        <v>30473.61521505488</v>
+        <v>30507.15706415824</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1011586824034027</v>
+        <v>0.1011328293529422</v>
       </c>
       <c r="T19">
         <v>1.078539835029958</v>
       </c>
       <c r="U19">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.19850534509237</v>
+        <v>14.55197446650863</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09116468174245221</v>
+        <v>0.09095427973676287</v>
       </c>
       <c r="C20">
-        <v>150908.9899623357</v>
+        <v>151251.0205381645</v>
       </c>
       <c r="D20">
-        <v>159060.7033438794</v>
+        <v>159402.7339197083</v>
       </c>
       <c r="E20">
         <v>-28076.30540481045</v>
@@ -2933,37 +2933,37 @@
         <v>26142</v>
       </c>
       <c r="M20">
-        <v>1949.484402275462</v>
+        <v>1902.131203541301</v>
       </c>
       <c r="N20">
-        <v>24192.51559772454</v>
+        <v>24239.8687964587</v>
       </c>
       <c r="O20">
-        <v>6048.128899431134</v>
+        <v>6059.967199114675</v>
       </c>
       <c r="P20">
-        <v>18144.38669829341</v>
+        <v>18179.90159734403</v>
       </c>
       <c r="Q20">
-        <v>30392.38669829341</v>
+        <v>30427.90159734403</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1016874859670855</v>
+        <v>0.1016613859601473</v>
       </c>
       <c r="T20">
         <v>1.088842387106281</v>
       </c>
       <c r="U20">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.40969949258724</v>
+        <v>13.74353144059149</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09101898846560705</v>
+        <v>0.09079814248611062</v>
       </c>
       <c r="C21">
-        <v>149292.300282763</v>
+        <v>149654.391834667</v>
       </c>
       <c r="D21">
-        <v>159323.1088521703</v>
+        <v>159685.2004040743</v>
       </c>
       <c r="E21">
         <v>-26197.21021694691</v>
@@ -3015,37 +3015,37 @@
         <v>26142</v>
       </c>
       <c r="M21">
-        <v>2057.789091290766</v>
+        <v>2007.805159293596</v>
       </c>
       <c r="N21">
-        <v>24084.21090870924</v>
+        <v>24134.1948407064</v>
       </c>
       <c r="O21">
-        <v>6021.052727177309</v>
+        <v>6033.548710176601</v>
       </c>
       <c r="P21">
-        <v>18063.15818153193</v>
+        <v>18100.6461305298</v>
       </c>
       <c r="Q21">
-        <v>30311.15818153193</v>
+        <v>30348.6461305298</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1022293464088839</v>
+        <v>0.1022029933477772</v>
       </c>
       <c r="T21">
         <v>1.099399323184488</v>
       </c>
       <c r="U21">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.70392583508265</v>
+        <v>13.02018768056036</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09087329518876189</v>
+        <v>0.09064200523545836</v>
       </c>
       <c r="C22">
-        <v>147676.4778247125</v>
+        <v>148058.7659866332</v>
       </c>
       <c r="D22">
-        <v>159586.3815819833</v>
+        <v>159968.6697439041</v>
       </c>
       <c r="E22">
         <v>-24318.11502908336</v>
@@ -3097,37 +3097,37 @@
         <v>26142</v>
       </c>
       <c r="M22">
-        <v>2166.093780306069</v>
+        <v>2113.47911504589</v>
       </c>
       <c r="N22">
-        <v>23975.90621969393</v>
+        <v>24028.52088495411</v>
       </c>
       <c r="O22">
-        <v>5993.976554923483</v>
+        <v>6007.130221238527</v>
       </c>
       <c r="P22">
-        <v>17981.92966477045</v>
+        <v>18021.39066371558</v>
       </c>
       <c r="Q22">
-        <v>30229.92966477045</v>
+        <v>30269.39066371558</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1027847533617272</v>
+        <v>0.1027581409200978</v>
       </c>
       <c r="T22">
         <v>1.11022018266465</v>
       </c>
       <c r="U22">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.06872954332851</v>
+        <v>12.36917829653234</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09072760191191673</v>
+        <v>0.0904858679848061</v>
       </c>
       <c r="C23">
-        <v>146061.5268944084</v>
+        <v>146464.1483442957</v>
       </c>
       <c r="D23">
-        <v>159850.5258395428</v>
+        <v>160253.1472894301</v>
       </c>
       <c r="E23">
         <v>-22439.01984121982</v>
@@ -3179,37 +3179,37 @@
         <v>26142</v>
       </c>
       <c r="M23">
-        <v>2274.398469321372</v>
+        <v>2219.153070798185</v>
       </c>
       <c r="N23">
-        <v>23867.60153067863</v>
+        <v>23922.84692920182</v>
       </c>
       <c r="O23">
-        <v>5966.900382669657</v>
+        <v>5980.711732300454</v>
       </c>
       <c r="P23">
-        <v>17900.70114800897</v>
+        <v>17942.13519690136</v>
       </c>
       <c r="Q23">
-        <v>30148.70114800897</v>
+        <v>30190.13519690136</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1033542212500856</v>
+        <v>0.1033273428613379</v>
       </c>
       <c r="T23">
         <v>1.121314987954437</v>
       </c>
       <c r="U23">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.49402813650335</v>
+        <v>11.78016980622128</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09058190863507157</v>
+        <v>0.09032973073415385</v>
       </c>
       <c r="C24">
-        <v>144447.4518266327</v>
+        <v>144870.5442960126</v>
       </c>
       <c r="D24">
-        <v>160115.5459596306</v>
+        <v>160538.6384290105</v>
       </c>
       <c r="E24">
         <v>-20559.92465335628</v>
@@ -3261,37 +3261,37 @@
         <v>26142</v>
       </c>
       <c r="M24">
-        <v>2382.703158336677</v>
+        <v>2324.827026550479</v>
       </c>
       <c r="N24">
-        <v>23759.29684166332</v>
+        <v>23817.17297344952</v>
       </c>
       <c r="O24">
-        <v>5939.824210415831</v>
+        <v>5954.29324336238</v>
       </c>
       <c r="P24">
-        <v>17819.47263124749</v>
+        <v>17862.87973008714</v>
       </c>
       <c r="Q24">
-        <v>30067.47263124749</v>
+        <v>30110.87973008714</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1039382908791711</v>
+        <v>0.1039111397241484</v>
       </c>
       <c r="T24">
         <v>1.132694275431141</v>
       </c>
       <c r="U24">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.97157231211683</v>
+        <v>11.24470754230212</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09043621535822642</v>
+        <v>0.0901735934835016</v>
       </c>
       <c r="C25">
-        <v>142834.2569849618</v>
+        <v>143277.9592686085</v>
       </c>
       <c r="D25">
-        <v>160381.4463058233</v>
+        <v>160825.1485894699</v>
       </c>
       <c r="E25">
         <v>-18680.82946549274</v>
@@ -3343,37 +3343,37 @@
         <v>26142</v>
       </c>
       <c r="M25">
-        <v>2491.00784735198</v>
+        <v>2430.500982302774</v>
       </c>
       <c r="N25">
-        <v>23650.99215264802</v>
+        <v>23711.49901769723</v>
       </c>
       <c r="O25">
-        <v>5912.748038162005</v>
+        <v>5927.874754424307</v>
       </c>
       <c r="P25">
-        <v>17738.24411448602</v>
+        <v>17783.62426327292</v>
       </c>
       <c r="Q25">
-        <v>29986.24411448602</v>
+        <v>30031.62426327292</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1045375311479731</v>
+        <v>0.104510100141837</v>
       </c>
       <c r="T25">
         <v>1.144369128816331</v>
       </c>
       <c r="U25">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.49454742898132</v>
+        <v>10.75580721437595</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09029052208138127</v>
+        <v>0.09001745623284933</v>
       </c>
       <c r="C26">
-        <v>141221.9467620067</v>
+        <v>141686.3987277173</v>
       </c>
       <c r="D26">
-        <v>160648.2312707317</v>
+        <v>161112.6832364423</v>
       </c>
       <c r="E26">
         <v>-16801.7342776292</v>
@@ -3425,37 +3425,37 @@
         <v>26142</v>
       </c>
       <c r="M26">
-        <v>2599.312536367283</v>
+        <v>2536.174938055068</v>
       </c>
       <c r="N26">
-        <v>23542.68746363272</v>
+        <v>23605.82506194493</v>
       </c>
       <c r="O26">
-        <v>5885.671865908179</v>
+        <v>5901.456265486233</v>
       </c>
       <c r="P26">
-        <v>17657.01559772454</v>
+        <v>17704.3687964587</v>
       </c>
       <c r="Q26">
-        <v>29905.01559772454</v>
+        <v>29952.3687964587</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1051525408975331</v>
+        <v>0.1051248226757805</v>
       </c>
       <c r="T26">
         <v>1.156351215185342</v>
       </c>
       <c r="U26">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.05727461944043</v>
+        <v>10.30764858044362</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09014482880453611</v>
+        <v>0.0898613189821971</v>
       </c>
       <c r="C27">
-        <v>139610.5255796542</v>
+        <v>140095.8681781307</v>
       </c>
       <c r="D27">
-        <v>160915.9052762427</v>
+        <v>161401.2478747192</v>
       </c>
       <c r="E27">
         <v>-14922.63908976565</v>
@@ -3507,37 +3507,37 @@
         <v>26142</v>
       </c>
       <c r="M27">
-        <v>2707.617225382587</v>
+        <v>2641.848893807363</v>
       </c>
       <c r="N27">
-        <v>23434.38277461741</v>
+        <v>23500.15110619264</v>
       </c>
       <c r="O27">
-        <v>5858.595693654353</v>
+        <v>5875.037776548159</v>
       </c>
       <c r="P27">
-        <v>17575.78708096306</v>
+        <v>17625.11332964448</v>
       </c>
       <c r="Q27">
-        <v>29823.78708096306</v>
+        <v>29873.11332964448</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1057839509070813</v>
+        <v>0.1057559378106293</v>
       </c>
       <c r="T27">
         <v>1.168652823857526</v>
       </c>
       <c r="U27">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.654983634662811</v>
+        <v>9.89534263722587</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08999913552769094</v>
+        <v>0.08970518173154483</v>
       </c>
       <c r="C28">
-        <v>137999.9978893115</v>
+        <v>138506.373164149</v>
       </c>
       <c r="D28">
-        <v>161184.4727737636</v>
+        <v>161690.8480486011</v>
       </c>
       <c r="E28">
         <v>-13043.54390190211</v>
@@ -3589,37 +3589,37 @@
         <v>26142</v>
       </c>
       <c r="M28">
-        <v>2815.92191439789</v>
+        <v>2747.522849559658</v>
       </c>
       <c r="N28">
-        <v>23326.07808560211</v>
+        <v>23394.47715044034</v>
       </c>
       <c r="O28">
-        <v>5831.519521400527</v>
+        <v>5848.619287610086</v>
       </c>
       <c r="P28">
-        <v>17494.55856420158</v>
+        <v>17545.85786283026</v>
       </c>
       <c r="Q28">
-        <v>29742.55856420158</v>
+        <v>29793.85786283026</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1064324260520227</v>
+        <v>0.1064041101112847</v>
       </c>
       <c r="T28">
         <v>1.18128690843977</v>
       </c>
       <c r="U28">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.283638110252701</v>
+        <v>9.514752535794107</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08985344225084579</v>
+        <v>0.08954904448089258</v>
       </c>
       <c r="C29">
-        <v>136390.3681721532</v>
+        <v>136917.9192699362</v>
       </c>
       <c r="D29">
-        <v>161453.9382444688</v>
+        <v>161981.4893422518</v>
       </c>
       <c r="E29">
         <v>-11164.44871403857</v>
@@ -3671,37 +3671,37 @@
         <v>26142</v>
       </c>
       <c r="M29">
-        <v>2924.226603413194</v>
+        <v>2853.196805311952</v>
       </c>
       <c r="N29">
-        <v>23217.77339658681</v>
+        <v>23288.80319468805</v>
       </c>
       <c r="O29">
-        <v>5804.443349146702</v>
+        <v>5822.200798672012</v>
       </c>
       <c r="P29">
-        <v>17413.3300474401</v>
+        <v>17466.60239601603</v>
       </c>
       <c r="Q29">
-        <v>29661.3300474401</v>
+        <v>29714.60239601603</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1070986676392913</v>
+        <v>0.1070700405571636</v>
       </c>
       <c r="T29">
         <v>1.194267132325637</v>
       </c>
       <c r="U29">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.939799661724823</v>
+        <v>9.162354293727658</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08993874897400063</v>
+        <v>0.08939290723024033</v>
       </c>
       <c r="C30">
-        <v>134353.3856099145</v>
+        <v>135330.5121198791</v>
       </c>
       <c r="D30">
-        <v>161296.0508700937</v>
+        <v>162273.1773800582</v>
       </c>
       <c r="E30">
         <v>-9285.353526175022</v>
@@ -3753,45 +3753,45 @@
         <v>26142</v>
       </c>
       <c r="M30">
-        <v>3090.407424214694</v>
+        <v>2958.870761064246</v>
       </c>
       <c r="N30">
-        <v>23051.5925757853</v>
+        <v>23183.12923893575</v>
       </c>
       <c r="O30">
-        <v>5762.898143946326</v>
+        <v>5795.782309733939</v>
       </c>
       <c r="P30">
-        <v>17288.69443183898</v>
+        <v>17387.34692920182</v>
       </c>
       <c r="Q30">
-        <v>29536.69443183898</v>
+        <v>29635.34692920182</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1077834159373173</v>
+        <v>0.1077544690709836</v>
       </c>
       <c r="T30">
         <v>1.207607917986111</v>
       </c>
       <c r="U30">
-        <v>0.0587366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04405246249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>8.459078824094838</v>
+        <v>8.835127354665957</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08980130569715547</v>
+        <v>0.08956301997958807</v>
       </c>
       <c r="C31">
-        <v>132728.8254391568</v>
+        <v>133133.6716679267</v>
       </c>
       <c r="D31">
-        <v>161550.5858871995</v>
+        <v>161955.4321159694</v>
       </c>
       <c r="E31">
         <v>-7406.258338311491</v>
@@ -3835,37 +3835,37 @@
         <v>26142</v>
       </c>
       <c r="M31">
-        <v>3200.779117936647</v>
+        <v>3146.285357488604</v>
       </c>
       <c r="N31">
-        <v>22941.22088206335</v>
+        <v>22995.7146425114</v>
       </c>
       <c r="O31">
-        <v>5735.305220515838</v>
+        <v>5748.928660627849</v>
       </c>
       <c r="P31">
-        <v>17205.91566154751</v>
+        <v>17246.78598188355</v>
       </c>
       <c r="Q31">
-        <v>29453.91566154751</v>
+        <v>29494.78598188355</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1084874529197948</v>
+        <v>0.1084581772612492</v>
       </c>
       <c r="T31">
         <v>1.221324500425753</v>
       </c>
       <c r="U31">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.167386450850191</v>
+        <v>8.308845838721634</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08966386242031031</v>
+        <v>0.08941813272893583</v>
       </c>
       <c r="C32">
-        <v>131105.0698817261</v>
+        <v>131525.1255614397</v>
       </c>
       <c r="D32">
-        <v>161805.9255176324</v>
+        <v>162225.9811973459</v>
       </c>
       <c r="E32">
         <v>-5527.163150447945</v>
@@ -3917,37 +3917,37 @@
         <v>26142</v>
       </c>
       <c r="M32">
-        <v>3311.150811658601</v>
+        <v>3254.777956022694</v>
       </c>
       <c r="N32">
-        <v>22830.8491883414</v>
+        <v>22887.2220439773</v>
       </c>
       <c r="O32">
-        <v>5707.71229708535</v>
+        <v>5721.805510994326</v>
       </c>
       <c r="P32">
-        <v>17123.13689125605</v>
+        <v>17165.41653298298</v>
       </c>
       <c r="Q32">
-        <v>29371.13689125605</v>
+        <v>29413.41653298298</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1092116052446288</v>
+        <v>0.1091819913998081</v>
       </c>
       <c r="T32">
         <v>1.235432985220814</v>
       </c>
       <c r="U32">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.895140235821851</v>
+        <v>8.031884310764246</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08952641914346515</v>
+        <v>0.08927324547828357</v>
       </c>
       <c r="C33">
-        <v>129482.1227588696</v>
+        <v>129917.4848804206</v>
       </c>
       <c r="D33">
-        <v>162062.0735826395</v>
+        <v>162497.4357041904</v>
       </c>
       <c r="E33">
         <v>-3648.067962584399</v>
@@ -3999,37 +3999,37 @@
         <v>26142</v>
       </c>
       <c r="M33">
-        <v>3421.522505380554</v>
+        <v>3363.270554556784</v>
       </c>
       <c r="N33">
-        <v>22720.47749461944</v>
+        <v>22778.72944544322</v>
       </c>
       <c r="O33">
-        <v>5680.119373654861</v>
+        <v>5694.682361360804</v>
       </c>
       <c r="P33">
-        <v>17040.35812096459</v>
+        <v>17084.04708408241</v>
       </c>
       <c r="Q33">
-        <v>29288.35812096459</v>
+        <v>29332.04708408241</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1099567474919217</v>
+        <v>0.1099267856583252</v>
       </c>
       <c r="T33">
         <v>1.249950411604137</v>
       </c>
       <c r="U33">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.640458292730823</v>
+        <v>7.772791268481528</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08938897586661999</v>
+        <v>0.08912835822763129</v>
       </c>
       <c r="C34">
-        <v>127859.9879160701</v>
+        <v>128310.7541776626</v>
       </c>
       <c r="D34">
-        <v>162319.0339277034</v>
+        <v>162769.8001892959</v>
       </c>
       <c r="E34">
         <v>-1768.97277472086</v>
@@ -4081,37 +4081,37 @@
         <v>26142</v>
       </c>
       <c r="M34">
-        <v>3531.894199102507</v>
+        <v>3471.763153090874</v>
       </c>
       <c r="N34">
-        <v>22610.10580089749</v>
+        <v>22670.23684690913</v>
       </c>
       <c r="O34">
-        <v>5652.526450224374</v>
+        <v>5667.559211727282</v>
       </c>
       <c r="P34">
-        <v>16957.57935067312</v>
+        <v>17002.67763518184</v>
       </c>
       <c r="Q34">
-        <v>29205.57935067312</v>
+        <v>29250.67763518184</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1107238056876644</v>
+        <v>0.1106934856303281</v>
       </c>
       <c r="T34">
         <v>1.264894821116382</v>
       </c>
       <c r="U34">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.401693971082986</v>
+        <v>7.529891541341481</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08925153258977485</v>
+        <v>0.08898347097697906</v>
       </c>
       <c r="C35">
-        <v>126238.6692232378</v>
+        <v>126704.938036534</v>
       </c>
       <c r="D35">
-        <v>162576.8104227346</v>
+        <v>163043.0792360309</v>
       </c>
       <c r="E35">
         <v>110.1224131426861</v>
@@ -4163,37 +4163,37 @@
         <v>26142</v>
       </c>
       <c r="M35">
-        <v>3642.265892824461</v>
+        <v>3580.255751624964</v>
       </c>
       <c r="N35">
-        <v>22499.73410717554</v>
+        <v>22561.74424837503</v>
       </c>
       <c r="O35">
-        <v>5624.933526793885</v>
+        <v>5640.436062093759</v>
       </c>
       <c r="P35">
-        <v>16874.80058038166</v>
+        <v>16921.30818628128</v>
       </c>
       <c r="Q35">
-        <v>29122.80058038166</v>
+        <v>29169.30818628128</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1115137611429816</v>
+        <v>0.1114830721686595</v>
       </c>
       <c r="T35">
         <v>1.280285332405111</v>
       </c>
       <c r="U35">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.177400214383502</v>
+        <v>7.301713009785677</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08911408931292969</v>
+        <v>0.0888385837263268</v>
       </c>
       <c r="C36">
-        <v>124618.1705749052</v>
+        <v>125100.0410712361</v>
       </c>
       <c r="D36">
-        <v>162835.4069622656</v>
+        <v>163317.2774585965</v>
       </c>
       <c r="E36">
         <v>1989.217601006232</v>
@@ -4245,37 +4245,37 @@
         <v>26142</v>
       </c>
       <c r="M36">
-        <v>3752.637586546415</v>
+        <v>3688.748350159054</v>
       </c>
       <c r="N36">
-        <v>22389.36241345359</v>
+        <v>22453.25164984095</v>
       </c>
       <c r="O36">
-        <v>5597.340603363396</v>
+        <v>5613.312912460236</v>
       </c>
       <c r="P36">
-        <v>16792.02181009019</v>
+        <v>16839.93873738071</v>
       </c>
       <c r="Q36">
-        <v>29040.02181009019</v>
+        <v>29087.93873738071</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1123276546423992</v>
+        <v>0.1122965855717888</v>
       </c>
       <c r="T36">
         <v>1.296142222823802</v>
       </c>
       <c r="U36">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.966300208078104</v>
+        <v>7.086956744791981</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08897664603608453</v>
+        <v>0.08869369647567456</v>
       </c>
       <c r="C37">
-        <v>122998.4958904231</v>
+        <v>123496.0679270615</v>
       </c>
       <c r="D37">
-        <v>163094.8274656471</v>
+        <v>163592.3995022855</v>
       </c>
       <c r="E37">
         <v>3868.312788869771</v>
@@ -4327,37 +4327,37 @@
         <v>26142</v>
       </c>
       <c r="M37">
-        <v>3863.009280268368</v>
+        <v>3797.240948693144</v>
       </c>
       <c r="N37">
-        <v>22278.99071973163</v>
+        <v>22344.75905130686</v>
       </c>
       <c r="O37">
-        <v>5569.747679932908</v>
+        <v>5586.189762826714</v>
       </c>
       <c r="P37">
-        <v>16709.24303979872</v>
+        <v>16758.56928848014</v>
       </c>
       <c r="Q37">
-        <v>28957.24303979872</v>
+        <v>29006.56928848014</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1131665910187221</v>
+        <v>0.1131351301565529</v>
       </c>
       <c r="T37">
         <v>1.312487017563068</v>
       </c>
       <c r="U37">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.767263059275872</v>
+        <v>6.884472266369353</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08943320275923938</v>
+        <v>0.08854880922502231</v>
       </c>
       <c r="C38">
-        <v>120260.8328551207</v>
+        <v>121893.0232806577</v>
       </c>
       <c r="D38">
-        <v>162236.2596182082</v>
+        <v>163868.4500437452</v>
       </c>
       <c r="E38">
         <v>5747.40797673331</v>
@@ -4409,45 +4409,45 @@
         <v>26142</v>
       </c>
       <c r="M38">
-        <v>4122.205312869113</v>
+        <v>3905.733547227233</v>
       </c>
       <c r="N38">
-        <v>22019.79468713089</v>
+        <v>22236.26645277277</v>
       </c>
       <c r="O38">
-        <v>5504.948671782722</v>
+        <v>5559.066613193192</v>
       </c>
       <c r="P38">
-        <v>16514.84601534816</v>
+        <v>16677.19983957957</v>
       </c>
       <c r="Q38">
-        <v>28762.84601534816</v>
+        <v>28925.19983957957</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1140317441568049</v>
+        <v>0.1139998792595908</v>
       </c>
       <c r="T38">
         <v>1.329342587137936</v>
       </c>
       <c r="U38">
-        <v>0.0609366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04570246249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.341751081244617</v>
+        <v>6.693236925636872</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08931225948239424</v>
+        <v>0.08887567197437005</v>
       </c>
       <c r="C39">
-        <v>118608.2935779038</v>
+        <v>119392.4784413257</v>
       </c>
       <c r="D39">
-        <v>162462.8155288548</v>
+        <v>163247.0003922767</v>
       </c>
       <c r="E39">
         <v>7626.503164596848</v>
@@ -4491,37 +4491,37 @@
         <v>26142</v>
       </c>
       <c r="M39">
-        <v>4236.711016004367</v>
+        <v>4132.42123307794</v>
       </c>
       <c r="N39">
-        <v>21905.28898399563</v>
+        <v>22009.57876692206</v>
       </c>
       <c r="O39">
-        <v>5476.322245998908</v>
+        <v>5502.394691730515</v>
       </c>
       <c r="P39">
-        <v>16428.96673799672</v>
+        <v>16507.18407519154</v>
       </c>
       <c r="Q39">
-        <v>28676.96673799672</v>
+        <v>28755.18407519154</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1149243624738746</v>
+        <v>0.1148920807151061</v>
       </c>
       <c r="T39">
         <v>1.346733254159626</v>
       </c>
       <c r="U39">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.17035240337314</v>
+        <v>6.326073390279413</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08919131620554907</v>
+        <v>0.08874353472371781</v>
       </c>
       <c r="C40">
-        <v>116956.3879365676</v>
+        <v>117764.0414885865</v>
       </c>
       <c r="D40">
-        <v>162690.0050753822</v>
+        <v>163497.658627401</v>
       </c>
       <c r="E40">
         <v>9505.598352460387</v>
@@ -4573,37 +4573,37 @@
         <v>26142</v>
       </c>
       <c r="M40">
-        <v>4351.216719139619</v>
+        <v>4244.108293431397</v>
       </c>
       <c r="N40">
-        <v>21790.78328086038</v>
+        <v>21897.8917065686</v>
       </c>
       <c r="O40">
-        <v>5447.695820215095</v>
+        <v>5474.472926642151</v>
       </c>
       <c r="P40">
-        <v>16343.08746064529</v>
+        <v>16423.41877992645</v>
       </c>
       <c r="Q40">
-        <v>28591.08746064529</v>
+        <v>28671.41877992645</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1158457749302046</v>
+        <v>0.1158130628627348</v>
       </c>
       <c r="T40">
         <v>1.364684910440079</v>
       </c>
       <c r="U40">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.007974708547532</v>
+        <v>6.159597774745746</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08907037292870391</v>
+        <v>0.08861139747306554</v>
       </c>
       <c r="C41">
-        <v>115305.1185930821</v>
+        <v>116136.3754678817</v>
       </c>
       <c r="D41">
-        <v>162917.8309197602</v>
+        <v>163749.0877945599</v>
       </c>
       <c r="E41">
         <v>11384.69354032394</v>
@@ -4655,37 +4655,37 @@
         <v>26142</v>
       </c>
       <c r="M41">
-        <v>4465.722422274873</v>
+        <v>4355.795353784856</v>
       </c>
       <c r="N41">
-        <v>21676.27757772513</v>
+        <v>21786.20464621514</v>
       </c>
       <c r="O41">
-        <v>5419.069394431282</v>
+        <v>5446.551161553786</v>
       </c>
       <c r="P41">
-        <v>16257.20818329385</v>
+        <v>16339.65348466136</v>
       </c>
       <c r="Q41">
-        <v>28505.20818329385</v>
+        <v>28587.65348466136</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1167973976310044</v>
+        <v>0.1167642411463513</v>
       </c>
       <c r="T41">
         <v>1.383225145614974</v>
       </c>
       <c r="U41">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.85392407499503</v>
+        <v>6.001659370265084</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08894942965185874</v>
+        <v>0.0884792602224133</v>
       </c>
       <c r="C42">
-        <v>113654.4882243488</v>
+        <v>114509.4839413421</v>
       </c>
       <c r="D42">
-        <v>163146.2957388905</v>
+        <v>164001.2914558838</v>
       </c>
       <c r="E42">
         <v>13263.78872818748</v>
@@ -4737,37 +4737,37 @@
         <v>26142</v>
       </c>
       <c r="M42">
-        <v>4580.228125410126</v>
+        <v>4467.482414138313</v>
       </c>
       <c r="N42">
-        <v>21561.77187458987</v>
+        <v>21674.51758586169</v>
       </c>
       <c r="O42">
-        <v>5390.442968647469</v>
+        <v>5418.629396465421</v>
       </c>
       <c r="P42">
-        <v>16171.32890594241</v>
+        <v>16255.88818939626</v>
       </c>
       <c r="Q42">
-        <v>28419.32890594241</v>
+        <v>28503.88818939626</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1177807410884975</v>
+        <v>0.1177471253727551</v>
       </c>
       <c r="T42">
         <v>1.402383388629032</v>
       </c>
       <c r="U42">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.707575973120155</v>
+        <v>5.851617886008458</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08928973637501361</v>
+        <v>0.08834712297176106</v>
       </c>
       <c r="C43">
-        <v>111134.1739443552</v>
+        <v>112883.3704930775</v>
       </c>
       <c r="D43">
-        <v>162505.0766467604</v>
+        <v>164254.2731954827</v>
       </c>
       <c r="E43">
         <v>15142.88391605102</v>
@@ -4819,45 +4819,45 @@
         <v>26142</v>
       </c>
       <c r="M43">
-        <v>4810.298182598987</v>
+        <v>4579.169474491771</v>
       </c>
       <c r="N43">
-        <v>21331.70181740101</v>
+        <v>21562.83052550823</v>
       </c>
       <c r="O43">
-        <v>5332.925454350253</v>
+        <v>5390.707631377058</v>
       </c>
       <c r="P43">
-        <v>15998.77636305076</v>
+        <v>16172.12289413117</v>
       </c>
       <c r="Q43">
-        <v>28246.77636305076</v>
+        <v>28420.12289413117</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1187974182225159</v>
+        <v>0.1187633277085285</v>
       </c>
       <c r="T43">
         <v>1.422191063609668</v>
       </c>
       <c r="U43">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04682746249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>5.434590332584241</v>
+        <v>5.708895498544837</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08918004309816846</v>
+        <v>0.0884669857211088</v>
       </c>
       <c r="C44">
-        <v>109461.2158713247</v>
+        <v>110774.7607234946</v>
       </c>
       <c r="D44">
-        <v>162711.2137615935</v>
+        <v>164024.7586137633</v>
       </c>
       <c r="E44">
         <v>17021.97910391456</v>
@@ -4901,37 +4901,37 @@
         <v>26142</v>
       </c>
       <c r="M44">
-        <v>4927.622528516035</v>
+        <v>4753.994133157444</v>
       </c>
       <c r="N44">
-        <v>21214.37747148396</v>
+        <v>21388.00586684256</v>
       </c>
       <c r="O44">
-        <v>5303.594367870991</v>
+        <v>5347.001466710639</v>
       </c>
       <c r="P44">
-        <v>15910.78310361297</v>
+        <v>16041.00440013192</v>
       </c>
       <c r="Q44">
-        <v>28158.78310361297</v>
+        <v>28289.00440013192</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1198491531887417</v>
+        <v>0.1198145715041561</v>
       </c>
       <c r="T44">
         <v>1.442681761865498</v>
       </c>
       <c r="U44">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.305195324665569</v>
+        <v>5.498955040282593</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08907034982132328</v>
+        <v>0.08834084847045656</v>
       </c>
       <c r="C45">
-        <v>107788.7814309222</v>
+        <v>109137.2122979935</v>
       </c>
       <c r="D45">
-        <v>162917.8745090545</v>
+        <v>164266.3053761258</v>
       </c>
       <c r="E45">
         <v>18901.0742917781</v>
@@ -4983,37 +4983,37 @@
         <v>26142</v>
       </c>
       <c r="M45">
-        <v>5044.946874433083</v>
+        <v>4867.184469661192</v>
       </c>
       <c r="N45">
-        <v>21097.05312556692</v>
+        <v>21274.81553033881</v>
       </c>
       <c r="O45">
-        <v>5274.263281391729</v>
+        <v>5318.703882584702</v>
       </c>
       <c r="P45">
-        <v>15822.78984417519</v>
+        <v>15956.11164775411</v>
       </c>
       <c r="Q45">
-        <v>28070.78984417519</v>
+        <v>28204.11164775411</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1209377911362386</v>
+        <v>0.1209027010469988</v>
       </c>
       <c r="T45">
         <v>1.463891431989954</v>
       </c>
       <c r="U45">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.181818689208231</v>
+        <v>5.371072364927183</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08896065654447813</v>
+        <v>0.0882147112198043</v>
       </c>
       <c r="C46">
-        <v>106116.8726208943</v>
+        <v>107500.3763367034</v>
       </c>
       <c r="D46">
-        <v>163125.0608868902</v>
+        <v>164508.5646026992</v>
       </c>
       <c r="E46">
         <v>20780.16947964165</v>
@@ -5065,37 +5065,37 @@
         <v>26142</v>
       </c>
       <c r="M46">
-        <v>5162.271220350132</v>
+        <v>4980.374806164942</v>
       </c>
       <c r="N46">
-        <v>20979.72877964987</v>
+        <v>21161.62519383506</v>
       </c>
       <c r="O46">
-        <v>5244.932194912467</v>
+        <v>5290.406298458764</v>
       </c>
       <c r="P46">
-        <v>15734.7965847374</v>
+        <v>15871.21889537629</v>
       </c>
       <c r="Q46">
-        <v>27982.7965847374</v>
+        <v>28119.21889537629</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1220653090104319</v>
+        <v>0.1220296923592286</v>
       </c>
       <c r="T46">
         <v>1.485858590333141</v>
       </c>
       <c r="U46">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.064050082635315</v>
+        <v>5.249002538451564</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08885096326763298</v>
+        <v>0.08808857396915204</v>
       </c>
       <c r="C47">
-        <v>104445.4914491631</v>
+        <v>105864.2559964974</v>
       </c>
       <c r="D47">
-        <v>163332.7749030225</v>
+        <v>164751.5394503568</v>
       </c>
       <c r="E47">
         <v>22659.26466750519</v>
@@ -5147,37 +5147,37 @@
         <v>26142</v>
       </c>
       <c r="M47">
-        <v>5279.595566267181</v>
+        <v>5093.56514266869</v>
       </c>
       <c r="N47">
-        <v>20862.40443373282</v>
+        <v>21048.43485733131</v>
       </c>
       <c r="O47">
-        <v>5215.601108433205</v>
+        <v>5262.108714332828</v>
       </c>
       <c r="P47">
-        <v>15646.80332529961</v>
+        <v>15786.32614299848</v>
       </c>
       <c r="Q47">
-        <v>27894.80332529961</v>
+        <v>28034.32614299849</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1232338275345958</v>
+        <v>0.1231976651737214</v>
       </c>
       <c r="T47">
         <v>1.508624554434261</v>
       </c>
       <c r="U47">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.951515636354531</v>
+        <v>5.132358037597086</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08874126999078781</v>
+        <v>0.08796243671849979</v>
       </c>
       <c r="C48">
-        <v>102774.6399338904</v>
+        <v>104228.8544529266</v>
       </c>
       <c r="D48">
-        <v>163541.0185756134</v>
+        <v>164995.2330946495</v>
       </c>
       <c r="E48">
         <v>24538.35985536873</v>
@@ -5229,37 +5229,37 @@
         <v>26142</v>
       </c>
       <c r="M48">
-        <v>5396.919912184229</v>
+        <v>5206.755479172439</v>
       </c>
       <c r="N48">
-        <v>20745.08008781577</v>
+        <v>20935.24452082756</v>
       </c>
       <c r="O48">
-        <v>5186.270021953943</v>
+        <v>5233.81113020689</v>
       </c>
       <c r="P48">
-        <v>15558.81006586183</v>
+        <v>15701.43339062067</v>
       </c>
       <c r="Q48">
-        <v>27806.81006586183</v>
+        <v>27949.43339062067</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1244456245226177</v>
+        <v>0.1244088962406028</v>
       </c>
       <c r="T48">
         <v>1.532233702390979</v>
       </c>
       <c r="U48">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.843873992085954</v>
+        <v>5.020785036779758</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08863157671394266</v>
+        <v>0.08783629946784755</v>
       </c>
       <c r="C49">
-        <v>101104.3201035439</v>
+        <v>102594.1749003584</v>
       </c>
       <c r="D49">
-        <v>163749.7939331304</v>
+        <v>165239.6487299449</v>
       </c>
       <c r="E49">
         <v>26417.45504323228</v>
@@ -5311,37 +5311,37 @@
         <v>26142</v>
       </c>
       <c r="M49">
-        <v>5514.244258101278</v>
+        <v>5319.945815676188</v>
       </c>
       <c r="N49">
-        <v>20627.75574189872</v>
+        <v>20822.05418432381</v>
       </c>
       <c r="O49">
-        <v>5156.93893547468</v>
+        <v>5205.513546080952</v>
       </c>
       <c r="P49">
-        <v>15470.81680642404</v>
+        <v>15616.54063824286</v>
       </c>
       <c r="Q49">
-        <v>27718.81680642404</v>
+        <v>27864.54063824286</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1257031496988668</v>
+        <v>0.1256658341401967</v>
       </c>
       <c r="T49">
         <v>1.556733761591346</v>
       </c>
       <c r="U49">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.740812843318167</v>
+        <v>4.913959823231251</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08852188343709751</v>
+        <v>0.08771016221719527</v>
       </c>
       <c r="C50">
-        <v>99434.53399696259</v>
+        <v>100960.2205521164</v>
       </c>
       <c r="D50">
-        <v>163959.1030144126</v>
+        <v>165484.7895695664</v>
       </c>
       <c r="E50">
         <v>28296.5502310958</v>
@@ -5393,37 +5393,37 @@
         <v>26142</v>
       </c>
       <c r="M50">
-        <v>5631.568604018325</v>
+        <v>5433.136152179935</v>
       </c>
       <c r="N50">
-        <v>20510.43139598168</v>
+        <v>20708.86384782007</v>
       </c>
       <c r="O50">
-        <v>5127.607848995419</v>
+        <v>5177.215961955017</v>
       </c>
       <c r="P50">
-        <v>15382.82354698626</v>
+        <v>15531.64788586505</v>
       </c>
       <c r="Q50">
-        <v>27630.82354698626</v>
+        <v>27779.64788586505</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1270090412280485</v>
+        <v>0.1269711158051596</v>
       </c>
       <c r="T50">
         <v>1.582176130760959</v>
       </c>
       <c r="U50">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.642045909082373</v>
+        <v>4.811585660247269</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08841219016025234</v>
+        <v>0.08758402496654302</v>
       </c>
       <c r="C51">
-        <v>97765.28366342296</v>
+        <v>99326.9946406207</v>
       </c>
       <c r="D51">
-        <v>164168.9478687365</v>
+        <v>165730.6588459343</v>
       </c>
       <c r="E51">
         <v>30175.64541895936</v>
@@ -5475,37 +5475,37 @@
         <v>26142</v>
       </c>
       <c r="M51">
-        <v>5748.892949935375</v>
+        <v>5546.326488683685</v>
       </c>
       <c r="N51">
-        <v>20393.10705006462</v>
+        <v>20595.67351131632</v>
       </c>
       <c r="O51">
-        <v>5098.276762516156</v>
+        <v>5148.918377829079</v>
       </c>
       <c r="P51">
-        <v>15294.83028754847</v>
+        <v>15446.75513348724</v>
       </c>
       <c r="Q51">
-        <v>27542.83028754847</v>
+        <v>27694.75513348724</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1283661441897472</v>
+        <v>0.1283275849863956</v>
       </c>
       <c r="T51">
         <v>1.608616239898007</v>
       </c>
       <c r="U51">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.547310278284773</v>
+        <v>4.713390034527936</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08830249688340719</v>
+        <v>0.08745788771589078</v>
       </c>
       <c r="C52">
-        <v>96096.57116270631</v>
+        <v>97694.50041753058</v>
       </c>
       <c r="D52">
-        <v>164379.3305558834</v>
+        <v>165977.2598107077</v>
       </c>
       <c r="E52">
         <v>32054.7406068229</v>
@@ -5557,37 +5557,37 @@
         <v>26142</v>
       </c>
       <c r="M52">
-        <v>5866.217295852423</v>
+        <v>5659.516825187434</v>
       </c>
       <c r="N52">
-        <v>20275.78270414758</v>
+        <v>20482.48317481257</v>
       </c>
       <c r="O52">
-        <v>5068.945676036894</v>
+        <v>5120.620793703141</v>
       </c>
       <c r="P52">
-        <v>15206.83702811068</v>
+        <v>15361.86238110942</v>
       </c>
       <c r="Q52">
-        <v>27454.83702811068</v>
+        <v>27609.86238110942</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1297775312699138</v>
+        <v>0.129738312934881</v>
       </c>
       <c r="T52">
         <v>1.636113953400537</v>
       </c>
       <c r="U52">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.456364072719078</v>
+        <v>4.619122233837377</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08819280360656202</v>
+        <v>0.08733175046523853</v>
       </c>
       <c r="C53">
-        <v>94428.39856516583</v>
+        <v>96062.74115388734</v>
       </c>
       <c r="D53">
-        <v>164590.2531462065</v>
+        <v>166224.595734928</v>
       </c>
       <c r="E53">
         <v>33933.83579468643</v>
@@ -5639,37 +5639,37 @@
         <v>26142</v>
       </c>
       <c r="M53">
-        <v>5983.541641769471</v>
+        <v>5772.707161691182</v>
       </c>
       <c r="N53">
-        <v>20158.45835823053</v>
+        <v>20369.29283830882</v>
       </c>
       <c r="O53">
-        <v>5039.614589557632</v>
+        <v>5092.323209577205</v>
       </c>
       <c r="P53">
-        <v>15118.8437686729</v>
+        <v>15276.96962873161</v>
       </c>
       <c r="Q53">
-        <v>27366.84376867289</v>
+        <v>27524.96962873161</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1312465259860056</v>
+        <v>0.1312066216159576</v>
       </c>
       <c r="T53">
         <v>1.664734022556232</v>
       </c>
       <c r="U53">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.368984385018704</v>
+        <v>4.528551209644489</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08808311032971687</v>
+        <v>0.08720561321458625</v>
       </c>
       <c r="C54">
-        <v>92760.76795179464</v>
+        <v>94431.72014025933</v>
       </c>
       <c r="D54">
-        <v>164801.7177206988</v>
+        <v>166472.6699091635</v>
       </c>
       <c r="E54">
         <v>35812.93098254999</v>
@@ -5721,37 +5721,37 @@
         <v>26142</v>
       </c>
       <c r="M54">
-        <v>6100.86598768652</v>
+        <v>5885.897498194931</v>
       </c>
       <c r="N54">
-        <v>20041.13401231348</v>
+        <v>20256.10250180507</v>
       </c>
       <c r="O54">
-        <v>5010.28350307837</v>
+        <v>5064.025625451267</v>
       </c>
       <c r="P54">
-        <v>15030.85050923511</v>
+        <v>15192.0768763538</v>
       </c>
       <c r="Q54">
-        <v>27278.85050923511</v>
+        <v>27440.0768763538</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1327767288152679</v>
+        <v>0.1327361098254124</v>
       </c>
       <c r="T54">
         <v>1.694546594593413</v>
       </c>
       <c r="U54">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.284965454537575</v>
+        <v>4.441463686382093</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08852991705287171</v>
+        <v>0.08707947596393401</v>
       </c>
       <c r="C55">
-        <v>90023.710713362</v>
+        <v>92801.44068688745</v>
       </c>
       <c r="D55">
-        <v>163943.7556701297</v>
+        <v>166721.4856436552</v>
       </c>
       <c r="E55">
         <v>37692.02617041353</v>
@@ -5803,45 +5803,45 @@
         <v>26142</v>
       </c>
       <c r="M55">
-        <v>6357.619196543043</v>
+        <v>5999.08783469868</v>
       </c>
       <c r="N55">
-        <v>19784.38080345696</v>
+        <v>20142.91216530132</v>
       </c>
       <c r="O55">
-        <v>4946.095200864239</v>
+        <v>5035.72804132533</v>
       </c>
       <c r="P55">
-        <v>14838.28560259272</v>
+        <v>15107.18412397599</v>
       </c>
       <c r="Q55">
-        <v>27086.28560259272</v>
+        <v>27355.18412397599</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1343720466585413</v>
+        <v>0.1343306826395249</v>
       </c>
       <c r="T55">
         <v>1.725627786717284</v>
       </c>
       <c r="U55">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.111916614039217</v>
+        <v>4.357662484752243</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08843072377602657</v>
+        <v>0.08695333871328176</v>
       </c>
       <c r="C56">
-        <v>88334.31494164836</v>
+        <v>91171.90612383274</v>
       </c>
       <c r="D56">
-        <v>164133.4550862796</v>
+        <v>166971.046268464</v>
       </c>
       <c r="E56">
         <v>39571.12135827707</v>
@@ -5885,45 +5885,45 @@
         <v>26142</v>
       </c>
       <c r="M56">
-        <v>6477.574275723101</v>
+        <v>6112.278171202428</v>
       </c>
       <c r="N56">
-        <v>19664.4257242769</v>
+        <v>20029.72182879757</v>
       </c>
       <c r="O56">
-        <v>4916.106431069225</v>
+        <v>5007.430457199393</v>
       </c>
       <c r="P56">
-        <v>14748.31929320767</v>
+        <v>15022.29137159818</v>
       </c>
       <c r="Q56">
-        <v>26996.31929320767</v>
+        <v>27270.29137159818</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1360367261471745</v>
+        <v>0.1359945847064249</v>
       </c>
       <c r="T56">
         <v>1.758060335020453</v>
       </c>
       <c r="U56">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.035770010075527</v>
+        <v>4.276965031330905</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08833153049918141</v>
+        <v>0.08723970146262952</v>
       </c>
       <c r="C57">
-        <v>86645.35868110547</v>
+        <v>88727.32022316889</v>
       </c>
       <c r="D57">
-        <v>164323.5940136003</v>
+        <v>166405.5555556637</v>
       </c>
       <c r="E57">
         <v>41450.21654614062</v>
@@ -5967,37 +5967,37 @@
         <v>26142</v>
       </c>
       <c r="M57">
-        <v>6597.529354903158</v>
+        <v>6328.818743038672</v>
       </c>
       <c r="N57">
-        <v>19544.47064509684</v>
+        <v>19813.18125696133</v>
       </c>
       <c r="O57">
-        <v>4886.11766127421</v>
+        <v>4953.295314240332</v>
       </c>
       <c r="P57">
-        <v>14658.35298382263</v>
+        <v>14859.885942721</v>
       </c>
       <c r="Q57">
-        <v>26906.35298382263</v>
+        <v>27107.885942721</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.137775391390858</v>
+        <v>0.1377324379762982</v>
       </c>
       <c r="T57">
         <v>1.791934329914874</v>
       </c>
       <c r="U57">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.9623923735287</v>
+        <v>4.130628646736748</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08823233722233624</v>
+        <v>0.08712106421197725</v>
       </c>
       <c r="C58">
-        <v>84956.84346094816</v>
+        <v>87082.03685757164</v>
       </c>
       <c r="D58">
-        <v>164514.1739813065</v>
+        <v>166639.36737793</v>
       </c>
       <c r="E58">
         <v>43329.31173400416</v>
@@ -6049,37 +6049,37 @@
         <v>26142</v>
       </c>
       <c r="M58">
-        <v>6717.484434083216</v>
+        <v>6443.888174730285</v>
       </c>
       <c r="N58">
-        <v>19424.51556591678</v>
+        <v>19698.11182526972</v>
       </c>
       <c r="O58">
-        <v>4856.128891479196</v>
+        <v>4924.527956317429</v>
       </c>
       <c r="P58">
-        <v>14568.38667443759</v>
+        <v>14773.58386895229</v>
       </c>
       <c r="Q58">
-        <v>26816.38667443759</v>
+        <v>27021.58386895229</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1395930868728907</v>
+        <v>0.1395492845766203</v>
       </c>
       <c r="T58">
         <v>1.82734805184995</v>
       </c>
       <c r="U58">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.891635366858544</v>
+        <v>4.056867420902163</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08813314394549109</v>
+        <v>0.087002426961325</v>
       </c>
       <c r="C59">
-        <v>83268.77081749366</v>
+        <v>85437.41146145826</v>
       </c>
       <c r="D59">
-        <v>164705.1965257156</v>
+        <v>166873.8371696802</v>
       </c>
       <c r="E59">
         <v>45208.4069218677</v>
@@ -6131,37 +6131,37 @@
         <v>26142</v>
       </c>
       <c r="M59">
-        <v>6837.439513263274</v>
+        <v>6558.957606421896</v>
       </c>
       <c r="N59">
-        <v>19304.56048673673</v>
+        <v>19583.0423935781</v>
       </c>
       <c r="O59">
-        <v>4826.140121684181</v>
+        <v>4895.760598394526</v>
       </c>
       <c r="P59">
-        <v>14478.42036505255</v>
+        <v>14687.28179518358</v>
       </c>
       <c r="Q59">
-        <v>26726.42036505255</v>
+        <v>26935.28179518358</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.141495326330832</v>
+        <v>0.1414506356699806</v>
       </c>
       <c r="T59">
         <v>1.864408923642473</v>
       </c>
       <c r="U59">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.823361062176815</v>
+        <v>3.985694308254757</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08803395066864593</v>
+        <v>0.08688378971067275</v>
       </c>
       <c r="C60">
-        <v>81581.14229420305</v>
+        <v>83793.44681612856</v>
       </c>
       <c r="D60">
-        <v>164896.6631902885</v>
+        <v>167108.967712214</v>
       </c>
       <c r="E60">
         <v>47087.50210973122</v>
@@ -6213,37 +6213,37 @@
         <v>26142</v>
       </c>
       <c r="M60">
-        <v>6957.394592443329</v>
+        <v>6674.027038113508</v>
       </c>
       <c r="N60">
-        <v>19184.60540755667</v>
+        <v>19467.97296188649</v>
       </c>
       <c r="O60">
-        <v>4796.151351889168</v>
+        <v>4866.993240471623</v>
       </c>
       <c r="P60">
-        <v>14388.4540556675</v>
+        <v>14600.97972141487</v>
       </c>
       <c r="Q60">
-        <v>26636.45405566751</v>
+        <v>26848.97972141487</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1434881486201038</v>
+        <v>0.1434425272915962</v>
       </c>
       <c r="T60">
         <v>1.903234598853686</v>
       </c>
       <c r="U60">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.757441043863424</v>
+        <v>3.916975440871055</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08793475739180077</v>
+        <v>0.08676515246002051</v>
       </c>
       <c r="C61">
-        <v>79893.95944172268</v>
+        <v>82150.14571858013</v>
       </c>
       <c r="D61">
-        <v>165088.5755256717</v>
+        <v>167344.7618025291</v>
       </c>
       <c r="E61">
         <v>48966.59729759477</v>
@@ -6295,37 +6295,37 @@
         <v>26142</v>
       </c>
       <c r="M61">
-        <v>7077.349671623388</v>
+        <v>6789.09646980512</v>
       </c>
       <c r="N61">
-        <v>19064.65032837661</v>
+        <v>19352.90353019488</v>
       </c>
       <c r="O61">
-        <v>4766.162582094154</v>
+        <v>4838.22588254872</v>
       </c>
       <c r="P61">
-        <v>14298.48774628246</v>
+        <v>14514.67764764616</v>
       </c>
       <c r="Q61">
-        <v>26546.48774628246</v>
+        <v>26762.67764764616</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1455781817527547</v>
+        <v>0.1455315843581687</v>
       </c>
       <c r="T61">
         <v>1.943954209441056</v>
       </c>
       <c r="U61">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.693755602442009</v>
+        <v>3.850586026619003</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08783556411495561</v>
+        <v>0.08664651520936824</v>
       </c>
       <c r="C62">
-        <v>78207.22381792615</v>
+        <v>80507.51098161949</v>
       </c>
       <c r="D62">
-        <v>165280.9350897387</v>
+        <v>167581.222253432</v>
       </c>
       <c r="E62">
         <v>50845.69248545831</v>
@@ -6377,37 +6377,37 @@
         <v>26142</v>
       </c>
       <c r="M62">
-        <v>7197.304750803445</v>
+        <v>6904.165901496733</v>
       </c>
       <c r="N62">
-        <v>18944.69524919656</v>
+        <v>19237.83409850327</v>
       </c>
       <c r="O62">
-        <v>4736.173812299139</v>
+        <v>4809.458524625817</v>
       </c>
       <c r="P62">
-        <v>14208.52143689742</v>
+        <v>14428.37557387745</v>
       </c>
       <c r="Q62">
-        <v>26456.52143689742</v>
+        <v>26676.37557387745</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1477727165420382</v>
+        <v>0.1477250942780697</v>
       </c>
       <c r="T62">
         <v>1.986709800557795</v>
       </c>
       <c r="U62">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.632193009067976</v>
+        <v>3.78640959284202</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08773637083811046</v>
+        <v>0.086527877958716</v>
       </c>
       <c r="C63">
-        <v>76520.9369879563</v>
+        <v>78865.54543397365</v>
       </c>
       <c r="D63">
-        <v>165473.7434476324</v>
+        <v>167818.3518936497</v>
       </c>
       <c r="E63">
         <v>52724.78767332185</v>
@@ -6459,37 +6459,37 @@
         <v>26142</v>
       </c>
       <c r="M63">
-        <v>7317.259829983502</v>
+        <v>7019.235333188345</v>
       </c>
       <c r="N63">
-        <v>18824.7401700165</v>
+        <v>19122.76466681165</v>
       </c>
       <c r="O63">
-        <v>4706.185042504125</v>
+        <v>4780.691166702914</v>
       </c>
       <c r="P63">
-        <v>14118.55512751237</v>
+        <v>14342.07350010874</v>
       </c>
       <c r="Q63">
-        <v>26366.55512751237</v>
+        <v>26590.07350010874</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1500797915769259</v>
+        <v>0.1500310918861709</v>
       </c>
       <c r="T63">
         <v>2.031657986090777</v>
       </c>
       <c r="U63">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.572648861378337</v>
+        <v>3.724337304434773</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08763717756126531</v>
+        <v>0.08640924070806374</v>
       </c>
       <c r="C64">
-        <v>74835.10052426794</v>
+        <v>77224.25192040316</v>
       </c>
       <c r="D64">
-        <v>165667.0021718075</v>
+        <v>168056.1535679428</v>
       </c>
       <c r="E64">
         <v>54603.8828611854</v>
@@ -6541,37 +6541,37 @@
         <v>26142</v>
       </c>
       <c r="M64">
-        <v>7437.21490916356</v>
+        <v>7134.304764879957</v>
       </c>
       <c r="N64">
-        <v>18704.78509083644</v>
+        <v>19007.69523512004</v>
       </c>
       <c r="O64">
-        <v>4676.19627270911</v>
+        <v>4751.92380878001</v>
       </c>
       <c r="P64">
-        <v>14028.58881812733</v>
+        <v>14255.77142634003</v>
       </c>
       <c r="Q64">
-        <v>26276.58881812733</v>
+        <v>26503.77142634003</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1525082916136499</v>
+        <v>0.1524584577894352</v>
       </c>
       <c r="T64">
         <v>2.078971865599179</v>
       </c>
       <c r="U64">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.515025492646428</v>
+        <v>3.664267347911632</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08753798428442014</v>
+        <v>0.08629060345741149</v>
       </c>
       <c r="C65">
-        <v>73149.71600667029</v>
+        <v>75583.63330181566</v>
       </c>
       <c r="D65">
-        <v>165860.7128420734</v>
+        <v>168294.6301372188</v>
       </c>
       <c r="E65">
         <v>56482.97804904894</v>
@@ -6623,37 +6623,37 @@
         <v>26142</v>
       </c>
       <c r="M65">
-        <v>7557.169988343618</v>
+        <v>7249.37419657157</v>
       </c>
       <c r="N65">
-        <v>18584.83001165638</v>
+        <v>18892.62580342843</v>
       </c>
       <c r="O65">
-        <v>4646.207502914096</v>
+        <v>4723.156450857107</v>
       </c>
       <c r="P65">
-        <v>13938.62250874229</v>
+        <v>14169.46935257132</v>
       </c>
       <c r="Q65">
-        <v>26186.62250874229</v>
+        <v>26417.46935257132</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1550680619226291</v>
+        <v>0.1550170326604436</v>
       </c>
       <c r="T65">
         <v>2.128843252108035</v>
       </c>
       <c r="U65">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.459231437207596</v>
+        <v>3.606104374135256</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08743879100757498</v>
+        <v>0.08617196620675924</v>
       </c>
       <c r="C66">
-        <v>71464.7850223702</v>
+        <v>73943.69245538078</v>
       </c>
       <c r="D66">
-        <v>166054.8770456369</v>
+        <v>168533.7844786475</v>
       </c>
       <c r="E66">
         <v>58362.07323691248</v>
@@ -6705,37 +6705,37 @@
         <v>26142</v>
       </c>
       <c r="M66">
-        <v>7677.125067523675</v>
+        <v>7364.443628263181</v>
       </c>
       <c r="N66">
-        <v>18464.87493247633</v>
+        <v>18777.55637173682</v>
       </c>
       <c r="O66">
-        <v>4616.218733119082</v>
+        <v>4694.389092934205</v>
       </c>
       <c r="P66">
-        <v>13848.65619935724</v>
+        <v>14083.16727880262</v>
       </c>
       <c r="Q66">
-        <v>26096.65619935725</v>
+        <v>26331.16727880262</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1577700416932184</v>
+        <v>0.1577177505798413</v>
       </c>
       <c r="T66">
         <v>2.181485271200716</v>
       </c>
       <c r="U66">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.405180946001227</v>
+        <v>3.549758993289394</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08733959773072983</v>
+        <v>0.08605332895610698</v>
       </c>
       <c r="C67">
-        <v>69780.30916601534</v>
+        <v>72304.43227464576</v>
       </c>
       <c r="D67">
-        <v>166249.4963771456</v>
+        <v>168773.619485776</v>
       </c>
       <c r="E67">
         <v>60241.16842477603</v>
@@ -6787,37 +6787,37 @@
         <v>26142</v>
       </c>
       <c r="M67">
-        <v>7797.080146703733</v>
+        <v>7479.513059954795</v>
       </c>
       <c r="N67">
-        <v>18344.91985329627</v>
+        <v>18662.4869400452</v>
       </c>
       <c r="O67">
-        <v>4586.229963324067</v>
+        <v>4665.621735011301</v>
       </c>
       <c r="P67">
-        <v>13758.6898899722</v>
+        <v>13996.8652050339</v>
       </c>
       <c r="Q67">
-        <v>26006.6898899722</v>
+        <v>26244.8652050339</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1606264203078413</v>
+        <v>0.1605727952374903</v>
       </c>
       <c r="T67">
         <v>2.237135405670122</v>
       </c>
       <c r="U67">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.352793546831977</v>
+        <v>3.495147316469556</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08724040445388467</v>
+        <v>0.08593469170545473</v>
       </c>
       <c r="C68">
-        <v>68096.29003973828</v>
+        <v>70665.85566965218</v>
       </c>
       <c r="D68">
-        <v>166444.5724387321</v>
+        <v>169014.138068646</v>
       </c>
       <c r="E68">
         <v>62120.26361263957</v>
@@ -6869,37 +6869,37 @@
         <v>26142</v>
       </c>
       <c r="M68">
-        <v>7917.03522588379</v>
+        <v>7594.582491646406</v>
       </c>
       <c r="N68">
-        <v>18224.96477411621</v>
+        <v>18547.4175083536</v>
       </c>
       <c r="O68">
-        <v>4556.241193529053</v>
+        <v>4636.854377088399</v>
       </c>
       <c r="P68">
-        <v>13668.72358058716</v>
+        <v>13910.5631312652</v>
       </c>
       <c r="Q68">
-        <v>25916.72358058716</v>
+        <v>26158.5631312652</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1636508211939126</v>
+        <v>0.1635957836985305</v>
       </c>
       <c r="T68">
         <v>2.296059077461258</v>
       </c>
       <c r="U68">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.30199364460725</v>
+        <v>3.442190538947291</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08714121117703952</v>
+        <v>0.08581605445480248</v>
       </c>
       <c r="C69">
-        <v>66412.72925319981</v>
+        <v>69027.96556705366</v>
       </c>
       <c r="D69">
-        <v>166640.1068400571</v>
+        <v>169255.343153911</v>
       </c>
       <c r="E69">
         <v>63999.35880050311</v>
@@ -6951,37 +6951,37 @@
         <v>26142</v>
       </c>
       <c r="M69">
-        <v>8036.990305063848</v>
+        <v>7709.651923338019</v>
       </c>
       <c r="N69">
-        <v>18105.00969493615</v>
+        <v>18432.34807666198</v>
       </c>
       <c r="O69">
-        <v>4526.252423734039</v>
+        <v>4608.087019165496</v>
       </c>
       <c r="P69">
-        <v>13578.75727120212</v>
+        <v>13824.26105749649</v>
       </c>
       <c r="Q69">
-        <v>25826.75727120211</v>
+        <v>26072.26105749649</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1668585191033822</v>
+        <v>0.1668019835814518</v>
       </c>
       <c r="T69">
         <v>2.358553880876099</v>
       </c>
       <c r="U69">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.252710157374306</v>
+        <v>3.390814560754047</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08704201790019436</v>
+        <v>0.08569741720415021</v>
       </c>
       <c r="C70">
-        <v>64729.62842363375</v>
+        <v>67390.76491023449</v>
       </c>
       <c r="D70">
-        <v>166836.1011983546</v>
+        <v>169497.2376849554</v>
       </c>
       <c r="E70">
         <v>65878.45398836667</v>
@@ -7033,37 +7033,37 @@
         <v>26142</v>
       </c>
       <c r="M70">
-        <v>8156.945384243905</v>
+        <v>7824.721355029631</v>
       </c>
       <c r="N70">
-        <v>17985.0546157561</v>
+        <v>18317.27864497037</v>
       </c>
       <c r="O70">
-        <v>4496.263653939024</v>
+        <v>4579.319661242593</v>
       </c>
       <c r="P70">
-        <v>13488.79096181707</v>
+        <v>13737.95898372778</v>
       </c>
       <c r="Q70">
-        <v>25736.79096181707</v>
+        <v>25985.95898372778</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1702666981321937</v>
+        <v>0.1702085709570557</v>
       </c>
       <c r="T70">
         <v>2.424954609504367</v>
       </c>
       <c r="U70">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.204876184471743</v>
+        <v>3.340949640742958</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08694282462334921</v>
+        <v>0.08557877995349797</v>
       </c>
       <c r="C71">
-        <v>63046.98917589136</v>
+        <v>65754.25665942943</v>
       </c>
       <c r="D71">
-        <v>167032.5571384758</v>
+        <v>169739.8246220138</v>
       </c>
       <c r="E71">
         <v>67757.54917623021</v>
@@ -7115,37 +7115,37 @@
         <v>26142</v>
       </c>
       <c r="M71">
-        <v>8276.900463423963</v>
+        <v>7939.790786721243</v>
       </c>
       <c r="N71">
-        <v>17865.09953657604</v>
+        <v>18202.20921327876</v>
       </c>
       <c r="O71">
-        <v>4466.27488414401</v>
+        <v>4550.55230331969</v>
       </c>
       <c r="P71">
-        <v>13398.82465243203</v>
+        <v>13651.65690995907</v>
       </c>
       <c r="Q71">
-        <v>25646.82465243203</v>
+        <v>25899.65690995907</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.173894759678993</v>
+        <v>0.1738349381633438</v>
       </c>
       <c r="T71">
         <v>2.495639256108654</v>
       </c>
       <c r="U71">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.15842870353737</v>
+        <v>3.292530080732191</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08684363134650405</v>
+        <v>0.08546014270284572</v>
       </c>
       <c r="C72">
-        <v>61364.81314248606</v>
+        <v>64118.44379184453</v>
       </c>
       <c r="D72">
-        <v>167229.476292934</v>
+        <v>169983.1069422925</v>
       </c>
       <c r="E72">
         <v>69636.64436409375</v>
@@ -7197,37 +7197,37 @@
         <v>26142</v>
       </c>
       <c r="M72">
-        <v>8396.85554260402</v>
+        <v>8054.860218412856</v>
       </c>
       <c r="N72">
-        <v>17745.14445739598</v>
+        <v>18087.13978158715</v>
       </c>
       <c r="O72">
-        <v>4436.286114348995</v>
+        <v>4521.784945396786</v>
       </c>
       <c r="P72">
-        <v>13308.85834304699</v>
+        <v>13565.35483619036</v>
       </c>
       <c r="Q72">
-        <v>25556.85834304699</v>
+        <v>25813.35483619036</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1777646919955788</v>
+        <v>0.1777030631833844</v>
       </c>
       <c r="T72">
         <v>2.571036212486558</v>
       </c>
       <c r="U72">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.113308293486836</v>
+        <v>3.245493936721731</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.0867444380696589</v>
+        <v>0.08534150545219346</v>
       </c>
       <c r="C73">
-        <v>59683.10196363897</v>
+        <v>62483.32930177881</v>
       </c>
       <c r="D73">
-        <v>167426.8603019505</v>
+        <v>170227.0876400903</v>
       </c>
       <c r="E73">
         <v>71515.73955195729</v>
@@ -7279,37 +7279,37 @@
         <v>26142</v>
       </c>
       <c r="M73">
-        <v>8516.810621784078</v>
+        <v>8169.929650104467</v>
       </c>
       <c r="N73">
-        <v>17625.18937821592</v>
+        <v>17972.07034989553</v>
       </c>
       <c r="O73">
-        <v>4406.297344553981</v>
+        <v>4493.017587473883</v>
       </c>
       <c r="P73">
-        <v>13218.89203366194</v>
+        <v>13479.05276242165</v>
       </c>
       <c r="Q73">
-        <v>25466.89203366194</v>
+        <v>25727.05276242165</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1819015161960672</v>
+        <v>0.1818379554461864</v>
       </c>
       <c r="T73">
         <v>2.651632958959491</v>
       </c>
       <c r="U73">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.069458880902514</v>
+        <v>3.199782754514383</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08664524479281374</v>
+        <v>0.08522286820154121</v>
       </c>
       <c r="C74">
-        <v>58001.85728732421</v>
+        <v>60848.91620074713</v>
       </c>
       <c r="D74">
-        <v>167624.7108134992</v>
+        <v>170471.7697269222</v>
       </c>
       <c r="E74">
         <v>73394.83473982083</v>
@@ -7361,37 +7361,37 @@
         <v>26142</v>
       </c>
       <c r="M74">
-        <v>8636.765700964133</v>
+        <v>8284.999081796079</v>
       </c>
       <c r="N74">
-        <v>17505.23429903587</v>
+        <v>17857.00091820392</v>
       </c>
       <c r="O74">
-        <v>4376.308574758967</v>
+        <v>4464.25022955098</v>
       </c>
       <c r="P74">
-        <v>13128.9257242769</v>
+        <v>13392.75068865294</v>
       </c>
       <c r="Q74">
-        <v>25376.9257242769</v>
+        <v>25640.75068865294</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1863338278394476</v>
+        <v>0.1862681971563314</v>
       </c>
       <c r="T74">
         <v>2.737986615894776</v>
       </c>
       <c r="U74">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.026827507556646</v>
+        <v>3.15534132736835</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.08796955151596857</v>
+        <v>0.08510423095088895</v>
       </c>
       <c r="C75">
-        <v>53519.25868745073</v>
+        <v>59215.20751760414</v>
       </c>
       <c r="D75">
-        <v>165021.2074014893</v>
+        <v>170717.1562316427</v>
       </c>
       <c r="E75">
         <v>75273.92992768437</v>
@@ -7443,45 +7443,45 @@
         <v>26142</v>
       </c>
       <c r="M75">
-        <v>9113.373046800691</v>
+        <v>8400.068513487691</v>
       </c>
       <c r="N75">
-        <v>17028.62695319931</v>
+        <v>17741.93148651231</v>
       </c>
       <c r="O75">
-        <v>4257.156738299827</v>
+        <v>4435.482871628077</v>
       </c>
       <c r="P75">
-        <v>12771.47021489948</v>
+        <v>13306.44861488423</v>
       </c>
       <c r="Q75">
-        <v>25019.47021489948</v>
+        <v>25554.44861488423</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1910944588638191</v>
+        <v>0.1910266049190798</v>
       </c>
       <c r="T75">
         <v>2.830736840010453</v>
       </c>
       <c r="U75">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.868531757204575</v>
+        <v>3.112117473568783</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.0878898582391234</v>
+        <v>0.0849855937002367</v>
       </c>
       <c r="C76">
-        <v>51794.54635803131</v>
+        <v>57582.20629866922</v>
       </c>
       <c r="D76">
-        <v>165175.5902599334</v>
+        <v>170963.2502005713</v>
       </c>
       <c r="E76">
         <v>77153.02511554791</v>
@@ -7525,45 +7525,45 @@
         <v>26142</v>
       </c>
       <c r="M76">
-        <v>9238.213773469193</v>
+        <v>8515.137945179304</v>
       </c>
       <c r="N76">
-        <v>16903.78622653081</v>
+        <v>17626.8620548207</v>
       </c>
       <c r="O76">
-        <v>4225.946556632702</v>
+        <v>4406.715513705174</v>
       </c>
       <c r="P76">
-        <v>12677.83966989811</v>
+        <v>13220.14654111552</v>
       </c>
       <c r="Q76">
-        <v>24925.83966989811</v>
+        <v>25468.14654111552</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1962212922746807</v>
+        <v>0.1961510440481934</v>
       </c>
       <c r="T76">
         <v>2.930621696750412</v>
       </c>
       <c r="U76">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.829767814539649</v>
+        <v>3.07006183203407</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08781016496227825</v>
+        <v>0.08486695644958445</v>
       </c>
       <c r="C77">
-        <v>50070.12315975814</v>
+        <v>55949.91560785254</v>
       </c>
       <c r="D77">
-        <v>165330.2622495238</v>
+        <v>171210.0546976182</v>
       </c>
       <c r="E77">
         <v>79032.12030341144</v>
@@ -7607,45 +7607,45 @@
         <v>26142</v>
       </c>
       <c r="M77">
-        <v>9363.054500137696</v>
+        <v>8630.207376870916</v>
       </c>
       <c r="N77">
-        <v>16778.9454998623</v>
+        <v>17511.79262312908</v>
       </c>
       <c r="O77">
-        <v>4194.736374965576</v>
+        <v>4377.948155782271</v>
       </c>
       <c r="P77">
-        <v>12584.20912489673</v>
+        <v>13133.84446734681</v>
       </c>
       <c r="Q77">
-        <v>24832.20912489673</v>
+        <v>25381.84446734681</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2017582723584113</v>
+        <v>0.2016854383076361</v>
       </c>
       <c r="T77">
         <v>3.038497342029569</v>
       </c>
       <c r="U77">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.792037577012453</v>
+        <v>3.029127674273616</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.0877304716854331</v>
+        <v>0.0861733191989322</v>
       </c>
       <c r="C78">
-        <v>48345.98990562797</v>
+        <v>51391.81894660741</v>
       </c>
       <c r="D78">
-        <v>165485.2241832571</v>
+        <v>168531.0532242366</v>
       </c>
       <c r="E78">
         <v>80911.21549127498</v>
@@ -7689,37 +7689,37 @@
         <v>26142</v>
       </c>
       <c r="M78">
-        <v>9487.895226806198</v>
+        <v>9102.3048942566</v>
       </c>
       <c r="N78">
-        <v>16654.1047731938</v>
+        <v>17039.6951057434</v>
       </c>
       <c r="O78">
-        <v>4163.52619329845</v>
+        <v>4259.92377643585</v>
       </c>
       <c r="P78">
-        <v>12490.57857989535</v>
+        <v>12779.77132930755</v>
       </c>
       <c r="Q78">
-        <v>24738.57857989535</v>
+        <v>25027.77132930755</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2077566674491195</v>
+        <v>0.207681032088699</v>
       </c>
       <c r="T78">
         <v>3.155362624415321</v>
       </c>
       <c r="U78">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.755300240472816</v>
+        <v>2.872019812970136</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.08765077840858795</v>
+        <v>0.08607343194827995</v>
       </c>
       <c r="C79">
-        <v>46622.14741168843</v>
+        <v>49714.60213827415</v>
       </c>
       <c r="D79">
-        <v>165640.4768771812</v>
+        <v>168732.9316037669</v>
       </c>
       <c r="E79">
         <v>82790.31067913855</v>
@@ -7771,37 +7771,37 @@
         <v>26142</v>
       </c>
       <c r="M79">
-        <v>9612.735953474703</v>
+        <v>9222.072063917873</v>
       </c>
       <c r="N79">
-        <v>16529.2640465253</v>
+        <v>16919.92793608213</v>
       </c>
       <c r="O79">
-        <v>4132.316011631325</v>
+        <v>4229.981984020532</v>
       </c>
       <c r="P79">
-        <v>12396.94803489397</v>
+        <v>12689.9459520616</v>
       </c>
       <c r="Q79">
-        <v>24644.94803489398</v>
+        <v>24937.9459520616</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2142766621129327</v>
+        <v>0.2141979818507239</v>
       </c>
       <c r="T79">
         <v>3.282390105269401</v>
       </c>
       <c r="U79">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.719517120466675</v>
+        <v>2.834720854360135</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.08757108513174279</v>
+        <v>0.08597354469762769</v>
       </c>
       <c r="C80">
-        <v>44898.59649705249</v>
+        <v>48037.86955830074</v>
       </c>
       <c r="D80">
-        <v>165796.0211504088</v>
+        <v>168935.294211657</v>
       </c>
       <c r="E80">
         <v>84669.40586700209</v>
@@ -7853,37 +7853,37 @@
         <v>26142</v>
       </c>
       <c r="M80">
-        <v>9737.576680143204</v>
+        <v>9341.839233579143</v>
       </c>
       <c r="N80">
-        <v>16404.4233198568</v>
+        <v>16800.16076642086</v>
       </c>
       <c r="O80">
-        <v>4101.105829964199</v>
+        <v>4200.040191605214</v>
       </c>
       <c r="P80">
-        <v>12303.3174898926</v>
+        <v>12600.12057481564</v>
       </c>
       <c r="Q80">
-        <v>24551.3174898926</v>
+        <v>24848.12057481564</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2213893835643652</v>
+        <v>0.2213073815911148</v>
       </c>
       <c r="T80">
         <v>3.420965538928395</v>
       </c>
       <c r="U80">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.684651516358128</v>
+        <v>2.798378279304235</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08749139185489763</v>
+        <v>0.08587365744697543</v>
       </c>
       <c r="C81">
-        <v>43175.33798391261</v>
+        <v>46361.62295099461</v>
       </c>
       <c r="D81">
-        <v>165951.8578251324</v>
+        <v>169138.1427922144</v>
       </c>
       <c r="E81">
         <v>86548.50105486563</v>
@@ -7935,37 +7935,37 @@
         <v>26142</v>
       </c>
       <c r="M81">
-        <v>9862.417406811706</v>
+        <v>9461.606403240414</v>
       </c>
       <c r="N81">
-        <v>16279.58259318829</v>
+        <v>16680.39359675959</v>
       </c>
       <c r="O81">
-        <v>4069.895648297073</v>
+        <v>4170.098399189897</v>
       </c>
       <c r="P81">
-        <v>12209.68694489122</v>
+        <v>12510.29519756969</v>
       </c>
       <c r="Q81">
-        <v>24457.68694489122</v>
+        <v>24758.29519756969</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2291795070587914</v>
+        <v>0.2290938670210666</v>
       </c>
       <c r="T81">
         <v>3.572738632935867</v>
       </c>
       <c r="U81">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V81">
         <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.650668585771316</v>
+        <v>2.762955769439625</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.08741169857805248</v>
+        <v>0.08577377019632318</v>
       </c>
       <c r="C82">
-        <v>41452.3726975554</v>
+        <v>44685.8640690514</v>
       </c>
       <c r="D82">
-        <v>166107.9877266388</v>
+        <v>169341.4790981348</v>
       </c>
       <c r="E82">
         <v>88427.59624272917</v>
@@ -8017,37 +8017,37 @@
         <v>26142</v>
       </c>
       <c r="M82">
-        <v>9987.258133480209</v>
+        <v>9581.373572901684</v>
       </c>
       <c r="N82">
-        <v>16154.74186651979</v>
+        <v>16560.62642709832</v>
       </c>
       <c r="O82">
-        <v>4038.685466629948</v>
+        <v>4140.156606774579</v>
       </c>
       <c r="P82">
-        <v>12116.05639988984</v>
+        <v>12420.46982032374</v>
       </c>
       <c r="Q82">
-        <v>24364.05639988984</v>
+        <v>24668.46982032373</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2377486429026602</v>
+        <v>0.2376590009940137</v>
       </c>
       <c r="T82">
         <v>3.739689036344085</v>
       </c>
       <c r="U82">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.617535228449175</v>
+        <v>2.72841882232163</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08733200530120731</v>
+        <v>0.08567388294567094</v>
       </c>
       <c r="C83">
-        <v>39729.70146637622</v>
+        <v>43010.59467360488</v>
       </c>
       <c r="D83">
-        <v>166264.4116833231</v>
+        <v>169545.3048905518</v>
       </c>
       <c r="E83">
         <v>90306.69143059271</v>
@@ -8099,37 +8099,37 @@
         <v>26142</v>
       </c>
       <c r="M83">
-        <v>10112.09886014871</v>
+        <v>9701.140742562957</v>
       </c>
       <c r="N83">
-        <v>16029.90113985129</v>
+        <v>16440.85925743704</v>
       </c>
       <c r="O83">
-        <v>4007.475284962822</v>
+        <v>4110.21481435926</v>
       </c>
       <c r="P83">
-        <v>12022.42585488847</v>
+        <v>12330.64444307778</v>
       </c>
       <c r="Q83">
-        <v>24270.42585488847</v>
+        <v>24578.64444307778</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2472197930458835</v>
+        <v>0.2471257280167446</v>
       </c>
       <c r="T83">
         <v>3.924213166426853</v>
       </c>
       <c r="U83">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.585219978715235</v>
+        <v>2.694734639330004</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08725231202436215</v>
+        <v>0.08557399569501867</v>
       </c>
       <c r="C84">
-        <v>38007.32512189375</v>
+        <v>41335.81653427845</v>
       </c>
       <c r="D84">
-        <v>166421.1305267042</v>
+        <v>169749.6219390889</v>
       </c>
       <c r="E84">
         <v>92185.78661845624</v>
@@ -8181,37 +8181,37 @@
         <v>26142</v>
       </c>
       <c r="M84">
-        <v>10236.93958681721</v>
+        <v>9820.907912224227</v>
       </c>
       <c r="N84">
-        <v>15905.06041318279</v>
+        <v>16321.09208777577</v>
       </c>
       <c r="O84">
-        <v>3976.265103295696</v>
+        <v>4080.273021943943</v>
       </c>
       <c r="P84">
-        <v>11928.79530988709</v>
+        <v>12240.81906583183</v>
       </c>
       <c r="Q84">
-        <v>24176.79530988709</v>
+        <v>24488.81906583183</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2577432932050205</v>
+        <v>0.2576443135975567</v>
       </c>
       <c r="T84">
         <v>4.129239977629927</v>
       </c>
       <c r="U84">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.553692905804073</v>
+        <v>2.661872021777199</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.087172618747517</v>
+        <v>0.08547410844436643</v>
       </c>
       <c r="C85">
-        <v>36285.24449876463</v>
+        <v>39661.53142923565</v>
       </c>
       <c r="D85">
-        <v>166578.1450914386</v>
+        <v>169954.4320219097</v>
       </c>
       <c r="E85">
         <v>94064.88180631981</v>
@@ -8263,37 +8263,37 @@
         <v>26142</v>
       </c>
       <c r="M85">
-        <v>10361.78031348572</v>
+        <v>9940.6750818855</v>
       </c>
       <c r="N85">
-        <v>15780.21968651428</v>
+        <v>16201.3249181145</v>
       </c>
       <c r="O85">
-        <v>3945.05492162857</v>
+        <v>4050.331229528625</v>
       </c>
       <c r="P85">
-        <v>11835.16476488571</v>
+        <v>12150.99368858588</v>
       </c>
       <c r="Q85">
-        <v>24083.16476488571</v>
+        <v>24398.99368858588</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2695048522064091</v>
+        <v>0.2694003798349351</v>
       </c>
       <c r="T85">
         <v>4.358387590151012</v>
       </c>
       <c r="U85">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.522925521396795</v>
+        <v>2.629801274526872</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.08879392547067186</v>
+        <v>0.08537422119371416</v>
       </c>
       <c r="C86">
-        <v>31268.99446381032</v>
+        <v>37987.74114523249</v>
       </c>
       <c r="D86">
-        <v>163440.9902443478</v>
+        <v>170159.73692577</v>
       </c>
       <c r="E86">
         <v>95943.97699418332</v>
@@ -8345,45 +8345,45 @@
         <v>26142</v>
       </c>
       <c r="M86">
-        <v>10912.79982876167</v>
+        <v>10060.44225154677</v>
       </c>
       <c r="N86">
-        <v>15229.20017123833</v>
+        <v>16081.55774845323</v>
       </c>
       <c r="O86">
-        <v>3807.300042809582</v>
+        <v>4020.389437113308</v>
       </c>
       <c r="P86">
-        <v>11421.90012842875</v>
+        <v>12061.16831133992</v>
       </c>
       <c r="Q86">
-        <v>23669.90012842874</v>
+        <v>24309.16831133992</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.282736606082971</v>
+        <v>0.2826259543519855</v>
       </c>
       <c r="T86">
         <v>4.616178654237229</v>
       </c>
       <c r="U86">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.39553555551348</v>
+        <v>2.598494116496791</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.08873448219382669</v>
+        <v>0.08527433394306191</v>
       </c>
       <c r="C87">
-        <v>29502.8311293101</v>
+        <v>36314.44747766864</v>
       </c>
       <c r="D87">
-        <v>163553.9220977112</v>
+        <v>170365.5384460697</v>
       </c>
       <c r="E87">
         <v>97823.07218204686</v>
@@ -8427,45 +8427,45 @@
         <v>26142</v>
       </c>
       <c r="M87">
-        <v>11042.7141124374</v>
+        <v>10180.20942120804</v>
       </c>
       <c r="N87">
-        <v>15099.2858875626</v>
+        <v>15961.79057879196</v>
       </c>
       <c r="O87">
-        <v>3774.821471890649</v>
+        <v>3990.44764469799</v>
       </c>
       <c r="P87">
-        <v>11324.46441567195</v>
+        <v>11971.34293409397</v>
       </c>
       <c r="Q87">
-        <v>23572.46441567194</v>
+        <v>24219.34293409397</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2977325938097414</v>
+        <v>0.2976149388046429</v>
       </c>
       <c r="T87">
         <v>4.90834186020161</v>
       </c>
       <c r="U87">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V87">
         <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.367352784272145</v>
+        <v>2.567923597479181</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.08867503891698153</v>
+        <v>0.08517444669240966</v>
       </c>
       <c r="C88">
-        <v>27736.82396642704</v>
+        <v>34641.65223064041</v>
       </c>
       <c r="D88">
-        <v>163667.0101226916</v>
+        <v>170571.838386905</v>
       </c>
       <c r="E88">
         <v>99702.1673699104</v>
@@ -8509,45 +8509,45 @@
         <v>26142</v>
       </c>
       <c r="M88">
-        <v>11172.62839611314</v>
+        <v>10299.97659086931</v>
       </c>
       <c r="N88">
-        <v>14969.37160388686</v>
+        <v>15842.02340913069</v>
       </c>
       <c r="O88">
-        <v>3742.342900971715</v>
+        <v>3960.505852282673</v>
       </c>
       <c r="P88">
-        <v>11227.02870291515</v>
+        <v>11881.51755684802</v>
       </c>
       <c r="Q88">
-        <v>23475.02870291514</v>
+        <v>24129.51755684802</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3148708654974788</v>
+        <v>0.3147452067505369</v>
       </c>
       <c r="T88">
         <v>5.242242667018046</v>
       </c>
       <c r="U88">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.339825426315493</v>
+        <v>2.538064020764307</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.08861559564013638</v>
+        <v>0.0850745594417574</v>
       </c>
       <c r="C89">
-        <v>25970.97329933604</v>
+        <v>32969.35721699314</v>
       </c>
       <c r="D89">
-        <v>163780.2546434642</v>
+        <v>170778.6385611213</v>
       </c>
       <c r="E89">
         <v>101581.262557774</v>
@@ -8591,45 +8591,45 @@
         <v>26142</v>
       </c>
       <c r="M89">
-        <v>11302.54267978888</v>
+        <v>10419.74376053058</v>
       </c>
       <c r="N89">
-        <v>14839.45732021112</v>
+        <v>15722.25623946942</v>
       </c>
       <c r="O89">
-        <v>3709.864330052781</v>
+        <v>3930.564059867354</v>
       </c>
       <c r="P89">
-        <v>11129.59299015834</v>
+        <v>11791.69217960206</v>
       </c>
       <c r="Q89">
-        <v>23377.59299015834</v>
+        <v>24039.69217960206</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3346457943679452</v>
+        <v>0.3345109005342609</v>
       </c>
       <c r="T89">
         <v>5.627512828729318</v>
       </c>
       <c r="U89">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.312930881185428</v>
+        <v>2.508890871100349</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.08855615236329123</v>
+        <v>0.08728467219110517</v>
       </c>
       <c r="C90">
-        <v>24205.27945310986</v>
+        <v>26628.72153483439</v>
       </c>
       <c r="D90">
-        <v>163893.6559851016</v>
+        <v>166317.0980668261</v>
       </c>
       <c r="E90">
         <v>103460.3577456375</v>
@@ -8673,37 +8673,37 @@
         <v>26142</v>
       </c>
       <c r="M90">
-        <v>11432.45696346461</v>
+        <v>11118.27224805383</v>
       </c>
       <c r="N90">
-        <v>14709.54303653539</v>
+        <v>15023.72775194617</v>
       </c>
       <c r="O90">
-        <v>3677.385759133848</v>
+        <v>3755.931937986544</v>
       </c>
       <c r="P90">
-        <v>11032.15727740154</v>
+        <v>11267.79581395963</v>
       </c>
       <c r="Q90">
-        <v>23280.15727740154</v>
+        <v>23515.79581395963</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3577165447168227</v>
+        <v>0.3575708766152721</v>
       </c>
       <c r="T90">
         <v>6.076994684059137</v>
       </c>
       <c r="U90">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V90">
         <v>0.25</v>
       </c>
       <c r="W90">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.286647575717413</v>
+        <v>2.351264604496079</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.08849670908644605</v>
+        <v>0.0872110349404529</v>
       </c>
       <c r="C91">
-        <v>22439.7427537223</v>
+        <v>24894.52005079415</v>
       </c>
       <c r="D91">
-        <v>164007.2144735775</v>
+        <v>166461.9917706494</v>
       </c>
       <c r="E91">
         <v>105339.452933501</v>
@@ -8755,37 +8755,37 @@
         <v>26142</v>
       </c>
       <c r="M91">
-        <v>11562.37124714034</v>
+        <v>11244.61625087262</v>
       </c>
       <c r="N91">
-        <v>14579.62875285966</v>
+        <v>14897.38374912738</v>
       </c>
       <c r="O91">
-        <v>3644.907188214914</v>
+        <v>3724.345937281845</v>
       </c>
       <c r="P91">
-        <v>10934.72156464474</v>
+        <v>11173.03781184554</v>
       </c>
       <c r="Q91">
-        <v>23182.72156464474</v>
+        <v>23421.03781184553</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3849819769473142</v>
+        <v>0.3848235756201037</v>
       </c>
       <c r="T91">
         <v>6.608200513085285</v>
       </c>
       <c r="U91">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V91">
         <v>0.25</v>
       </c>
       <c r="W91">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.26095490632733</v>
+        <v>2.324845901074774</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.09160976580960092</v>
+        <v>0.08713739768980065</v>
       </c>
       <c r="C92">
-        <v>14817.83052358497</v>
+        <v>23160.57124662277</v>
       </c>
       <c r="D92">
-        <v>158264.3974313037</v>
+        <v>166607.1381543415</v>
       </c>
       <c r="E92">
         <v>107218.5481213646</v>
@@ -8837,45 +8837,45 @@
         <v>26142</v>
       </c>
       <c r="M92">
-        <v>12487.14279528236</v>
+        <v>11370.96025369141</v>
       </c>
       <c r="N92">
-        <v>13654.85720471764</v>
+        <v>14771.03974630859</v>
       </c>
       <c r="O92">
-        <v>3413.714301179411</v>
+        <v>3692.759936577147</v>
       </c>
       <c r="P92">
-        <v>10241.14290353823</v>
+        <v>11078.27980973144</v>
       </c>
       <c r="Q92">
-        <v>22489.14290353823</v>
+        <v>23326.27980973144</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.417700495623904</v>
+        <v>0.4175268144259015</v>
       </c>
       <c r="T92">
         <v>7.245647507916665</v>
       </c>
       <c r="U92">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.093513338365638</v>
+        <v>2.299014279951721</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.09158557253275576</v>
+        <v>0.0870637604391484</v>
       </c>
       <c r="C93">
-        <v>12981.81488158845</v>
+        <v>21426.87578386909</v>
       </c>
       <c r="D93">
-        <v>158307.4769771708</v>
+        <v>166752.5378794514</v>
       </c>
       <c r="E93">
         <v>109097.6433092281</v>
@@ -8919,45 +8919,45 @@
         <v>26142</v>
       </c>
       <c r="M93">
-        <v>12625.88882634105</v>
+        <v>11497.3042565102</v>
       </c>
       <c r="N93">
-        <v>13516.11117365895</v>
+        <v>14644.6957434898</v>
       </c>
       <c r="O93">
-        <v>3379.027793414738</v>
+        <v>3661.173935872449</v>
       </c>
       <c r="P93">
-        <v>10137.08338024421</v>
+        <v>10983.52180761735</v>
       </c>
       <c r="Q93">
-        <v>22385.08338024421</v>
+        <v>23231.52180761735</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.457689796228625</v>
+        <v>0.4574974396329878</v>
       </c>
       <c r="T93">
         <v>8.024749390488351</v>
       </c>
       <c r="U93">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V93">
         <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.070507697284698</v>
+        <v>2.273750386765439</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.0915613792559106</v>
+        <v>0.08892212318849615</v>
       </c>
       <c r="C94">
-        <v>11145.82269846959</v>
+        <v>15954.30979163351</v>
       </c>
       <c r="D94">
-        <v>158350.5799819154</v>
+        <v>163159.0670750794</v>
       </c>
       <c r="E94">
         <v>110976.7384970917</v>
@@ -9001,37 +9001,37 @@
         <v>26142</v>
       </c>
       <c r="M94">
-        <v>12764.63485739974</v>
+        <v>12107.70317972265</v>
       </c>
       <c r="N94">
-        <v>13377.36514260026</v>
+        <v>14034.29682027735</v>
       </c>
       <c r="O94">
-        <v>3344.341285650064</v>
+        <v>3508.574205069338</v>
       </c>
       <c r="P94">
-        <v>10033.02385695019</v>
+        <v>10525.72261520801</v>
       </c>
       <c r="Q94">
-        <v>22281.02385695019</v>
+        <v>22773.72261520801</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5076764219845261</v>
+        <v>0.5074607211418456</v>
       </c>
       <c r="T94">
         <v>8.998626743702959</v>
       </c>
       <c r="U94">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V94">
         <v>0.25</v>
       </c>
       <c r="W94">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.048002178835951</v>
+        <v>2.159121314088808</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.09153718597906545</v>
+        <v>0.0888694859378439</v>
       </c>
       <c r="C95">
-        <v>9309.853993395314</v>
+        <v>14174.86539595074</v>
       </c>
       <c r="D95">
-        <v>158393.7064647047</v>
+        <v>163258.7178672602</v>
       </c>
       <c r="E95">
         <v>112855.8336849552</v>
@@ -9083,37 +9083,37 @@
         <v>26142</v>
       </c>
       <c r="M95">
-        <v>12903.38088845844</v>
+        <v>12239.30864906746</v>
       </c>
       <c r="N95">
-        <v>13238.61911154156</v>
+        <v>13902.69135093254</v>
       </c>
       <c r="O95">
-        <v>3309.654777885391</v>
+        <v>3475.672837733135</v>
       </c>
       <c r="P95">
-        <v>9928.964333656171</v>
+        <v>10427.01851319941</v>
       </c>
       <c r="Q95">
-        <v>22176.96433365617</v>
+        <v>22675.01851319941</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5719449408135419</v>
+        <v>0.5716992259389484</v>
       </c>
       <c r="T95">
         <v>10.2507547692646</v>
       </c>
       <c r="U95">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V95">
         <v>0.25</v>
       </c>
       <c r="W95">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.025980650031263</v>
+        <v>2.135904955872799</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09151299270222028</v>
+        <v>0.08881684868719164</v>
       </c>
       <c r="C96">
-        <v>7473.908785553562</v>
+        <v>12395.54279980107</v>
       </c>
       <c r="D96">
-        <v>158436.8564447265</v>
+        <v>163358.490458974</v>
       </c>
       <c r="E96">
         <v>114734.9288728188</v>
@@ -9165,37 +9165,37 @@
         <v>26142</v>
       </c>
       <c r="M96">
-        <v>13042.12691951713</v>
+        <v>12370.91411841227</v>
       </c>
       <c r="N96">
-        <v>13099.87308048287</v>
+        <v>13771.08588158773</v>
       </c>
       <c r="O96">
-        <v>3274.968270120718</v>
+        <v>3442.771470396932</v>
       </c>
       <c r="P96">
-        <v>9824.904810362154</v>
+        <v>10328.3144111908</v>
       </c>
       <c r="Q96">
-        <v>22072.90481036215</v>
+        <v>22576.3144111908</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6576362992522296</v>
+        <v>0.657350565668419</v>
       </c>
       <c r="T96">
         <v>11.92025880334678</v>
       </c>
       <c r="U96">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V96">
         <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.004427664392633</v>
+        <v>2.113182562725216</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09811504942537513</v>
+        <v>0.0887642114365394</v>
       </c>
       <c r="C97">
-        <v>-5368.48849522596</v>
+        <v>10616.34222662772</v>
       </c>
       <c r="D97">
-        <v>147473.5543518105</v>
+        <v>163458.3850736642</v>
       </c>
       <c r="E97">
         <v>116614.0240606823</v>
@@ -9247,45 +9247,45 @@
         <v>26142</v>
       </c>
       <c r="M97">
-        <v>14841.05354905326</v>
+        <v>12502.51958775708</v>
       </c>
       <c r="N97">
-        <v>11300.94645094674</v>
+        <v>13639.48041224292</v>
       </c>
       <c r="O97">
-        <v>2825.236612736685</v>
+        <v>3409.870103060729</v>
       </c>
       <c r="P97">
-        <v>8475.709838210056</v>
+        <v>10229.61030918219</v>
       </c>
       <c r="Q97">
-        <v>20723.70983821006</v>
+        <v>22477.61030918219</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7776042010663926</v>
+        <v>0.777262441289678</v>
       </c>
       <c r="T97">
         <v>14.25756445106184</v>
       </c>
       <c r="U97">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V97">
         <v>0.25</v>
       </c>
       <c r="W97">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.761465243258801</v>
+        <v>2.090938535749161</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.10154460614853</v>
+        <v>0.08871157418588714</v>
       </c>
       <c r="C98">
-        <v>-12364.6513996922</v>
+        <v>8837.263900420832</v>
       </c>
       <c r="D98">
-        <v>142356.4866352078</v>
+        <v>163558.4019353208</v>
       </c>
       <c r="E98">
         <v>118493.1192485458</v>
@@ -9329,45 +9329,45 @@
         <v>26142</v>
       </c>
       <c r="M98">
-        <v>15845.12291412311</v>
+        <v>12634.12505710189</v>
       </c>
       <c r="N98">
-        <v>10296.87708587689</v>
+        <v>13507.87494289811</v>
       </c>
       <c r="O98">
-        <v>2574.219271469222</v>
+        <v>3376.968735724528</v>
       </c>
       <c r="P98">
-        <v>7722.657814407667</v>
+        <v>10130.90620717358</v>
       </c>
       <c r="Q98">
-        <v>19970.65781440767</v>
+        <v>22378.90620717358</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9575560537876348</v>
+        <v>0.957130254721564</v>
       </c>
       <c r="T98">
         <v>17.76352292263439</v>
       </c>
       <c r="U98">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V98">
         <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.649845201055465</v>
+        <v>2.069157926001775</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1016254128716848</v>
+        <v>0.08865893693523488</v>
       </c>
       <c r="C99">
-        <v>-14360.03564997329</v>
+        <v>7058.308045719081</v>
       </c>
       <c r="D99">
-        <v>142240.1975727903</v>
+        <v>163658.5412684826</v>
       </c>
       <c r="E99">
         <v>120372.2144364094</v>
@@ -9411,45 +9411,45 @@
         <v>26142</v>
       </c>
       <c r="M99">
-        <v>16010.17627781189</v>
+        <v>12765.7305264467</v>
       </c>
       <c r="N99">
-        <v>10131.82372218811</v>
+        <v>13376.2694735533</v>
       </c>
       <c r="O99">
-        <v>2532.955930547027</v>
+        <v>3344.067368388325</v>
       </c>
       <c r="P99">
-        <v>7598.867791641082</v>
+        <v>10032.20210516497</v>
       </c>
       <c r="Q99">
-        <v>19846.86779164108</v>
+        <v>22280.20210516497</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.257475808323041</v>
+        <v>1.25690994377471</v>
       </c>
       <c r="T99">
         <v>23.60678704192201</v>
       </c>
       <c r="U99">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V99">
         <v>0.25</v>
       </c>
       <c r="W99">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.632836487642522</v>
+        <v>2.047826400991447</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1017062195948397</v>
+        <v>0.08860629968458264</v>
       </c>
       <c r="C100">
-        <v>-16355.23006544603</v>
+        <v>5279.474887611286</v>
       </c>
       <c r="D100">
-        <v>142124.0983451811</v>
+        <v>163758.8032982384</v>
       </c>
       <c r="E100">
         <v>122251.3096242729</v>
@@ -9493,45 +9493,45 @@
         <v>26142</v>
       </c>
       <c r="M100">
-        <v>16175.22964150068</v>
+        <v>12897.33599579151</v>
       </c>
       <c r="N100">
-        <v>9966.770358499323</v>
+        <v>13244.66400420849</v>
       </c>
       <c r="O100">
-        <v>2491.692589624831</v>
+        <v>3311.166001052121</v>
       </c>
       <c r="P100">
-        <v>7475.077768874493</v>
+        <v>9933.498003156365</v>
       </c>
       <c r="Q100">
-        <v>19723.07776887449</v>
+        <v>22181.49800315636</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.857315317393853</v>
+        <v>1.856469321881002</v>
       </c>
       <c r="T100">
         <v>35.29331528049727</v>
       </c>
       <c r="U100">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V100">
         <v>0.25</v>
       </c>
       <c r="W100">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.616174890829843</v>
+        <v>2.026930213226228</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1017870263179945</v>
+        <v>0.08855366243393038</v>
       </c>
       <c r="C101">
-        <v>-18350.23511057181</v>
+        <v>3500.764651738515</v>
       </c>
       <c r="D101">
-        <v>142008.1884879188</v>
+        <v>163859.1882502292</v>
       </c>
       <c r="E101">
         <v>124130.4048121365</v>
@@ -9575,45 +9575,45 @@
         <v>26142</v>
       </c>
       <c r="M101">
-        <v>16340.28300518946</v>
+        <v>13028.94146513633</v>
       </c>
       <c r="N101">
-        <v>9801.71699481054</v>
+        <v>13113.05853486367</v>
       </c>
       <c r="O101">
-        <v>2450.429248702635</v>
+        <v>3278.264633715919</v>
       </c>
       <c r="P101">
-        <v>7351.287746107905</v>
+        <v>9834.793901147756</v>
       </c>
       <c r="Q101">
-        <v>19599.2877461079</v>
+        <v>22082.79390114776</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.65683384460629</v>
+        <v>3.655147456199878</v>
       </c>
       <c r="T101">
         <v>70.35289999622303</v>
       </c>
       <c r="U101">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V101">
         <v>0.25</v>
       </c>
       <c r="W101">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y101">
-        <v>1.599849891932572</v>
+        <v>2.006456170668387</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/france/france_oil_gas_integrated.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09376475024850341</v>
+        <v>0.09360861299785116</v>
       </c>
       <c r="C2">
-        <v>180155.9457972118</v>
+        <v>178542.1390662081</v>
       </c>
       <c r="D2">
-        <v>154483.9457972118</v>
+        <v>154749.2342540716</v>
       </c>
       <c r="E2">
-        <v>-61900.0187863542</v>
+        <v>-60020.92359849066</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1879.095187863542</v>
       </c>
       <c r="G2">
         <v>25672</v>
@@ -1457,28 +1457,28 @@
         <v>26142</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>105.6739557522945</v>
       </c>
       <c r="N2">
-        <v>26142</v>
+        <v>26036.3260442477</v>
       </c>
       <c r="O2">
-        <v>6535.5</v>
+        <v>6509.081511061926</v>
       </c>
       <c r="P2">
-        <v>19606.5</v>
+        <v>19527.24453318578</v>
       </c>
       <c r="Q2">
-        <v>31854.5</v>
+        <v>31775.24453318578</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09376475024850341</v>
+        <v>0.09412811956856783</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9420050034730364</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>247.3835659306468</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09360861299785116</v>
+        <v>0.09345247574719891</v>
       </c>
       <c r="C3">
-        <v>178542.1390662081</v>
+        <v>176929.2450388494</v>
       </c>
       <c r="D3">
-        <v>154749.2342540716</v>
+        <v>155015.4354145765</v>
       </c>
       <c r="E3">
-        <v>-60020.92359849066</v>
+        <v>-58141.82841062712</v>
       </c>
       <c r="F3">
-        <v>1879.095187863542</v>
+        <v>3758.190375727084</v>
       </c>
       <c r="G3">
         <v>25672</v>
@@ -1539,28 +1539,28 @@
         <v>26142</v>
       </c>
       <c r="M3">
-        <v>105.6739557522945</v>
+        <v>211.347911504589</v>
       </c>
       <c r="N3">
-        <v>26036.3260442477</v>
+        <v>25930.65208849541</v>
       </c>
       <c r="O3">
-        <v>6509.081511061926</v>
+        <v>6482.663022123853</v>
       </c>
       <c r="P3">
-        <v>19527.24453318578</v>
+        <v>19447.98906637156</v>
       </c>
       <c r="Q3">
-        <v>31775.24453318578</v>
+        <v>31695.98906637156</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09412811956856783</v>
+        <v>0.09449890458904173</v>
       </c>
       <c r="T3">
-        <v>0.9420050034730364</v>
+        <v>0.9492322936638684</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>247.3835659306468</v>
+        <v>123.6917829653234</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09345247574719891</v>
+        <v>0.09329633849654664</v>
       </c>
       <c r="C4">
-        <v>176929.2450388494</v>
+        <v>175317.2684333776</v>
       </c>
       <c r="D4">
-        <v>155015.4354145765</v>
+        <v>155282.5539969682</v>
       </c>
       <c r="E4">
-        <v>-58141.82841062712</v>
+        <v>-56262.73322276358</v>
       </c>
       <c r="F4">
-        <v>3758.190375727084</v>
+        <v>5637.285563590625</v>
       </c>
       <c r="G4">
         <v>25672</v>
@@ -1621,28 +1621,28 @@
         <v>26142</v>
       </c>
       <c r="M4">
-        <v>211.347911504589</v>
+        <v>317.0218672568835</v>
       </c>
       <c r="N4">
-        <v>25930.65208849541</v>
+        <v>25824.97813274312</v>
       </c>
       <c r="O4">
-        <v>6482.663022123853</v>
+        <v>6456.244533185779</v>
       </c>
       <c r="P4">
-        <v>19447.98906637156</v>
+        <v>19368.73359955734</v>
       </c>
       <c r="Q4">
-        <v>31695.98906637156</v>
+        <v>31616.73359955734</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09449890458904173</v>
+        <v>0.09487733466148415</v>
       </c>
       <c r="T4">
-        <v>0.9492322936638684</v>
+        <v>0.9566086001472948</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>123.6917829653234</v>
+        <v>82.46118864354894</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09329633849654664</v>
+        <v>0.09314020124589439</v>
       </c>
       <c r="C5">
-        <v>175317.2684333776</v>
+        <v>173706.214000612</v>
       </c>
       <c r="D5">
-        <v>155282.5539969682</v>
+        <v>155550.5947520662</v>
       </c>
       <c r="E5">
-        <v>-56262.73322276358</v>
+        <v>-54383.63803490003</v>
       </c>
       <c r="F5">
-        <v>5637.285563590625</v>
+        <v>7516.380751454168</v>
       </c>
       <c r="G5">
         <v>25672</v>
@@ -1703,28 +1703,28 @@
         <v>26142</v>
       </c>
       <c r="M5">
-        <v>317.0218672568835</v>
+        <v>422.695823009178</v>
       </c>
       <c r="N5">
-        <v>25824.97813274312</v>
+        <v>25719.30417699082</v>
       </c>
       <c r="O5">
-        <v>6456.244533185779</v>
+        <v>6429.826044247706</v>
       </c>
       <c r="P5">
-        <v>19368.73359955734</v>
+        <v>19289.47813274312</v>
       </c>
       <c r="Q5">
-        <v>31616.73359955734</v>
+        <v>31537.47813274312</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09487733466148415</v>
+        <v>0.09526364869376913</v>
       </c>
       <c r="T5">
-        <v>0.9566086001472948</v>
+        <v>0.9641385796824593</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.46118864354894</v>
+        <v>61.84589148266171</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09314020124589439</v>
+        <v>0.09298406399524213</v>
       </c>
       <c r="C6">
-        <v>173706.214000612</v>
+        <v>172096.0865242312</v>
       </c>
       <c r="D6">
-        <v>155550.5947520662</v>
+        <v>155819.5624635489</v>
       </c>
       <c r="E6">
-        <v>-54383.63803490003</v>
+        <v>-52504.54284703649</v>
       </c>
       <c r="F6">
-        <v>7516.380751454168</v>
+        <v>9395.47593931771</v>
       </c>
       <c r="G6">
         <v>25672</v>
@@ -1785,28 +1785,28 @@
         <v>26142</v>
       </c>
       <c r="M6">
-        <v>422.695823009178</v>
+        <v>528.3697787614726</v>
       </c>
       <c r="N6">
-        <v>25719.30417699082</v>
+        <v>25613.63022123853</v>
       </c>
       <c r="O6">
-        <v>6429.826044247706</v>
+        <v>6403.407555309632</v>
       </c>
       <c r="P6">
-        <v>19289.47813274312</v>
+        <v>19210.22266592889</v>
       </c>
       <c r="Q6">
-        <v>31537.47813274312</v>
+        <v>31458.22266592889</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09526364869376913</v>
+        <v>0.09565809565304959</v>
       </c>
       <c r="T6">
-        <v>0.9641385796824593</v>
+        <v>0.9718270851025745</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.84589148266171</v>
+        <v>49.47671318612935</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09298406399524213</v>
+        <v>0.09282792674458991</v>
       </c>
       <c r="C7">
-        <v>172096.0865242312</v>
+        <v>170486.8908210575</v>
       </c>
       <c r="D7">
-        <v>155819.5624635489</v>
+        <v>156089.4619482388</v>
       </c>
       <c r="E7">
-        <v>-52504.54284703649</v>
+        <v>-50625.44765917295</v>
       </c>
       <c r="F7">
-        <v>9395.47593931771</v>
+        <v>11274.57112718125</v>
       </c>
       <c r="G7">
         <v>25672</v>
@@ -1867,28 +1867,28 @@
         <v>26142</v>
       </c>
       <c r="M7">
-        <v>528.3697787614726</v>
+        <v>634.043734513767</v>
       </c>
       <c r="N7">
-        <v>25613.63022123853</v>
+        <v>25507.95626548623</v>
       </c>
       <c r="O7">
-        <v>6403.407555309632</v>
+        <v>6376.989066371558</v>
       </c>
       <c r="P7">
-        <v>19210.22266592889</v>
+        <v>19130.96719911468</v>
       </c>
       <c r="Q7">
-        <v>31458.22266592889</v>
+        <v>31378.96719911468</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09565809565304959</v>
+        <v>0.09606093510082539</v>
       </c>
       <c r="T7">
-        <v>0.9718270851025745</v>
+        <v>0.9796791757443944</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.47671318612935</v>
+        <v>41.23059432177446</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09282792674458989</v>
+        <v>0.09267178949393763</v>
       </c>
       <c r="C8">
-        <v>170486.8908210576</v>
+        <v>168878.6317413448</v>
       </c>
       <c r="D8">
-        <v>156089.4619482388</v>
+        <v>156360.2980563896</v>
       </c>
       <c r="E8">
-        <v>-50625.44765917295</v>
+        <v>-48746.35247130941</v>
       </c>
       <c r="F8">
-        <v>11274.57112718125</v>
+        <v>13153.66631504479</v>
       </c>
       <c r="G8">
         <v>25672</v>
@@ -1949,28 +1949,28 @@
         <v>26142</v>
       </c>
       <c r="M8">
-        <v>634.0437345137669</v>
+        <v>739.7176902660615</v>
       </c>
       <c r="N8">
-        <v>25507.95626548623</v>
+        <v>25402.28230973394</v>
       </c>
       <c r="O8">
-        <v>6376.989066371559</v>
+        <v>6350.570577433485</v>
       </c>
       <c r="P8">
-        <v>19130.96719911468</v>
+        <v>19051.71173230045</v>
       </c>
       <c r="Q8">
-        <v>31378.96719911468</v>
+        <v>31299.71173230045</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09606093510082539</v>
+        <v>0.09647243776253182</v>
       </c>
       <c r="T8">
-        <v>0.9796791757443944</v>
+        <v>0.9877001285505546</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.23059432177448</v>
+        <v>35.34050941866383</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09267178949393762</v>
+        <v>0.0925156522432854</v>
       </c>
       <c r="C9">
-        <v>168878.6317413448</v>
+        <v>167271.3141690684</v>
       </c>
       <c r="D9">
-        <v>156360.2980563896</v>
+        <v>156632.0756719767</v>
       </c>
       <c r="E9">
-        <v>-48746.35247130941</v>
+        <v>-46867.25728344587</v>
       </c>
       <c r="F9">
-        <v>13153.66631504479</v>
+        <v>15032.76150290834</v>
       </c>
       <c r="G9">
         <v>25672</v>
@@ -2031,28 +2031,28 @@
         <v>26142</v>
       </c>
       <c r="M9">
-        <v>739.7176902660616</v>
+        <v>845.391646018356</v>
       </c>
       <c r="N9">
-        <v>25402.28230973394</v>
+        <v>25296.60835398164</v>
       </c>
       <c r="O9">
-        <v>6350.570577433485</v>
+        <v>6324.152088495411</v>
       </c>
       <c r="P9">
-        <v>19051.71173230045</v>
+        <v>18972.45626548623</v>
       </c>
       <c r="Q9">
-        <v>31299.71173230045</v>
+        <v>31220.45626548623</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09647243776253182</v>
+        <v>0.09689288613427538</v>
       </c>
       <c r="T9">
-        <v>0.9877001285505546</v>
+        <v>0.9958954498959791</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.34050941866383</v>
+        <v>30.92294574133085</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0925156522432854</v>
+        <v>0.09235951499263312</v>
       </c>
       <c r="C10">
-        <v>167271.3141690684</v>
+        <v>165664.9430222194</v>
       </c>
       <c r="D10">
-        <v>156632.0756719767</v>
+        <v>156904.7997129913</v>
       </c>
       <c r="E10">
-        <v>-46867.25728344587</v>
+        <v>-44988.16209558232</v>
       </c>
       <c r="F10">
-        <v>15032.76150290834</v>
+        <v>16911.85669077188</v>
       </c>
       <c r="G10">
         <v>25672</v>
@@ -2113,28 +2113,28 @@
         <v>26142</v>
       </c>
       <c r="M10">
-        <v>845.391646018356</v>
+        <v>951.0656017706506</v>
       </c>
       <c r="N10">
-        <v>25296.60835398164</v>
+        <v>25190.93439822935</v>
       </c>
       <c r="O10">
-        <v>6324.152088495411</v>
+        <v>6297.733599557338</v>
       </c>
       <c r="P10">
-        <v>18972.45626548623</v>
+        <v>18893.20079867201</v>
       </c>
       <c r="Q10">
-        <v>31220.45626548623</v>
+        <v>31141.20079867201</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09689288613427538</v>
+        <v>0.09732257512957371</v>
       </c>
       <c r="T10">
-        <v>0.9958954498959791</v>
+        <v>1.00427088819405</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.92294574133085</v>
+        <v>27.48706288118298</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09235951499263312</v>
+        <v>0.09220337774198088</v>
       </c>
       <c r="C11">
-        <v>165664.9430222194</v>
+        <v>164059.5232531009</v>
       </c>
       <c r="D11">
-        <v>156904.7997129913</v>
+        <v>157178.4751317363</v>
       </c>
       <c r="E11">
-        <v>-44988.16209558232</v>
+        <v>-43109.06690771878</v>
       </c>
       <c r="F11">
-        <v>16911.85669077188</v>
+        <v>18790.95187863542</v>
       </c>
       <c r="G11">
         <v>25672</v>
@@ -2195,28 +2195,28 @@
         <v>26142</v>
       </c>
       <c r="M11">
-        <v>951.0656017706506</v>
+        <v>1056.739557522945</v>
       </c>
       <c r="N11">
-        <v>25190.93439822935</v>
+        <v>25085.26044247705</v>
       </c>
       <c r="O11">
-        <v>6297.733599557338</v>
+        <v>6271.315110619264</v>
       </c>
       <c r="P11">
-        <v>18893.20079867201</v>
+        <v>18813.94533185779</v>
       </c>
       <c r="Q11">
-        <v>31141.20079867201</v>
+        <v>31061.94533185779</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09732257512957371</v>
+        <v>0.09776181276921203</v>
       </c>
       <c r="T11">
-        <v>1.00427088819405</v>
+        <v>1.01283244734319</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.48706288118298</v>
+        <v>24.73835659306468</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09220337774198088</v>
+        <v>0.09204724049132862</v>
       </c>
       <c r="C12">
-        <v>164059.5232531009</v>
+        <v>162455.0598486278</v>
       </c>
       <c r="D12">
-        <v>157178.4751317363</v>
+        <v>157453.1069151267</v>
       </c>
       <c r="E12">
-        <v>-43109.06690771878</v>
+        <v>-41229.97171985524</v>
       </c>
       <c r="F12">
-        <v>18790.95187863542</v>
+        <v>20670.04706649896</v>
       </c>
       <c r="G12">
         <v>25672</v>
@@ -2277,28 +2277,28 @@
         <v>26142</v>
       </c>
       <c r="M12">
-        <v>1056.739557522945</v>
+        <v>1162.41351327524</v>
       </c>
       <c r="N12">
-        <v>25085.26044247705</v>
+        <v>24979.58648672476</v>
       </c>
       <c r="O12">
-        <v>6271.315110619264</v>
+        <v>6244.89662168119</v>
       </c>
       <c r="P12">
-        <v>18813.94533185779</v>
+        <v>18734.68986504357</v>
       </c>
       <c r="Q12">
-        <v>31061.94533185779</v>
+        <v>30982.68986504357</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09776181276921203</v>
+        <v>0.09821092091760625</v>
       </c>
       <c r="T12">
-        <v>1.01283244734319</v>
+        <v>1.02158640107995</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.73835659306468</v>
+        <v>22.48941508460425</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09204724049132862</v>
+        <v>0.09189110324067638</v>
       </c>
       <c r="C13">
-        <v>162455.0598486278</v>
+        <v>160851.5578306298</v>
       </c>
       <c r="D13">
-        <v>157453.1069151267</v>
+        <v>157728.7000849923</v>
       </c>
       <c r="E13">
-        <v>-41229.97171985524</v>
+        <v>-39350.8765319917</v>
       </c>
       <c r="F13">
-        <v>20670.04706649896</v>
+        <v>22549.1422543625</v>
       </c>
       <c r="G13">
         <v>25672</v>
@@ -2359,28 +2359,28 @@
         <v>26142</v>
       </c>
       <c r="M13">
-        <v>1162.41351327524</v>
+        <v>1268.087469027534</v>
       </c>
       <c r="N13">
-        <v>24979.58648672476</v>
+        <v>24873.91253097247</v>
       </c>
       <c r="O13">
-        <v>6244.89662168119</v>
+        <v>6218.478132743116</v>
       </c>
       <c r="P13">
-        <v>18734.68986504357</v>
+        <v>18655.43439822935</v>
       </c>
       <c r="Q13">
-        <v>30982.68986504357</v>
+        <v>30903.43439822935</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09821092091760625</v>
+        <v>0.09867023606937309</v>
       </c>
       <c r="T13">
-        <v>1.02158640107995</v>
+        <v>1.030539308310728</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.48941508460425</v>
+        <v>20.61529716088724</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09189110324067638</v>
+        <v>0.09173496599002412</v>
       </c>
       <c r="C14">
-        <v>160851.5578306298</v>
+        <v>159249.0222561577</v>
       </c>
       <c r="D14">
-        <v>157728.7000849923</v>
+        <v>158005.2596983837</v>
       </c>
       <c r="E14">
-        <v>-39350.8765319917</v>
+        <v>-37471.78134412815</v>
       </c>
       <c r="F14">
-        <v>22549.1422543625</v>
+        <v>24428.23744222605</v>
       </c>
       <c r="G14">
         <v>25672</v>
@@ -2441,28 +2441,28 @@
         <v>26142</v>
       </c>
       <c r="M14">
-        <v>1268.087469027534</v>
+        <v>1373.761424779829</v>
       </c>
       <c r="N14">
-        <v>24873.91253097247</v>
+        <v>24768.23857522017</v>
       </c>
       <c r="O14">
-        <v>6218.478132743116</v>
+        <v>6192.059643805042</v>
       </c>
       <c r="P14">
-        <v>18655.43439822935</v>
+        <v>18576.17893141513</v>
       </c>
       <c r="Q14">
-        <v>30903.43439822935</v>
+        <v>30824.17893141513</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09867023606937309</v>
+        <v>0.09914011019014603</v>
       </c>
       <c r="T14">
-        <v>1.030539308310728</v>
+        <v>1.039698029500834</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.61529716088724</v>
+        <v>19.02950507158821</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09173496599002412</v>
+        <v>0.09157882873937187</v>
       </c>
       <c r="C15">
-        <v>159249.0222561577</v>
+        <v>157647.458217792</v>
       </c>
       <c r="D15">
-        <v>158005.2596983837</v>
+        <v>158282.7908478816</v>
       </c>
       <c r="E15">
-        <v>-37471.78134412815</v>
+        <v>-35592.68615626461</v>
       </c>
       <c r="F15">
-        <v>24428.23744222605</v>
+        <v>26307.33263008959</v>
       </c>
       <c r="G15">
         <v>25672</v>
@@ -2523,28 +2523,28 @@
         <v>26142</v>
       </c>
       <c r="M15">
-        <v>1373.761424779829</v>
+        <v>1479.435380532123</v>
       </c>
       <c r="N15">
-        <v>24768.23857522017</v>
+        <v>24662.56461946788</v>
       </c>
       <c r="O15">
-        <v>6192.059643805042</v>
+        <v>6165.641154866969</v>
       </c>
       <c r="P15">
-        <v>18576.17893141513</v>
+        <v>18496.92346460091</v>
       </c>
       <c r="Q15">
-        <v>30824.17893141513</v>
+        <v>30744.92346460091</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09914011019014603</v>
+        <v>0.09962091161605324</v>
       </c>
       <c r="T15">
-        <v>1.039698029500834</v>
+        <v>1.049069744206989</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.02950507158821</v>
+        <v>17.67025470933191</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09157882873937187</v>
+        <v>0.09142269148871961</v>
       </c>
       <c r="C16">
-        <v>157647.458217792</v>
+        <v>156046.8708439565</v>
       </c>
       <c r="D16">
-        <v>158282.7908478816</v>
+        <v>158561.2986619096</v>
       </c>
       <c r="E16">
-        <v>-35592.68615626461</v>
+        <v>-33713.59096840107</v>
       </c>
       <c r="F16">
-        <v>26307.33263008959</v>
+        <v>28186.42781795313</v>
       </c>
       <c r="G16">
         <v>25672</v>
@@ -2605,28 +2605,28 @@
         <v>26142</v>
       </c>
       <c r="M16">
-        <v>1479.435380532123</v>
+        <v>1585.109336284418</v>
       </c>
       <c r="N16">
-        <v>24662.56461946788</v>
+        <v>24556.89066371558</v>
       </c>
       <c r="O16">
-        <v>6165.641154866969</v>
+        <v>6139.222665928895</v>
       </c>
       <c r="P16">
-        <v>18496.92346460091</v>
+        <v>18417.66799778669</v>
       </c>
       <c r="Q16">
-        <v>30744.92346460091</v>
+        <v>30665.66799778669</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09962091161605324</v>
+        <v>0.1001130260166877</v>
       </c>
       <c r="T16">
-        <v>1.049069744206989</v>
+        <v>1.058661969847406</v>
       </c>
       <c r="U16">
         <v>0.0562366166625341</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.67025470933191</v>
+        <v>16.49223772870978</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09142269148871961</v>
+        <v>0.09126655423806737</v>
       </c>
       <c r="C17">
-        <v>156046.8708439565</v>
+        <v>154447.2652992332</v>
       </c>
       <c r="D17">
-        <v>158561.2986619096</v>
+        <v>158840.7883050498</v>
       </c>
       <c r="E17">
-        <v>-33713.59096840107</v>
+        <v>-31834.49578053753</v>
       </c>
       <c r="F17">
-        <v>28186.42781795313</v>
+        <v>30065.52300581667</v>
       </c>
       <c r="G17">
         <v>25672</v>
@@ -2687,28 +2687,28 @@
         <v>26142</v>
       </c>
       <c r="M17">
-        <v>1585.109336284418</v>
+        <v>1690.783292036712</v>
       </c>
       <c r="N17">
-        <v>24556.89066371558</v>
+        <v>24451.21670796329</v>
       </c>
       <c r="O17">
-        <v>6139.222665928895</v>
+        <v>6112.804176990822</v>
       </c>
       <c r="P17">
-        <v>18417.66799778669</v>
+        <v>18338.41253097247</v>
       </c>
       <c r="Q17">
-        <v>30665.66799778669</v>
+        <v>30586.41253097247</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1001130260166877</v>
+        <v>0.1006168574268611</v>
       </c>
       <c r="T17">
-        <v>1.058661969847406</v>
+        <v>1.068482581812596</v>
       </c>
       <c r="U17">
         <v>0.0562366166625341</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.49223772870979</v>
+        <v>15.46147287066543</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09126655423806737</v>
+        <v>0.09111041698741511</v>
       </c>
       <c r="C18">
-        <v>154447.2652992332</v>
+        <v>152848.6467846823</v>
       </c>
       <c r="D18">
-        <v>158840.7883050498</v>
+        <v>159121.2649783625</v>
       </c>
       <c r="E18">
-        <v>-31834.49578053753</v>
+        <v>-29955.40059267398</v>
       </c>
       <c r="F18">
-        <v>30065.52300581667</v>
+        <v>31944.61819368022</v>
       </c>
       <c r="G18">
         <v>25672</v>
@@ -2769,28 +2769,28 @@
         <v>26142</v>
       </c>
       <c r="M18">
-        <v>1690.783292036712</v>
+        <v>1796.457247789007</v>
       </c>
       <c r="N18">
-        <v>24451.21670796329</v>
+        <v>24345.54275221099</v>
       </c>
       <c r="O18">
-        <v>6112.804176990822</v>
+        <v>6086.385688052748</v>
       </c>
       <c r="P18">
-        <v>18338.41253097247</v>
+        <v>18259.15706415824</v>
       </c>
       <c r="Q18">
-        <v>30586.41253097247</v>
+        <v>30507.15706415824</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1006168574268611</v>
+        <v>0.1011328293529422</v>
       </c>
       <c r="T18">
-        <v>1.068482581812596</v>
+        <v>1.078539835029958</v>
       </c>
       <c r="U18">
         <v>0.0562366166625341</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.46147287066543</v>
+        <v>14.55197446650863</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09111041698741511</v>
+        <v>0.09095427973676286</v>
       </c>
       <c r="C19">
-        <v>152848.6467846823</v>
+        <v>151251.0205381645</v>
       </c>
       <c r="D19">
-        <v>159121.2649783625</v>
+        <v>159402.7339197083</v>
       </c>
       <c r="E19">
-        <v>-29955.40059267398</v>
+        <v>-28076.30540481045</v>
       </c>
       <c r="F19">
-        <v>31944.61819368022</v>
+        <v>33823.71338154376</v>
       </c>
       <c r="G19">
         <v>25672</v>
@@ -2851,28 +2851,28 @@
         <v>26142</v>
       </c>
       <c r="M19">
-        <v>1796.457247789007</v>
+        <v>1902.131203541301</v>
       </c>
       <c r="N19">
-        <v>24345.54275221099</v>
+        <v>24239.8687964587</v>
       </c>
       <c r="O19">
-        <v>6086.385688052748</v>
+        <v>6059.967199114675</v>
       </c>
       <c r="P19">
-        <v>18259.15706415824</v>
+        <v>18179.90159734403</v>
       </c>
       <c r="Q19">
-        <v>30507.15706415824</v>
+        <v>30427.90159734403</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1011328293529422</v>
+        <v>0.1016613859601473</v>
       </c>
       <c r="T19">
-        <v>1.078539835029958</v>
+        <v>1.088842387106281</v>
       </c>
       <c r="U19">
         <v>0.0562366166625341</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.55197446650863</v>
+        <v>13.74353144059149</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09095427973676287</v>
+        <v>0.09079814248611062</v>
       </c>
       <c r="C20">
-        <v>151251.0205381645</v>
+        <v>149654.391834667</v>
       </c>
       <c r="D20">
-        <v>159402.7339197083</v>
+        <v>159685.2004040743</v>
       </c>
       <c r="E20">
-        <v>-28076.30540481045</v>
+        <v>-26197.21021694691</v>
       </c>
       <c r="F20">
-        <v>33823.71338154376</v>
+        <v>35702.80856940729</v>
       </c>
       <c r="G20">
         <v>25672</v>
@@ -2933,28 +2933,28 @@
         <v>26142</v>
       </c>
       <c r="M20">
-        <v>1902.131203541301</v>
+        <v>2007.805159293596</v>
       </c>
       <c r="N20">
-        <v>24239.8687964587</v>
+        <v>24134.1948407064</v>
       </c>
       <c r="O20">
-        <v>6059.967199114675</v>
+        <v>6033.548710176601</v>
       </c>
       <c r="P20">
-        <v>18179.90159734403</v>
+        <v>18100.6461305298</v>
       </c>
       <c r="Q20">
-        <v>30427.90159734403</v>
+        <v>30348.6461305298</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1016613859601473</v>
+        <v>0.1022029933477772</v>
       </c>
       <c r="T20">
-        <v>1.088842387106281</v>
+        <v>1.099399323184488</v>
       </c>
       <c r="U20">
         <v>0.0562366166625341</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.74353144059149</v>
+        <v>13.02018768056036</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09079814248611062</v>
+        <v>0.09064200523545836</v>
       </c>
       <c r="C21">
-        <v>149654.391834667</v>
+        <v>148058.7659866332</v>
       </c>
       <c r="D21">
-        <v>159685.2004040743</v>
+        <v>159968.6697439041</v>
       </c>
       <c r="E21">
-        <v>-26197.21021694691</v>
+        <v>-24318.11502908336</v>
       </c>
       <c r="F21">
-        <v>35702.80856940729</v>
+        <v>37581.90375727084</v>
       </c>
       <c r="G21">
         <v>25672</v>
@@ -3015,28 +3015,28 @@
         <v>26142</v>
       </c>
       <c r="M21">
-        <v>2007.805159293596</v>
+        <v>2113.47911504589</v>
       </c>
       <c r="N21">
-        <v>24134.1948407064</v>
+        <v>24028.52088495411</v>
       </c>
       <c r="O21">
-        <v>6033.548710176601</v>
+        <v>6007.130221238527</v>
       </c>
       <c r="P21">
-        <v>18100.6461305298</v>
+        <v>18021.39066371558</v>
       </c>
       <c r="Q21">
-        <v>30348.6461305298</v>
+        <v>30269.39066371558</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1022029933477772</v>
+        <v>0.1027581409200978</v>
       </c>
       <c r="T21">
-        <v>1.099399323184488</v>
+        <v>1.11022018266465</v>
       </c>
       <c r="U21">
         <v>0.0562366166625341</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.02018768056036</v>
+        <v>12.36917829653234</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09064200523545836</v>
+        <v>0.0904858679848061</v>
       </c>
       <c r="C22">
-        <v>148058.7659866332</v>
+        <v>146464.1483442957</v>
       </c>
       <c r="D22">
-        <v>159968.6697439041</v>
+        <v>160253.1472894301</v>
       </c>
       <c r="E22">
-        <v>-24318.11502908336</v>
+        <v>-22439.01984121982</v>
       </c>
       <c r="F22">
-        <v>37581.90375727084</v>
+        <v>39460.99894513439</v>
       </c>
       <c r="G22">
         <v>25672</v>
@@ -3097,28 +3097,28 @@
         <v>26142</v>
       </c>
       <c r="M22">
-        <v>2113.47911504589</v>
+        <v>2219.153070798185</v>
       </c>
       <c r="N22">
-        <v>24028.52088495411</v>
+        <v>23922.84692920182</v>
       </c>
       <c r="O22">
-        <v>6007.130221238527</v>
+        <v>5980.711732300454</v>
       </c>
       <c r="P22">
-        <v>18021.39066371558</v>
+        <v>17942.13519690136</v>
       </c>
       <c r="Q22">
-        <v>30269.39066371558</v>
+        <v>30190.13519690136</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1027581409200978</v>
+        <v>0.1033273428613379</v>
       </c>
       <c r="T22">
-        <v>1.11022018266465</v>
+        <v>1.121314987954437</v>
       </c>
       <c r="U22">
         <v>0.0562366166625341</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.36917829653234</v>
+        <v>11.78016980622127</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0904858679848061</v>
+        <v>0.09032973073415385</v>
       </c>
       <c r="C23">
-        <v>146464.1483442957</v>
+        <v>144870.5442960126</v>
       </c>
       <c r="D23">
-        <v>160253.1472894301</v>
+        <v>160538.6384290105</v>
       </c>
       <c r="E23">
-        <v>-22439.01984121982</v>
+        <v>-20559.92465335628</v>
       </c>
       <c r="F23">
-        <v>39460.99894513438</v>
+        <v>41340.09413299793</v>
       </c>
       <c r="G23">
         <v>25672</v>
@@ -3179,28 +3179,28 @@
         <v>26142</v>
       </c>
       <c r="M23">
-        <v>2219.153070798185</v>
+        <v>2324.827026550479</v>
       </c>
       <c r="N23">
-        <v>23922.84692920182</v>
+        <v>23817.17297344952</v>
       </c>
       <c r="O23">
-        <v>5980.711732300454</v>
+        <v>5954.29324336238</v>
       </c>
       <c r="P23">
-        <v>17942.13519690136</v>
+        <v>17862.87973008714</v>
       </c>
       <c r="Q23">
-        <v>30190.13519690136</v>
+        <v>30110.87973008714</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1033273428613379</v>
+        <v>0.1039111397241484</v>
       </c>
       <c r="T23">
-        <v>1.121314987954437</v>
+        <v>1.132694275431141</v>
       </c>
       <c r="U23">
         <v>0.0562366166625341</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.78016980622128</v>
+        <v>11.24470754230212</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09032973073415385</v>
+        <v>0.0901735934835016</v>
       </c>
       <c r="C24">
-        <v>144870.5442960126</v>
+        <v>143277.9592686085</v>
       </c>
       <c r="D24">
-        <v>160538.6384290105</v>
+        <v>160825.1485894699</v>
       </c>
       <c r="E24">
-        <v>-20559.92465335628</v>
+        <v>-18680.82946549274</v>
       </c>
       <c r="F24">
-        <v>41340.09413299793</v>
+        <v>43219.18932086146</v>
       </c>
       <c r="G24">
         <v>25672</v>
@@ -3261,28 +3261,28 @@
         <v>26142</v>
       </c>
       <c r="M24">
-        <v>2324.827026550479</v>
+        <v>2430.500982302774</v>
       </c>
       <c r="N24">
-        <v>23817.17297344952</v>
+        <v>23711.49901769723</v>
       </c>
       <c r="O24">
-        <v>5954.29324336238</v>
+        <v>5927.874754424307</v>
       </c>
       <c r="P24">
-        <v>17862.87973008714</v>
+        <v>17783.62426327292</v>
       </c>
       <c r="Q24">
-        <v>30110.87973008714</v>
+        <v>30031.62426327292</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1039111397241484</v>
+        <v>0.104510100141837</v>
       </c>
       <c r="T24">
-        <v>1.132694275431141</v>
+        <v>1.144369128816331</v>
       </c>
       <c r="U24">
         <v>0.0562366166625341</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.24470754230212</v>
+        <v>10.75580721437595</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0901735934835016</v>
+        <v>0.09001745623284933</v>
       </c>
       <c r="C25">
-        <v>143277.9592686085</v>
+        <v>141686.3987277173</v>
       </c>
       <c r="D25">
-        <v>160825.1485894699</v>
+        <v>161112.6832364423</v>
       </c>
       <c r="E25">
-        <v>-18680.82946549274</v>
+        <v>-16801.73427762919</v>
       </c>
       <c r="F25">
-        <v>43219.18932086146</v>
+        <v>45098.28450872501</v>
       </c>
       <c r="G25">
         <v>25672</v>
@@ -3343,28 +3343,28 @@
         <v>26142</v>
       </c>
       <c r="M25">
-        <v>2430.500982302774</v>
+        <v>2536.174938055068</v>
       </c>
       <c r="N25">
-        <v>23711.49901769723</v>
+        <v>23605.82506194493</v>
       </c>
       <c r="O25">
-        <v>5927.874754424307</v>
+        <v>5901.456265486233</v>
       </c>
       <c r="P25">
-        <v>17783.62426327292</v>
+        <v>17704.3687964587</v>
       </c>
       <c r="Q25">
-        <v>30031.62426327292</v>
+        <v>29952.3687964587</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.104510100141837</v>
+        <v>0.1051248226757805</v>
       </c>
       <c r="T25">
-        <v>1.144369128816331</v>
+        <v>1.156351215185342</v>
       </c>
       <c r="U25">
         <v>0.0562366166625341</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.75580721437595</v>
+        <v>10.30764858044362</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09001745623284933</v>
+        <v>0.0898613189821971</v>
       </c>
       <c r="C26">
-        <v>141686.3987277173</v>
+        <v>140095.8681781307</v>
       </c>
       <c r="D26">
-        <v>161112.6832364423</v>
+        <v>161401.2478747192</v>
       </c>
       <c r="E26">
-        <v>-16801.7342776292</v>
+        <v>-14922.63908976565</v>
       </c>
       <c r="F26">
-        <v>45098.284508725</v>
+        <v>46977.37969658855</v>
       </c>
       <c r="G26">
         <v>25672</v>
@@ -3425,28 +3425,28 @@
         <v>26142</v>
       </c>
       <c r="M26">
-        <v>2536.174938055068</v>
+        <v>2641.848893807363</v>
       </c>
       <c r="N26">
-        <v>23605.82506194493</v>
+        <v>23500.15110619264</v>
       </c>
       <c r="O26">
-        <v>5901.456265486233</v>
+        <v>5875.037776548159</v>
       </c>
       <c r="P26">
-        <v>17704.3687964587</v>
+        <v>17625.11332964448</v>
       </c>
       <c r="Q26">
-        <v>29952.3687964587</v>
+        <v>29873.11332964448</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1051248226757805</v>
+        <v>0.1057559378106293</v>
       </c>
       <c r="T26">
-        <v>1.156351215185342</v>
+        <v>1.168652823857526</v>
       </c>
       <c r="U26">
         <v>0.0562366166625341</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.30764858044362</v>
+        <v>9.89534263722587</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0898613189821971</v>
+        <v>0.08970518173154483</v>
       </c>
       <c r="C27">
-        <v>140095.8681781307</v>
+        <v>138506.373164149</v>
       </c>
       <c r="D27">
-        <v>161401.2478747192</v>
+        <v>161690.8480486011</v>
       </c>
       <c r="E27">
-        <v>-14922.63908976565</v>
+        <v>-13043.54390190211</v>
       </c>
       <c r="F27">
-        <v>46977.37969658855</v>
+        <v>48856.47488445209</v>
       </c>
       <c r="G27">
         <v>25672</v>
@@ -3507,28 +3507,28 @@
         <v>26142</v>
       </c>
       <c r="M27">
-        <v>2641.848893807363</v>
+        <v>2747.522849559658</v>
       </c>
       <c r="N27">
-        <v>23500.15110619264</v>
+        <v>23394.47715044034</v>
       </c>
       <c r="O27">
-        <v>5875.037776548159</v>
+        <v>5848.619287610086</v>
       </c>
       <c r="P27">
-        <v>17625.11332964448</v>
+        <v>17545.85786283026</v>
       </c>
       <c r="Q27">
-        <v>29873.11332964448</v>
+        <v>29793.85786283026</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1057559378106293</v>
+        <v>0.1064041101112847</v>
       </c>
       <c r="T27">
-        <v>1.168652823857526</v>
+        <v>1.18128690843977</v>
       </c>
       <c r="U27">
         <v>0.0562366166625341</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.89534263722587</v>
+        <v>9.514752535794107</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08970518173154483</v>
+        <v>0.08954904448089258</v>
       </c>
       <c r="C28">
-        <v>138506.373164149</v>
+        <v>136917.9192699362</v>
       </c>
       <c r="D28">
-        <v>161690.8480486011</v>
+        <v>161981.4893422518</v>
       </c>
       <c r="E28">
-        <v>-13043.54390190211</v>
+        <v>-11164.44871403857</v>
       </c>
       <c r="F28">
-        <v>48856.47488445209</v>
+        <v>50735.57007231563</v>
       </c>
       <c r="G28">
         <v>25672</v>
@@ -3589,28 +3589,28 @@
         <v>26142</v>
       </c>
       <c r="M28">
-        <v>2747.522849559658</v>
+        <v>2853.196805311952</v>
       </c>
       <c r="N28">
-        <v>23394.47715044034</v>
+        <v>23288.80319468805</v>
       </c>
       <c r="O28">
-        <v>5848.619287610086</v>
+        <v>5822.200798672012</v>
       </c>
       <c r="P28">
-        <v>17545.85786283026</v>
+        <v>17466.60239601603</v>
       </c>
       <c r="Q28">
-        <v>29793.85786283026</v>
+        <v>29714.60239601603</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1064041101112847</v>
+        <v>0.1070700405571636</v>
       </c>
       <c r="T28">
-        <v>1.18128690843977</v>
+        <v>1.194267132325637</v>
       </c>
       <c r="U28">
         <v>0.0562366166625341</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.514752535794107</v>
+        <v>9.162354293727658</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08954904448089258</v>
+        <v>0.08939290723024033</v>
       </c>
       <c r="C29">
-        <v>136917.9192699362</v>
+        <v>135330.5121198791</v>
       </c>
       <c r="D29">
-        <v>161981.4893422518</v>
+        <v>162273.1773800582</v>
       </c>
       <c r="E29">
-        <v>-11164.44871403857</v>
+        <v>-9285.353526175022</v>
       </c>
       <c r="F29">
-        <v>50735.57007231563</v>
+        <v>52614.66526017918</v>
       </c>
       <c r="G29">
         <v>25672</v>
@@ -3671,28 +3671,28 @@
         <v>26142</v>
       </c>
       <c r="M29">
-        <v>2853.196805311952</v>
+        <v>2958.870761064246</v>
       </c>
       <c r="N29">
-        <v>23288.80319468805</v>
+        <v>23183.12923893575</v>
       </c>
       <c r="O29">
-        <v>5822.200798672012</v>
+        <v>5795.782309733939</v>
       </c>
       <c r="P29">
-        <v>17466.60239601603</v>
+        <v>17387.34692920182</v>
       </c>
       <c r="Q29">
-        <v>29714.60239601603</v>
+        <v>29635.34692920182</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1070700405571636</v>
+        <v>0.1077544690709836</v>
       </c>
       <c r="T29">
-        <v>1.194267132325637</v>
+        <v>1.207607917986111</v>
       </c>
       <c r="U29">
         <v>0.0562366166625341</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.162354293727658</v>
+        <v>8.835127354665957</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08939290723024033</v>
+        <v>0.08956301997958808</v>
       </c>
       <c r="C30">
-        <v>135330.5121198791</v>
+        <v>133133.6716679267</v>
       </c>
       <c r="D30">
-        <v>162273.1773800582</v>
+        <v>161955.4321159694</v>
       </c>
       <c r="E30">
-        <v>-9285.353526175022</v>
+        <v>-7406.258338311476</v>
       </c>
       <c r="F30">
-        <v>52614.66526017918</v>
+        <v>54493.76044804273</v>
       </c>
       <c r="G30">
         <v>25672</v>
@@ -3753,45 +3753,45 @@
         <v>26142</v>
       </c>
       <c r="M30">
-        <v>2958.870761064246</v>
+        <v>3146.285357488605</v>
       </c>
       <c r="N30">
-        <v>23183.12923893575</v>
+        <v>22995.7146425114</v>
       </c>
       <c r="O30">
-        <v>5795.782309733939</v>
+        <v>5748.928660627849</v>
       </c>
       <c r="P30">
-        <v>17387.34692920182</v>
+        <v>17246.78598188355</v>
       </c>
       <c r="Q30">
-        <v>29635.34692920182</v>
+        <v>29494.78598188355</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1077544690709836</v>
+        <v>0.1084581772612492</v>
       </c>
       <c r="T30">
-        <v>1.207607917986111</v>
+        <v>1.221324500425753</v>
       </c>
       <c r="U30">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>8.835127354665957</v>
+        <v>8.308845838721634</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08956301997958807</v>
+        <v>0.08941813272893583</v>
       </c>
       <c r="C31">
-        <v>133133.6716679267</v>
+        <v>131525.1255614397</v>
       </c>
       <c r="D31">
-        <v>161955.4321159694</v>
+        <v>162225.9811973459</v>
       </c>
       <c r="E31">
-        <v>-7406.258338311491</v>
+        <v>-5527.163150447945</v>
       </c>
       <c r="F31">
-        <v>54493.76044804271</v>
+        <v>56372.85563590626</v>
       </c>
       <c r="G31">
         <v>25672</v>
@@ -3835,28 +3835,28 @@
         <v>26142</v>
       </c>
       <c r="M31">
-        <v>3146.285357488604</v>
+        <v>3254.777956022694</v>
       </c>
       <c r="N31">
-        <v>22995.7146425114</v>
+        <v>22887.2220439773</v>
       </c>
       <c r="O31">
-        <v>5748.928660627849</v>
+        <v>5721.805510994326</v>
       </c>
       <c r="P31">
-        <v>17246.78598188355</v>
+        <v>17165.41653298298</v>
       </c>
       <c r="Q31">
-        <v>29494.78598188355</v>
+        <v>29413.41653298298</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1084581772612492</v>
+        <v>0.1091819913998081</v>
       </c>
       <c r="T31">
-        <v>1.221324500425753</v>
+        <v>1.235432985220814</v>
       </c>
       <c r="U31">
         <v>0.05773661666253409</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.308845838721634</v>
+        <v>8.031884310764246</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08941813272893583</v>
+        <v>0.08927324547828357</v>
       </c>
       <c r="C32">
-        <v>131525.1255614397</v>
+        <v>129917.4848804206</v>
       </c>
       <c r="D32">
-        <v>162225.9811973459</v>
+        <v>162497.4357041904</v>
       </c>
       <c r="E32">
-        <v>-5527.163150447945</v>
+        <v>-3648.067962584399</v>
       </c>
       <c r="F32">
-        <v>56372.85563590626</v>
+        <v>58251.9508237698</v>
       </c>
       <c r="G32">
         <v>25672</v>
@@ -3917,28 +3917,28 @@
         <v>26142</v>
       </c>
       <c r="M32">
-        <v>3254.777956022694</v>
+        <v>3363.270554556784</v>
       </c>
       <c r="N32">
-        <v>22887.2220439773</v>
+        <v>22778.72944544322</v>
       </c>
       <c r="O32">
-        <v>5721.805510994326</v>
+        <v>5694.682361360804</v>
       </c>
       <c r="P32">
-        <v>17165.41653298298</v>
+        <v>17084.04708408241</v>
       </c>
       <c r="Q32">
-        <v>29413.41653298298</v>
+        <v>29332.04708408241</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1091819913998081</v>
+        <v>0.1099267856583252</v>
       </c>
       <c r="T32">
-        <v>1.235432985220814</v>
+        <v>1.249950411604137</v>
       </c>
       <c r="U32">
         <v>0.05773661666253409</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.031884310764246</v>
+        <v>7.772791268481528</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08927324547828357</v>
+        <v>0.08912835822763129</v>
       </c>
       <c r="C33">
-        <v>129917.4848804206</v>
+        <v>128310.7541776626</v>
       </c>
       <c r="D33">
-        <v>162497.4357041904</v>
+        <v>162769.8001892959</v>
       </c>
       <c r="E33">
-        <v>-3648.067962584399</v>
+        <v>-1768.97277472086</v>
       </c>
       <c r="F33">
-        <v>58251.9508237698</v>
+        <v>60131.04601163334</v>
       </c>
       <c r="G33">
         <v>25672</v>
@@ -3999,28 +3999,28 @@
         <v>26142</v>
       </c>
       <c r="M33">
-        <v>3363.270554556784</v>
+        <v>3471.763153090874</v>
       </c>
       <c r="N33">
-        <v>22778.72944544322</v>
+        <v>22670.23684690913</v>
       </c>
       <c r="O33">
-        <v>5694.682361360804</v>
+        <v>5667.559211727282</v>
       </c>
       <c r="P33">
-        <v>17084.04708408241</v>
+        <v>17002.67763518184</v>
       </c>
       <c r="Q33">
-        <v>29332.04708408241</v>
+        <v>29250.67763518184</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1099267856583252</v>
+        <v>0.1106934856303281</v>
       </c>
       <c r="T33">
-        <v>1.249950411604137</v>
+        <v>1.264894821116382</v>
       </c>
       <c r="U33">
         <v>0.05773661666253409</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.772791268481528</v>
+        <v>7.529891541341481</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08912835822763129</v>
+        <v>0.08898347097697906</v>
       </c>
       <c r="C34">
-        <v>128310.7541776626</v>
+        <v>126704.938036534</v>
       </c>
       <c r="D34">
-        <v>162769.8001892959</v>
+        <v>163043.0792360309</v>
       </c>
       <c r="E34">
-        <v>-1768.97277472086</v>
+        <v>110.1224131426861</v>
       </c>
       <c r="F34">
-        <v>60131.04601163334</v>
+        <v>62010.14119949689</v>
       </c>
       <c r="G34">
         <v>25672</v>
@@ -4081,28 +4081,28 @@
         <v>26142</v>
       </c>
       <c r="M34">
-        <v>3471.763153090874</v>
+        <v>3580.255751624964</v>
       </c>
       <c r="N34">
-        <v>22670.23684690913</v>
+        <v>22561.74424837503</v>
       </c>
       <c r="O34">
-        <v>5667.559211727282</v>
+        <v>5640.436062093759</v>
       </c>
       <c r="P34">
-        <v>17002.67763518184</v>
+        <v>16921.30818628128</v>
       </c>
       <c r="Q34">
-        <v>29250.67763518184</v>
+        <v>29169.30818628128</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1106934856303281</v>
+        <v>0.1114830721686595</v>
       </c>
       <c r="T34">
-        <v>1.264894821116382</v>
+        <v>1.280285332405111</v>
       </c>
       <c r="U34">
         <v>0.05773661666253409</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.529891541341481</v>
+        <v>7.301713009785677</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08898347097697906</v>
+        <v>0.0888385837263268</v>
       </c>
       <c r="C35">
-        <v>126704.938036534</v>
+        <v>125100.0410712361</v>
       </c>
       <c r="D35">
-        <v>163043.0792360309</v>
+        <v>163317.2774585965</v>
       </c>
       <c r="E35">
-        <v>110.1224131426861</v>
+        <v>1989.217601006232</v>
       </c>
       <c r="F35">
-        <v>62010.14119949689</v>
+        <v>63889.23638736043</v>
       </c>
       <c r="G35">
         <v>25672</v>
@@ -4163,28 +4163,28 @@
         <v>26142</v>
       </c>
       <c r="M35">
-        <v>3580.255751624964</v>
+        <v>3688.748350159054</v>
       </c>
       <c r="N35">
-        <v>22561.74424837503</v>
+        <v>22453.25164984095</v>
       </c>
       <c r="O35">
-        <v>5640.436062093759</v>
+        <v>5613.312912460236</v>
       </c>
       <c r="P35">
-        <v>16921.30818628128</v>
+        <v>16839.93873738071</v>
       </c>
       <c r="Q35">
-        <v>29169.30818628128</v>
+        <v>29087.93873738071</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1114830721686595</v>
+        <v>0.1122965855717888</v>
       </c>
       <c r="T35">
-        <v>1.280285332405111</v>
+        <v>1.296142222823802</v>
       </c>
       <c r="U35">
         <v>0.05773661666253409</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.301713009785677</v>
+        <v>7.086956744791981</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0888385837263268</v>
+        <v>0.08869369647567456</v>
       </c>
       <c r="C36">
-        <v>125100.0410712361</v>
+        <v>123496.0679270615</v>
       </c>
       <c r="D36">
-        <v>163317.2774585965</v>
+        <v>163592.3995022855</v>
       </c>
       <c r="E36">
-        <v>1989.217601006232</v>
+        <v>3868.312788869771</v>
       </c>
       <c r="F36">
-        <v>63889.23638736043</v>
+        <v>65768.33157522397</v>
       </c>
       <c r="G36">
         <v>25672</v>
@@ -4245,28 +4245,28 @@
         <v>26142</v>
       </c>
       <c r="M36">
-        <v>3688.748350159054</v>
+        <v>3797.240948693144</v>
       </c>
       <c r="N36">
-        <v>22453.25164984095</v>
+        <v>22344.75905130686</v>
       </c>
       <c r="O36">
-        <v>5613.312912460236</v>
+        <v>5586.189762826714</v>
       </c>
       <c r="P36">
-        <v>16839.93873738071</v>
+        <v>16758.56928848014</v>
       </c>
       <c r="Q36">
-        <v>29087.93873738071</v>
+        <v>29006.56928848014</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1122965855717888</v>
+        <v>0.1131351301565529</v>
       </c>
       <c r="T36">
-        <v>1.296142222823802</v>
+        <v>1.312487017563068</v>
       </c>
       <c r="U36">
         <v>0.05773661666253409</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.086956744791981</v>
+        <v>6.884472266369353</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08869369647567456</v>
+        <v>0.0885488092250223</v>
       </c>
       <c r="C37">
-        <v>123496.0679270615</v>
+        <v>121893.0232806577</v>
       </c>
       <c r="D37">
-        <v>163592.3995022855</v>
+        <v>163868.4500437452</v>
       </c>
       <c r="E37">
-        <v>3868.312788869771</v>
+        <v>5747.40797673331</v>
       </c>
       <c r="F37">
-        <v>65768.33157522397</v>
+        <v>67647.42676308751</v>
       </c>
       <c r="G37">
         <v>25672</v>
@@ -4327,28 +4327,28 @@
         <v>26142</v>
       </c>
       <c r="M37">
-        <v>3797.240948693144</v>
+        <v>3905.733547227233</v>
       </c>
       <c r="N37">
-        <v>22344.75905130686</v>
+        <v>22236.26645277277</v>
       </c>
       <c r="O37">
-        <v>5586.189762826714</v>
+        <v>5559.066613193192</v>
       </c>
       <c r="P37">
-        <v>16758.56928848014</v>
+        <v>16677.19983957957</v>
       </c>
       <c r="Q37">
-        <v>29006.56928848014</v>
+        <v>28925.19983957957</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1131351301565529</v>
+        <v>0.1139998792595908</v>
       </c>
       <c r="T37">
-        <v>1.312487017563068</v>
+        <v>1.329342587137936</v>
       </c>
       <c r="U37">
         <v>0.05773661666253409</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.884472266369353</v>
+        <v>6.693236925636872</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08854880922502231</v>
+        <v>0.08887567197437005</v>
       </c>
       <c r="C38">
-        <v>121893.0232806577</v>
+        <v>119392.4784413257</v>
       </c>
       <c r="D38">
-        <v>163868.4500437452</v>
+        <v>163247.0003922767</v>
       </c>
       <c r="E38">
-        <v>5747.40797673331</v>
+        <v>7626.503164596848</v>
       </c>
       <c r="F38">
-        <v>67647.42676308751</v>
+        <v>69526.52195095105</v>
       </c>
       <c r="G38">
         <v>25672</v>
@@ -4409,45 +4409,45 @@
         <v>26142</v>
       </c>
       <c r="M38">
-        <v>3905.733547227233</v>
+        <v>4132.42123307794</v>
       </c>
       <c r="N38">
-        <v>22236.26645277277</v>
+        <v>22009.57876692206</v>
       </c>
       <c r="O38">
-        <v>5559.066613193192</v>
+        <v>5502.394691730515</v>
       </c>
       <c r="P38">
-        <v>16677.19983957957</v>
+        <v>16507.18407519154</v>
       </c>
       <c r="Q38">
-        <v>28925.19983957957</v>
+        <v>28755.18407519154</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1139998792595908</v>
+        <v>0.1148920807151061</v>
       </c>
       <c r="T38">
-        <v>1.329342587137936</v>
+        <v>1.346733254159626</v>
       </c>
       <c r="U38">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.693236925636872</v>
+        <v>6.326073390279413</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08887567197437005</v>
+        <v>0.08874353472371781</v>
       </c>
       <c r="C39">
-        <v>119392.4784413257</v>
+        <v>117764.0414885865</v>
       </c>
       <c r="D39">
-        <v>163247.0003922767</v>
+        <v>163497.658627401</v>
       </c>
       <c r="E39">
-        <v>7626.503164596848</v>
+        <v>9505.598352460387</v>
       </c>
       <c r="F39">
-        <v>69526.52195095105</v>
+        <v>71405.61713881459</v>
       </c>
       <c r="G39">
         <v>25672</v>
@@ -4491,28 +4491,28 @@
         <v>26142</v>
       </c>
       <c r="M39">
-        <v>4132.42123307794</v>
+        <v>4244.108293431397</v>
       </c>
       <c r="N39">
-        <v>22009.57876692206</v>
+        <v>21897.8917065686</v>
       </c>
       <c r="O39">
-        <v>5502.394691730515</v>
+        <v>5474.472926642151</v>
       </c>
       <c r="P39">
-        <v>16507.18407519154</v>
+        <v>16423.41877992645</v>
       </c>
       <c r="Q39">
-        <v>28755.18407519154</v>
+        <v>28671.41877992645</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1148920807151061</v>
+        <v>0.1158130628627348</v>
       </c>
       <c r="T39">
-        <v>1.346733254159626</v>
+        <v>1.364684910440079</v>
       </c>
       <c r="U39">
         <v>0.05943661666253409</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.326073390279413</v>
+        <v>6.159597774745746</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08874353472371781</v>
+        <v>0.08861139747306554</v>
       </c>
       <c r="C40">
-        <v>117764.0414885865</v>
+        <v>116136.3754678817</v>
       </c>
       <c r="D40">
-        <v>163497.658627401</v>
+        <v>163749.0877945599</v>
       </c>
       <c r="E40">
-        <v>9505.598352460387</v>
+        <v>11384.69354032394</v>
       </c>
       <c r="F40">
-        <v>71405.61713881459</v>
+        <v>73284.71232667814</v>
       </c>
       <c r="G40">
         <v>25672</v>
@@ -4573,28 +4573,28 @@
         <v>26142</v>
       </c>
       <c r="M40">
-        <v>4244.108293431397</v>
+        <v>4355.795353784856</v>
       </c>
       <c r="N40">
-        <v>21897.8917065686</v>
+        <v>21786.20464621514</v>
       </c>
       <c r="O40">
-        <v>5474.472926642151</v>
+        <v>5446.551161553786</v>
       </c>
       <c r="P40">
-        <v>16423.41877992645</v>
+        <v>16339.65348466136</v>
       </c>
       <c r="Q40">
-        <v>28671.41877992645</v>
+        <v>28587.65348466136</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1158130628627348</v>
+        <v>0.1167642411463513</v>
       </c>
       <c r="T40">
-        <v>1.364684910440079</v>
+        <v>1.383225145614974</v>
       </c>
       <c r="U40">
         <v>0.05943661666253409</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.159597774745746</v>
+        <v>6.001659370265084</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08861139747306554</v>
+        <v>0.0884792602224133</v>
       </c>
       <c r="C41">
-        <v>116136.3754678817</v>
+        <v>114509.4839413421</v>
       </c>
       <c r="D41">
-        <v>163749.0877945599</v>
+        <v>164001.2914558838</v>
       </c>
       <c r="E41">
-        <v>11384.69354032394</v>
+        <v>13263.78872818748</v>
       </c>
       <c r="F41">
-        <v>73284.71232667814</v>
+        <v>75163.80751454168</v>
       </c>
       <c r="G41">
         <v>25672</v>
@@ -4655,28 +4655,28 @@
         <v>26142</v>
       </c>
       <c r="M41">
-        <v>4355.795353784856</v>
+        <v>4467.482414138313</v>
       </c>
       <c r="N41">
-        <v>21786.20464621514</v>
+        <v>21674.51758586169</v>
       </c>
       <c r="O41">
-        <v>5446.551161553786</v>
+        <v>5418.629396465421</v>
       </c>
       <c r="P41">
-        <v>16339.65348466136</v>
+        <v>16255.88818939626</v>
       </c>
       <c r="Q41">
-        <v>28587.65348466136</v>
+        <v>28503.88818939626</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1167642411463513</v>
+        <v>0.1177471253727551</v>
       </c>
       <c r="T41">
-        <v>1.383225145614974</v>
+        <v>1.402383388629032</v>
       </c>
       <c r="U41">
         <v>0.05943661666253409</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.001659370265084</v>
+        <v>5.851617886008458</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0884792602224133</v>
+        <v>0.08834712297176106</v>
       </c>
       <c r="C42">
-        <v>114509.4839413421</v>
+        <v>112883.3704930775</v>
       </c>
       <c r="D42">
-        <v>164001.2914558838</v>
+        <v>164254.2731954827</v>
       </c>
       <c r="E42">
-        <v>13263.78872818748</v>
+        <v>15142.88391605102</v>
       </c>
       <c r="F42">
-        <v>75163.80751454168</v>
+        <v>77042.90270240522</v>
       </c>
       <c r="G42">
         <v>25672</v>
@@ -4737,28 +4737,28 @@
         <v>26142</v>
       </c>
       <c r="M42">
-        <v>4467.482414138313</v>
+        <v>4579.169474491771</v>
       </c>
       <c r="N42">
-        <v>21674.51758586169</v>
+        <v>21562.83052550823</v>
       </c>
       <c r="O42">
-        <v>5418.629396465421</v>
+        <v>5390.707631377058</v>
       </c>
       <c r="P42">
-        <v>16255.88818939626</v>
+        <v>16172.12289413117</v>
       </c>
       <c r="Q42">
-        <v>28503.88818939626</v>
+        <v>28420.12289413117</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1177471253727551</v>
+        <v>0.1187633277085285</v>
       </c>
       <c r="T42">
-        <v>1.402383388629032</v>
+        <v>1.422191063609668</v>
       </c>
       <c r="U42">
         <v>0.05943661666253409</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.851617886008458</v>
+        <v>5.708895498544837</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08834712297176106</v>
+        <v>0.08846698572110878</v>
       </c>
       <c r="C43">
-        <v>112883.3704930775</v>
+        <v>110774.7607234946</v>
       </c>
       <c r="D43">
-        <v>164254.2731954827</v>
+        <v>164024.7586137634</v>
       </c>
       <c r="E43">
-        <v>15142.88391605102</v>
+        <v>17021.97910391457</v>
       </c>
       <c r="F43">
-        <v>77042.90270240522</v>
+        <v>78921.99789026877</v>
       </c>
       <c r="G43">
         <v>25672</v>
@@ -4819,45 +4819,45 @@
         <v>26142</v>
       </c>
       <c r="M43">
-        <v>4579.169474491771</v>
+        <v>4753.994133157445</v>
       </c>
       <c r="N43">
-        <v>21562.83052550823</v>
+        <v>21388.00586684256</v>
       </c>
       <c r="O43">
-        <v>5390.707631377058</v>
+        <v>5347.001466710639</v>
       </c>
       <c r="P43">
-        <v>16172.12289413117</v>
+        <v>16041.00440013192</v>
       </c>
       <c r="Q43">
-        <v>28420.12289413117</v>
+        <v>28289.00440013192</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1187633277085285</v>
+        <v>0.1198145715041561</v>
       </c>
       <c r="T43">
-        <v>1.422191063609668</v>
+        <v>1.442681761865498</v>
       </c>
       <c r="U43">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>5.708895498544837</v>
+        <v>5.498955040282592</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0884669857211088</v>
+        <v>0.08834084847045656</v>
       </c>
       <c r="C44">
-        <v>110774.7607234946</v>
+        <v>109137.2122979935</v>
       </c>
       <c r="D44">
-        <v>164024.7586137633</v>
+        <v>164266.3053761258</v>
       </c>
       <c r="E44">
-        <v>17021.97910391456</v>
+        <v>18901.0742917781</v>
       </c>
       <c r="F44">
-        <v>78921.99789026876</v>
+        <v>80801.0930781323</v>
       </c>
       <c r="G44">
         <v>25672</v>
@@ -4901,28 +4901,28 @@
         <v>26142</v>
       </c>
       <c r="M44">
-        <v>4753.994133157444</v>
+        <v>4867.184469661192</v>
       </c>
       <c r="N44">
-        <v>21388.00586684256</v>
+        <v>21274.81553033881</v>
       </c>
       <c r="O44">
-        <v>5347.001466710639</v>
+        <v>5318.703882584702</v>
       </c>
       <c r="P44">
-        <v>16041.00440013192</v>
+        <v>15956.11164775411</v>
       </c>
       <c r="Q44">
-        <v>28289.00440013192</v>
+        <v>28204.11164775411</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1198145715041561</v>
+        <v>0.1209027010469988</v>
       </c>
       <c r="T44">
-        <v>1.442681761865498</v>
+        <v>1.463891431989954</v>
       </c>
       <c r="U44">
         <v>0.0602366166625341</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.498955040282593</v>
+        <v>5.371072364927183</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08834084847045656</v>
+        <v>0.0882147112198043</v>
       </c>
       <c r="C45">
-        <v>109137.2122979935</v>
+        <v>107500.3763367034</v>
       </c>
       <c r="D45">
-        <v>164266.3053761258</v>
+        <v>164508.5646026992</v>
       </c>
       <c r="E45">
-        <v>18901.0742917781</v>
+        <v>20780.16947964165</v>
       </c>
       <c r="F45">
-        <v>80801.0930781323</v>
+        <v>82680.18826599585</v>
       </c>
       <c r="G45">
         <v>25672</v>
@@ -4983,28 +4983,28 @@
         <v>26142</v>
       </c>
       <c r="M45">
-        <v>4867.184469661192</v>
+        <v>4980.374806164942</v>
       </c>
       <c r="N45">
-        <v>21274.81553033881</v>
+        <v>21161.62519383506</v>
       </c>
       <c r="O45">
-        <v>5318.703882584702</v>
+        <v>5290.406298458764</v>
       </c>
       <c r="P45">
-        <v>15956.11164775411</v>
+        <v>15871.21889537629</v>
       </c>
       <c r="Q45">
-        <v>28204.11164775411</v>
+        <v>28119.21889537629</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1209027010469988</v>
+        <v>0.1220296923592286</v>
       </c>
       <c r="T45">
-        <v>1.463891431989954</v>
+        <v>1.485858590333141</v>
       </c>
       <c r="U45">
         <v>0.0602366166625341</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.371072364927183</v>
+        <v>5.249002538451564</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0882147112198043</v>
+        <v>0.08808857396915204</v>
       </c>
       <c r="C46">
-        <v>107500.3763367034</v>
+        <v>105864.2559964974</v>
       </c>
       <c r="D46">
-        <v>164508.5646026992</v>
+        <v>164751.5394503568</v>
       </c>
       <c r="E46">
-        <v>20780.16947964165</v>
+        <v>22659.26466750519</v>
       </c>
       <c r="F46">
-        <v>82680.18826599585</v>
+        <v>84559.28345385939</v>
       </c>
       <c r="G46">
         <v>25672</v>
@@ -5065,28 +5065,28 @@
         <v>26142</v>
       </c>
       <c r="M46">
-        <v>4980.374806164942</v>
+        <v>5093.56514266869</v>
       </c>
       <c r="N46">
-        <v>21161.62519383506</v>
+        <v>21048.43485733131</v>
       </c>
       <c r="O46">
-        <v>5290.406298458764</v>
+        <v>5262.108714332828</v>
       </c>
       <c r="P46">
-        <v>15871.21889537629</v>
+        <v>15786.32614299848</v>
       </c>
       <c r="Q46">
-        <v>28119.21889537629</v>
+        <v>28034.32614299849</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1220296923592286</v>
+        <v>0.1231976651737214</v>
       </c>
       <c r="T46">
-        <v>1.485858590333141</v>
+        <v>1.508624554434261</v>
       </c>
       <c r="U46">
         <v>0.0602366166625341</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.249002538451564</v>
+        <v>5.132358037597086</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08808857396915204</v>
+        <v>0.08796243671849979</v>
       </c>
       <c r="C47">
-        <v>105864.2559964974</v>
+        <v>104228.8544529266</v>
       </c>
       <c r="D47">
-        <v>164751.5394503568</v>
+        <v>164995.2330946495</v>
       </c>
       <c r="E47">
-        <v>22659.26466750519</v>
+        <v>24538.35985536873</v>
       </c>
       <c r="F47">
-        <v>84559.28345385939</v>
+        <v>86438.37864172293</v>
       </c>
       <c r="G47">
         <v>25672</v>
@@ -5147,28 +5147,28 @@
         <v>26142</v>
       </c>
       <c r="M47">
-        <v>5093.56514266869</v>
+        <v>5206.755479172439</v>
       </c>
       <c r="N47">
-        <v>21048.43485733131</v>
+        <v>20935.24452082756</v>
       </c>
       <c r="O47">
-        <v>5262.108714332828</v>
+        <v>5233.81113020689</v>
       </c>
       <c r="P47">
-        <v>15786.32614299848</v>
+        <v>15701.43339062067</v>
       </c>
       <c r="Q47">
-        <v>28034.32614299849</v>
+        <v>27949.43339062067</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1231976651737214</v>
+        <v>0.1244088962406028</v>
       </c>
       <c r="T47">
-        <v>1.508624554434261</v>
+        <v>1.532233702390979</v>
       </c>
       <c r="U47">
         <v>0.0602366166625341</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.132358037597086</v>
+        <v>5.020785036779758</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08796243671849979</v>
+        <v>0.08783629946784755</v>
       </c>
       <c r="C48">
-        <v>104228.8544529266</v>
+        <v>102594.1749003584</v>
       </c>
       <c r="D48">
-        <v>164995.2330946495</v>
+        <v>165239.6487299449</v>
       </c>
       <c r="E48">
-        <v>24538.35985536873</v>
+        <v>26417.45504323228</v>
       </c>
       <c r="F48">
-        <v>86438.37864172293</v>
+        <v>88317.47382958648</v>
       </c>
       <c r="G48">
         <v>25672</v>
@@ -5229,28 +5229,28 @@
         <v>26142</v>
       </c>
       <c r="M48">
-        <v>5206.755479172439</v>
+        <v>5319.945815676188</v>
       </c>
       <c r="N48">
-        <v>20935.24452082756</v>
+        <v>20822.05418432381</v>
       </c>
       <c r="O48">
-        <v>5233.81113020689</v>
+        <v>5205.513546080952</v>
       </c>
       <c r="P48">
-        <v>15701.43339062067</v>
+        <v>15616.54063824286</v>
       </c>
       <c r="Q48">
-        <v>27949.43339062067</v>
+        <v>27864.54063824286</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1244088962406028</v>
+        <v>0.1256658341401967</v>
       </c>
       <c r="T48">
-        <v>1.532233702390979</v>
+        <v>1.556733761591346</v>
       </c>
       <c r="U48">
         <v>0.0602366166625341</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.020785036779758</v>
+        <v>4.913959823231251</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08783629946784755</v>
+        <v>0.08771016221719527</v>
       </c>
       <c r="C49">
-        <v>102594.1749003584</v>
+        <v>100960.2205521164</v>
       </c>
       <c r="D49">
-        <v>165239.6487299449</v>
+        <v>165484.7895695664</v>
       </c>
       <c r="E49">
-        <v>26417.45504323228</v>
+        <v>28296.55023109582</v>
       </c>
       <c r="F49">
-        <v>88317.47382958648</v>
+        <v>90196.56901745002</v>
       </c>
       <c r="G49">
         <v>25672</v>
@@ -5311,28 +5311,28 @@
         <v>26142</v>
       </c>
       <c r="M49">
-        <v>5319.945815676188</v>
+        <v>5433.136152179936</v>
       </c>
       <c r="N49">
-        <v>20822.05418432381</v>
+        <v>20708.86384782006</v>
       </c>
       <c r="O49">
-        <v>5205.513546080952</v>
+        <v>5177.215961955016</v>
       </c>
       <c r="P49">
-        <v>15616.54063824286</v>
+        <v>15531.64788586505</v>
       </c>
       <c r="Q49">
-        <v>27864.54063824286</v>
+        <v>27779.64788586505</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1256658341401967</v>
+        <v>0.1269711158051596</v>
       </c>
       <c r="T49">
-        <v>1.556733761591346</v>
+        <v>1.582176130760959</v>
       </c>
       <c r="U49">
         <v>0.0602366166625341</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.913959823231251</v>
+        <v>4.811585660247268</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08771016221719527</v>
+        <v>0.08758402496654302</v>
       </c>
       <c r="C50">
-        <v>100960.2205521164</v>
+        <v>99326.9946406207</v>
       </c>
       <c r="D50">
-        <v>165484.7895695664</v>
+        <v>165730.6588459343</v>
       </c>
       <c r="E50">
-        <v>28296.5502310958</v>
+        <v>30175.64541895936</v>
       </c>
       <c r="F50">
-        <v>90196.56901745001</v>
+        <v>92075.66420531356</v>
       </c>
       <c r="G50">
         <v>25672</v>
@@ -5393,28 +5393,28 @@
         <v>26142</v>
       </c>
       <c r="M50">
-        <v>5433.136152179935</v>
+        <v>5546.326488683685</v>
       </c>
       <c r="N50">
-        <v>20708.86384782007</v>
+        <v>20595.67351131632</v>
       </c>
       <c r="O50">
-        <v>5177.215961955017</v>
+        <v>5148.918377829079</v>
       </c>
       <c r="P50">
-        <v>15531.64788586505</v>
+        <v>15446.75513348724</v>
       </c>
       <c r="Q50">
-        <v>27779.64788586505</v>
+        <v>27694.75513348724</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1269711158051596</v>
+        <v>0.1283275849863956</v>
       </c>
       <c r="T50">
-        <v>1.582176130760959</v>
+        <v>1.608616239898007</v>
       </c>
       <c r="U50">
         <v>0.0602366166625341</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.811585660247269</v>
+        <v>4.713390034527936</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08758402496654302</v>
+        <v>0.08745788771589078</v>
       </c>
       <c r="C51">
-        <v>99326.9946406207</v>
+        <v>97694.50041753058</v>
       </c>
       <c r="D51">
-        <v>165730.6588459343</v>
+        <v>165977.2598107077</v>
       </c>
       <c r="E51">
-        <v>30175.64541895936</v>
+        <v>32054.7406068229</v>
       </c>
       <c r="F51">
-        <v>92075.66420531356</v>
+        <v>93954.7593931771</v>
       </c>
       <c r="G51">
         <v>25672</v>
@@ -5475,28 +5475,28 @@
         <v>26142</v>
       </c>
       <c r="M51">
-        <v>5546.326488683685</v>
+        <v>5659.516825187434</v>
       </c>
       <c r="N51">
-        <v>20595.67351131632</v>
+        <v>20482.48317481257</v>
       </c>
       <c r="O51">
-        <v>5148.918377829079</v>
+        <v>5120.620793703141</v>
       </c>
       <c r="P51">
-        <v>15446.75513348724</v>
+        <v>15361.86238110942</v>
       </c>
       <c r="Q51">
-        <v>27694.75513348724</v>
+        <v>27609.86238110942</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1283275849863956</v>
+        <v>0.129738312934881</v>
       </c>
       <c r="T51">
-        <v>1.608616239898007</v>
+        <v>1.636113953400537</v>
       </c>
       <c r="U51">
         <v>0.0602366166625341</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.713390034527936</v>
+        <v>4.619122233837377</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08745788771589078</v>
+        <v>0.08733175046523853</v>
       </c>
       <c r="C52">
-        <v>97694.50041753058</v>
+        <v>96062.74115388734</v>
       </c>
       <c r="D52">
-        <v>165977.2598107077</v>
+        <v>166224.595734928</v>
       </c>
       <c r="E52">
-        <v>32054.7406068229</v>
+        <v>33933.83579468643</v>
       </c>
       <c r="F52">
-        <v>93954.7593931771</v>
+        <v>95833.85458104064</v>
       </c>
       <c r="G52">
         <v>25672</v>
@@ -5557,28 +5557,28 @@
         <v>26142</v>
       </c>
       <c r="M52">
-        <v>5659.516825187434</v>
+        <v>5772.707161691182</v>
       </c>
       <c r="N52">
-        <v>20482.48317481257</v>
+        <v>20369.29283830882</v>
       </c>
       <c r="O52">
-        <v>5120.620793703141</v>
+        <v>5092.323209577205</v>
       </c>
       <c r="P52">
-        <v>15361.86238110942</v>
+        <v>15276.96962873161</v>
       </c>
       <c r="Q52">
-        <v>27609.86238110942</v>
+        <v>27524.96962873161</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.129738312934881</v>
+        <v>0.1312066216159576</v>
       </c>
       <c r="T52">
-        <v>1.636113953400537</v>
+        <v>1.664734022556232</v>
       </c>
       <c r="U52">
         <v>0.0602366166625341</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.619122233837377</v>
+        <v>4.528551209644489</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08733175046523853</v>
+        <v>0.08720561321458625</v>
       </c>
       <c r="C53">
-        <v>96062.74115388734</v>
+        <v>94431.72014025933</v>
       </c>
       <c r="D53">
-        <v>166224.595734928</v>
+        <v>166472.6699091635</v>
       </c>
       <c r="E53">
-        <v>33933.83579468643</v>
+        <v>35812.93098254999</v>
       </c>
       <c r="F53">
-        <v>95833.85458104064</v>
+        <v>97712.94976890419</v>
       </c>
       <c r="G53">
         <v>25672</v>
@@ -5639,28 +5639,28 @@
         <v>26142</v>
       </c>
       <c r="M53">
-        <v>5772.707161691182</v>
+        <v>5885.897498194931</v>
       </c>
       <c r="N53">
-        <v>20369.29283830882</v>
+        <v>20256.10250180507</v>
       </c>
       <c r="O53">
-        <v>5092.323209577205</v>
+        <v>5064.025625451267</v>
       </c>
       <c r="P53">
-        <v>15276.96962873161</v>
+        <v>15192.0768763538</v>
       </c>
       <c r="Q53">
-        <v>27524.96962873161</v>
+        <v>27440.0768763538</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1312066216159576</v>
+        <v>0.1327361098254124</v>
       </c>
       <c r="T53">
-        <v>1.664734022556232</v>
+        <v>1.694546594593413</v>
       </c>
       <c r="U53">
         <v>0.0602366166625341</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.528551209644489</v>
+        <v>4.441463686382093</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08720561321458625</v>
+        <v>0.08707947596393401</v>
       </c>
       <c r="C54">
-        <v>94431.72014025933</v>
+        <v>92801.44068688745</v>
       </c>
       <c r="D54">
-        <v>166472.6699091635</v>
+        <v>166721.4856436552</v>
       </c>
       <c r="E54">
-        <v>35812.93098254999</v>
+        <v>37692.02617041353</v>
       </c>
       <c r="F54">
-        <v>97712.94976890419</v>
+        <v>99592.04495676773</v>
       </c>
       <c r="G54">
         <v>25672</v>
@@ -5721,28 +5721,28 @@
         <v>26142</v>
       </c>
       <c r="M54">
-        <v>5885.897498194931</v>
+        <v>5999.08783469868</v>
       </c>
       <c r="N54">
-        <v>20256.10250180507</v>
+        <v>20142.91216530132</v>
       </c>
       <c r="O54">
-        <v>5064.025625451267</v>
+        <v>5035.72804132533</v>
       </c>
       <c r="P54">
-        <v>15192.0768763538</v>
+        <v>15107.18412397599</v>
       </c>
       <c r="Q54">
-        <v>27440.0768763538</v>
+        <v>27355.18412397599</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1327361098254124</v>
+        <v>0.1343306826395249</v>
       </c>
       <c r="T54">
-        <v>1.694546594593413</v>
+        <v>1.725627786717284</v>
       </c>
       <c r="U54">
         <v>0.0602366166625341</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.441463686382093</v>
+        <v>4.357662484752243</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08707947596393401</v>
+        <v>0.08695333871328176</v>
       </c>
       <c r="C55">
-        <v>92801.44068688745</v>
+        <v>91171.90612383274</v>
       </c>
       <c r="D55">
-        <v>166721.4856436552</v>
+        <v>166971.046268464</v>
       </c>
       <c r="E55">
-        <v>37692.02617041353</v>
+        <v>39571.12135827707</v>
       </c>
       <c r="F55">
-        <v>99592.04495676773</v>
+        <v>101471.1401446313</v>
       </c>
       <c r="G55">
         <v>25672</v>
@@ -5803,28 +5803,28 @@
         <v>26142</v>
       </c>
       <c r="M55">
-        <v>5999.08783469868</v>
+        <v>6112.278171202428</v>
       </c>
       <c r="N55">
-        <v>20142.91216530132</v>
+        <v>20029.72182879757</v>
       </c>
       <c r="O55">
-        <v>5035.72804132533</v>
+        <v>5007.430457199393</v>
       </c>
       <c r="P55">
-        <v>15107.18412397599</v>
+        <v>15022.29137159818</v>
       </c>
       <c r="Q55">
-        <v>27355.18412397599</v>
+        <v>27270.29137159818</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1343306826395249</v>
+        <v>0.1359945847064249</v>
       </c>
       <c r="T55">
-        <v>1.725627786717284</v>
+        <v>1.758060335020453</v>
       </c>
       <c r="U55">
         <v>0.0602366166625341</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.357662484752243</v>
+        <v>4.276965031330905</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08695333871328176</v>
+        <v>0.08723970146262952</v>
       </c>
       <c r="C56">
-        <v>91171.90612383274</v>
+        <v>88727.32022316889</v>
       </c>
       <c r="D56">
-        <v>166971.046268464</v>
+        <v>166405.5555556637</v>
       </c>
       <c r="E56">
-        <v>39571.12135827707</v>
+        <v>41450.21654614062</v>
       </c>
       <c r="F56">
-        <v>101471.1401446313</v>
+        <v>103350.2353324948</v>
       </c>
       <c r="G56">
         <v>25672</v>
@@ -5885,45 +5885,45 @@
         <v>26142</v>
       </c>
       <c r="M56">
-        <v>6112.278171202428</v>
+        <v>6328.818743038672</v>
       </c>
       <c r="N56">
-        <v>20029.72182879757</v>
+        <v>19813.18125696133</v>
       </c>
       <c r="O56">
-        <v>5007.430457199393</v>
+        <v>4953.295314240332</v>
       </c>
       <c r="P56">
-        <v>15022.29137159818</v>
+        <v>14859.885942721</v>
       </c>
       <c r="Q56">
-        <v>27270.29137159818</v>
+        <v>27107.885942721</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1359945847064249</v>
+        <v>0.1377324379762982</v>
       </c>
       <c r="T56">
-        <v>1.758060335020453</v>
+        <v>1.791934329914874</v>
       </c>
       <c r="U56">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.276965031330905</v>
+        <v>4.130628646736748</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08723970146262952</v>
+        <v>0.08712106421197725</v>
       </c>
       <c r="C57">
-        <v>88727.32022316889</v>
+        <v>87082.03685757164</v>
       </c>
       <c r="D57">
-        <v>166405.5555556637</v>
+        <v>166639.36737793</v>
       </c>
       <c r="E57">
-        <v>41450.21654614062</v>
+        <v>43329.31173400416</v>
       </c>
       <c r="F57">
-        <v>103350.2353324948</v>
+        <v>105229.3305203584</v>
       </c>
       <c r="G57">
         <v>25672</v>
@@ -5967,28 +5967,28 @@
         <v>26142</v>
       </c>
       <c r="M57">
-        <v>6328.818743038672</v>
+        <v>6443.888174730285</v>
       </c>
       <c r="N57">
-        <v>19813.18125696133</v>
+        <v>19698.11182526972</v>
       </c>
       <c r="O57">
-        <v>4953.295314240332</v>
+        <v>4924.527956317429</v>
       </c>
       <c r="P57">
-        <v>14859.885942721</v>
+        <v>14773.58386895229</v>
       </c>
       <c r="Q57">
-        <v>27107.885942721</v>
+        <v>27021.58386895229</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1377324379762982</v>
+        <v>0.1395492845766203</v>
       </c>
       <c r="T57">
-        <v>1.791934329914874</v>
+        <v>1.82734805184995</v>
       </c>
       <c r="U57">
         <v>0.0612366166625341</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.130628646736748</v>
+        <v>4.056867420902163</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08712106421197725</v>
+        <v>0.087002426961325</v>
       </c>
       <c r="C58">
-        <v>87082.03685757164</v>
+        <v>85437.41146145826</v>
       </c>
       <c r="D58">
-        <v>166639.36737793</v>
+        <v>166873.8371696802</v>
       </c>
       <c r="E58">
-        <v>43329.31173400416</v>
+        <v>45208.4069218677</v>
       </c>
       <c r="F58">
-        <v>105229.3305203584</v>
+        <v>107108.4257082219</v>
       </c>
       <c r="G58">
         <v>25672</v>
@@ -6049,28 +6049,28 @@
         <v>26142</v>
       </c>
       <c r="M58">
-        <v>6443.888174730285</v>
+        <v>6558.957606421896</v>
       </c>
       <c r="N58">
-        <v>19698.11182526972</v>
+        <v>19583.0423935781</v>
       </c>
       <c r="O58">
-        <v>4924.527956317429</v>
+        <v>4895.760598394526</v>
       </c>
       <c r="P58">
-        <v>14773.58386895229</v>
+        <v>14687.28179518358</v>
       </c>
       <c r="Q58">
-        <v>27021.58386895229</v>
+        <v>26935.28179518358</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1395492845766203</v>
+        <v>0.1414506356699806</v>
       </c>
       <c r="T58">
-        <v>1.82734805184995</v>
+        <v>1.864408923642473</v>
       </c>
       <c r="U58">
         <v>0.0612366166625341</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.056867420902163</v>
+        <v>3.985694308254757</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.087002426961325</v>
+        <v>0.08688378971067275</v>
       </c>
       <c r="C59">
-        <v>85437.41146145826</v>
+        <v>83793.44681612853</v>
       </c>
       <c r="D59">
-        <v>166873.8371696802</v>
+        <v>167108.967712214</v>
       </c>
       <c r="E59">
-        <v>45208.4069218677</v>
+        <v>47087.50210973125</v>
       </c>
       <c r="F59">
-        <v>107108.4257082219</v>
+        <v>108987.5208960855</v>
       </c>
       <c r="G59">
         <v>25672</v>
@@ -6131,28 +6131,28 @@
         <v>26142</v>
       </c>
       <c r="M59">
-        <v>6558.957606421896</v>
+        <v>6674.02703811351</v>
       </c>
       <c r="N59">
-        <v>19583.0423935781</v>
+        <v>19467.97296188649</v>
       </c>
       <c r="O59">
-        <v>4895.760598394526</v>
+        <v>4866.993240471623</v>
       </c>
       <c r="P59">
-        <v>14687.28179518358</v>
+        <v>14600.97972141487</v>
       </c>
       <c r="Q59">
-        <v>26935.28179518358</v>
+        <v>26848.97972141487</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1414506356699806</v>
+        <v>0.1434425272915962</v>
       </c>
       <c r="T59">
-        <v>1.864408923642473</v>
+        <v>1.903234598853686</v>
       </c>
       <c r="U59">
         <v>0.0612366166625341</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.985694308254757</v>
+        <v>3.916975440871054</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08688378971067275</v>
+        <v>0.08676515246002051</v>
       </c>
       <c r="C60">
-        <v>83793.44681612856</v>
+        <v>82150.14571858013</v>
       </c>
       <c r="D60">
-        <v>167108.967712214</v>
+        <v>167344.7618025291</v>
       </c>
       <c r="E60">
-        <v>47087.50210973122</v>
+        <v>48966.59729759477</v>
       </c>
       <c r="F60">
-        <v>108987.5208960854</v>
+        <v>110866.616083949</v>
       </c>
       <c r="G60">
         <v>25672</v>
@@ -6213,28 +6213,28 @@
         <v>26142</v>
       </c>
       <c r="M60">
-        <v>6674.027038113508</v>
+        <v>6789.09646980512</v>
       </c>
       <c r="N60">
-        <v>19467.97296188649</v>
+        <v>19352.90353019488</v>
       </c>
       <c r="O60">
-        <v>4866.993240471623</v>
+        <v>4838.22588254872</v>
       </c>
       <c r="P60">
-        <v>14600.97972141487</v>
+        <v>14514.67764764616</v>
       </c>
       <c r="Q60">
-        <v>26848.97972141487</v>
+        <v>26762.67764764616</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1434425272915962</v>
+        <v>0.1455315843581687</v>
       </c>
       <c r="T60">
-        <v>1.903234598853686</v>
+        <v>1.943954209441056</v>
       </c>
       <c r="U60">
         <v>0.0612366166625341</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.916975440871055</v>
+        <v>3.850586026619003</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08676515246002051</v>
+        <v>0.08664651520936824</v>
       </c>
       <c r="C61">
-        <v>82150.14571858013</v>
+        <v>80507.51098161949</v>
       </c>
       <c r="D61">
-        <v>167344.7618025291</v>
+        <v>167581.222253432</v>
       </c>
       <c r="E61">
-        <v>48966.59729759477</v>
+        <v>50845.69248545831</v>
       </c>
       <c r="F61">
-        <v>110866.616083949</v>
+        <v>112745.7112718125</v>
       </c>
       <c r="G61">
         <v>25672</v>
@@ -6295,28 +6295,28 @@
         <v>26142</v>
       </c>
       <c r="M61">
-        <v>6789.09646980512</v>
+        <v>6904.165901496733</v>
       </c>
       <c r="N61">
-        <v>19352.90353019488</v>
+        <v>19237.83409850327</v>
       </c>
       <c r="O61">
-        <v>4838.22588254872</v>
+        <v>4809.458524625817</v>
       </c>
       <c r="P61">
-        <v>14514.67764764616</v>
+        <v>14428.37557387745</v>
       </c>
       <c r="Q61">
-        <v>26762.67764764616</v>
+        <v>26676.37557387745</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1455315843581687</v>
+        <v>0.1477250942780697</v>
       </c>
       <c r="T61">
-        <v>1.943954209441056</v>
+        <v>1.986709800557795</v>
       </c>
       <c r="U61">
         <v>0.0612366166625341</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.850586026619003</v>
+        <v>3.78640959284202</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08664651520936824</v>
+        <v>0.086527877958716</v>
       </c>
       <c r="C62">
-        <v>80507.51098161949</v>
+        <v>78865.54543397365</v>
       </c>
       <c r="D62">
-        <v>167581.222253432</v>
+        <v>167818.3518936497</v>
       </c>
       <c r="E62">
-        <v>50845.69248545831</v>
+        <v>52724.78767332185</v>
       </c>
       <c r="F62">
-        <v>112745.7112718125</v>
+        <v>114624.8064596761</v>
       </c>
       <c r="G62">
         <v>25672</v>
@@ -6377,28 +6377,28 @@
         <v>26142</v>
       </c>
       <c r="M62">
-        <v>6904.165901496733</v>
+        <v>7019.235333188345</v>
       </c>
       <c r="N62">
-        <v>19237.83409850327</v>
+        <v>19122.76466681165</v>
       </c>
       <c r="O62">
-        <v>4809.458524625817</v>
+        <v>4780.691166702914</v>
       </c>
       <c r="P62">
-        <v>14428.37557387745</v>
+        <v>14342.07350010874</v>
       </c>
       <c r="Q62">
-        <v>26676.37557387745</v>
+        <v>26590.07350010874</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1477250942780697</v>
+        <v>0.1500310918861709</v>
       </c>
       <c r="T62">
-        <v>1.986709800557795</v>
+        <v>2.031657986090777</v>
       </c>
       <c r="U62">
         <v>0.0612366166625341</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.78640959284202</v>
+        <v>3.724337304434773</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.086527877958716</v>
+        <v>0.08640924070806374</v>
       </c>
       <c r="C63">
-        <v>78865.54543397365</v>
+        <v>77224.25192040316</v>
       </c>
       <c r="D63">
-        <v>167818.3518936497</v>
+        <v>168056.1535679428</v>
       </c>
       <c r="E63">
-        <v>52724.78767332185</v>
+        <v>54603.8828611854</v>
       </c>
       <c r="F63">
-        <v>114624.8064596761</v>
+        <v>116503.9016475396</v>
       </c>
       <c r="G63">
         <v>25672</v>
@@ -6459,28 +6459,28 @@
         <v>26142</v>
       </c>
       <c r="M63">
-        <v>7019.235333188345</v>
+        <v>7134.304764879957</v>
       </c>
       <c r="N63">
-        <v>19122.76466681165</v>
+        <v>19007.69523512004</v>
       </c>
       <c r="O63">
-        <v>4780.691166702914</v>
+        <v>4751.92380878001</v>
       </c>
       <c r="P63">
-        <v>14342.07350010874</v>
+        <v>14255.77142634003</v>
       </c>
       <c r="Q63">
-        <v>26590.07350010874</v>
+        <v>26503.77142634003</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1500310918861709</v>
+        <v>0.1524584577894352</v>
       </c>
       <c r="T63">
-        <v>2.031657986090777</v>
+        <v>2.078971865599179</v>
       </c>
       <c r="U63">
         <v>0.0612366166625341</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.724337304434773</v>
+        <v>3.664267347911632</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08640924070806374</v>
+        <v>0.08629060345741149</v>
       </c>
       <c r="C64">
-        <v>77224.25192040316</v>
+        <v>75583.63330181566</v>
       </c>
       <c r="D64">
-        <v>168056.1535679428</v>
+        <v>168294.6301372188</v>
       </c>
       <c r="E64">
-        <v>54603.8828611854</v>
+        <v>56482.97804904894</v>
       </c>
       <c r="F64">
-        <v>116503.9016475396</v>
+        <v>118382.9968354031</v>
       </c>
       <c r="G64">
         <v>25672</v>
@@ -6541,28 +6541,28 @@
         <v>26142</v>
       </c>
       <c r="M64">
-        <v>7134.304764879957</v>
+        <v>7249.37419657157</v>
       </c>
       <c r="N64">
-        <v>19007.69523512004</v>
+        <v>18892.62580342843</v>
       </c>
       <c r="O64">
-        <v>4751.92380878001</v>
+        <v>4723.156450857107</v>
       </c>
       <c r="P64">
-        <v>14255.77142634003</v>
+        <v>14169.46935257132</v>
       </c>
       <c r="Q64">
-        <v>26503.77142634003</v>
+        <v>26417.46935257132</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1524584577894352</v>
+        <v>0.1550170326604436</v>
       </c>
       <c r="T64">
-        <v>2.078971865599179</v>
+        <v>2.128843252108035</v>
       </c>
       <c r="U64">
         <v>0.0612366166625341</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.664267347911632</v>
+        <v>3.606104374135256</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08629060345741149</v>
+        <v>0.08617196620675924</v>
       </c>
       <c r="C65">
-        <v>75583.63330181566</v>
+        <v>73943.69245538078</v>
       </c>
       <c r="D65">
-        <v>168294.6301372188</v>
+        <v>168533.7844786475</v>
       </c>
       <c r="E65">
-        <v>56482.97804904894</v>
+        <v>58362.07323691248</v>
       </c>
       <c r="F65">
-        <v>118382.9968354031</v>
+        <v>120262.0920232667</v>
       </c>
       <c r="G65">
         <v>25672</v>
@@ -6623,28 +6623,28 @@
         <v>26142</v>
       </c>
       <c r="M65">
-        <v>7249.37419657157</v>
+        <v>7364.443628263181</v>
       </c>
       <c r="N65">
-        <v>18892.62580342843</v>
+        <v>18777.55637173682</v>
       </c>
       <c r="O65">
-        <v>4723.156450857107</v>
+        <v>4694.389092934205</v>
       </c>
       <c r="P65">
-        <v>14169.46935257132</v>
+        <v>14083.16727880262</v>
       </c>
       <c r="Q65">
-        <v>26417.46935257132</v>
+        <v>26331.16727880262</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1550170326604436</v>
+        <v>0.1577177505798413</v>
       </c>
       <c r="T65">
-        <v>2.128843252108035</v>
+        <v>2.181485271200716</v>
       </c>
       <c r="U65">
         <v>0.0612366166625341</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.606104374135256</v>
+        <v>3.549758993289394</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08617196620675924</v>
+        <v>0.08605332895610698</v>
       </c>
       <c r="C66">
-        <v>73943.69245538078</v>
+        <v>72304.43227464576</v>
       </c>
       <c r="D66">
-        <v>168533.7844786475</v>
+        <v>168773.619485776</v>
       </c>
       <c r="E66">
-        <v>58362.07323691248</v>
+        <v>60241.16842477603</v>
       </c>
       <c r="F66">
-        <v>120262.0920232667</v>
+        <v>122141.1872111302</v>
       </c>
       <c r="G66">
         <v>25672</v>
@@ -6705,28 +6705,28 @@
         <v>26142</v>
       </c>
       <c r="M66">
-        <v>7364.443628263181</v>
+        <v>7479.513059954795</v>
       </c>
       <c r="N66">
-        <v>18777.55637173682</v>
+        <v>18662.4869400452</v>
       </c>
       <c r="O66">
-        <v>4694.389092934205</v>
+        <v>4665.621735011301</v>
       </c>
       <c r="P66">
-        <v>14083.16727880262</v>
+        <v>13996.8652050339</v>
       </c>
       <c r="Q66">
-        <v>26331.16727880262</v>
+        <v>26244.8652050339</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1577177505798413</v>
+        <v>0.1605727952374903</v>
       </c>
       <c r="T66">
-        <v>2.181485271200716</v>
+        <v>2.237135405670122</v>
       </c>
       <c r="U66">
         <v>0.0612366166625341</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.549758993289394</v>
+        <v>3.495147316469556</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08605332895610698</v>
+        <v>0.08593469170545473</v>
       </c>
       <c r="C67">
-        <v>72304.43227464576</v>
+        <v>70665.85566965218</v>
       </c>
       <c r="D67">
-        <v>168773.619485776</v>
+        <v>169014.138068646</v>
       </c>
       <c r="E67">
-        <v>60241.16842477603</v>
+        <v>62120.26361263957</v>
       </c>
       <c r="F67">
-        <v>122141.1872111302</v>
+        <v>124020.2823989938</v>
       </c>
       <c r="G67">
         <v>25672</v>
@@ -6787,28 +6787,28 @@
         <v>26142</v>
       </c>
       <c r="M67">
-        <v>7479.513059954795</v>
+        <v>7594.582491646406</v>
       </c>
       <c r="N67">
-        <v>18662.4869400452</v>
+        <v>18547.4175083536</v>
       </c>
       <c r="O67">
-        <v>4665.621735011301</v>
+        <v>4636.854377088399</v>
       </c>
       <c r="P67">
-        <v>13996.8652050339</v>
+        <v>13910.5631312652</v>
       </c>
       <c r="Q67">
-        <v>26244.8652050339</v>
+        <v>26158.5631312652</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1605727952374903</v>
+        <v>0.1635957836985305</v>
       </c>
       <c r="T67">
-        <v>2.237135405670122</v>
+        <v>2.296059077461258</v>
       </c>
       <c r="U67">
         <v>0.0612366166625341</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.495147316469556</v>
+        <v>3.442190538947291</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08593469170545473</v>
+        <v>0.08581605445480248</v>
       </c>
       <c r="C68">
-        <v>70665.85566965218</v>
+        <v>69027.96556705366</v>
       </c>
       <c r="D68">
-        <v>169014.138068646</v>
+        <v>169255.343153911</v>
       </c>
       <c r="E68">
-        <v>62120.26361263957</v>
+        <v>63999.35880050311</v>
       </c>
       <c r="F68">
-        <v>124020.2823989938</v>
+        <v>125899.3775868573</v>
       </c>
       <c r="G68">
         <v>25672</v>
@@ -6869,28 +6869,28 @@
         <v>26142</v>
       </c>
       <c r="M68">
-        <v>7594.582491646406</v>
+        <v>7709.651923338019</v>
       </c>
       <c r="N68">
-        <v>18547.4175083536</v>
+        <v>18432.34807666198</v>
       </c>
       <c r="O68">
-        <v>4636.854377088399</v>
+        <v>4608.087019165496</v>
       </c>
       <c r="P68">
-        <v>13910.5631312652</v>
+        <v>13824.26105749649</v>
       </c>
       <c r="Q68">
-        <v>26158.5631312652</v>
+        <v>26072.26105749649</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1635957836985305</v>
+        <v>0.1668019835814518</v>
       </c>
       <c r="T68">
-        <v>2.296059077461258</v>
+        <v>2.358553880876099</v>
       </c>
       <c r="U68">
         <v>0.0612366166625341</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.442190538947291</v>
+        <v>3.390814560754047</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08581605445480248</v>
+        <v>0.08569741720415021</v>
       </c>
       <c r="C69">
-        <v>69027.96556705366</v>
+        <v>67390.76491023449</v>
       </c>
       <c r="D69">
-        <v>169255.343153911</v>
+        <v>169497.2376849554</v>
       </c>
       <c r="E69">
-        <v>63999.35880050311</v>
+        <v>65878.45398836667</v>
       </c>
       <c r="F69">
-        <v>125899.3775868573</v>
+        <v>127778.4727747209</v>
       </c>
       <c r="G69">
         <v>25672</v>
@@ -6951,28 +6951,28 @@
         <v>26142</v>
       </c>
       <c r="M69">
-        <v>7709.651923338019</v>
+        <v>7824.721355029631</v>
       </c>
       <c r="N69">
-        <v>18432.34807666198</v>
+        <v>18317.27864497037</v>
       </c>
       <c r="O69">
-        <v>4608.087019165496</v>
+        <v>4579.319661242593</v>
       </c>
       <c r="P69">
-        <v>13824.26105749649</v>
+        <v>13737.95898372778</v>
       </c>
       <c r="Q69">
-        <v>26072.26105749649</v>
+        <v>25985.95898372778</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1668019835814518</v>
+        <v>0.1702085709570557</v>
       </c>
       <c r="T69">
-        <v>2.358553880876099</v>
+        <v>2.424954609504367</v>
       </c>
       <c r="U69">
         <v>0.0612366166625341</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.390814560754047</v>
+        <v>3.340949640742958</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08569741720415021</v>
+        <v>0.08557877995349797</v>
       </c>
       <c r="C70">
-        <v>67390.76491023449</v>
+        <v>65754.25665942943</v>
       </c>
       <c r="D70">
-        <v>169497.2376849554</v>
+        <v>169739.8246220138</v>
       </c>
       <c r="E70">
-        <v>65878.45398836667</v>
+        <v>67757.54917623021</v>
       </c>
       <c r="F70">
-        <v>127778.4727747209</v>
+        <v>129657.5679625844</v>
       </c>
       <c r="G70">
         <v>25672</v>
@@ -7033,28 +7033,28 @@
         <v>26142</v>
       </c>
       <c r="M70">
-        <v>7824.721355029631</v>
+        <v>7939.790786721243</v>
       </c>
       <c r="N70">
-        <v>18317.27864497037</v>
+        <v>18202.20921327876</v>
       </c>
       <c r="O70">
-        <v>4579.319661242593</v>
+        <v>4550.55230331969</v>
       </c>
       <c r="P70">
-        <v>13737.95898372778</v>
+        <v>13651.65690995907</v>
       </c>
       <c r="Q70">
-        <v>25985.95898372778</v>
+        <v>25899.65690995907</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1702085709570557</v>
+        <v>0.1738349381633438</v>
       </c>
       <c r="T70">
-        <v>2.424954609504367</v>
+        <v>2.495639256108654</v>
       </c>
       <c r="U70">
         <v>0.0612366166625341</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.340949640742958</v>
+        <v>3.292530080732191</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08557877995349797</v>
+        <v>0.08546014270284572</v>
       </c>
       <c r="C71">
-        <v>65754.25665942943</v>
+        <v>64118.44379184453</v>
       </c>
       <c r="D71">
-        <v>169739.8246220138</v>
+        <v>169983.1069422925</v>
       </c>
       <c r="E71">
-        <v>67757.54917623021</v>
+        <v>69636.64436409375</v>
       </c>
       <c r="F71">
-        <v>129657.5679625844</v>
+        <v>131536.6631504479</v>
       </c>
       <c r="G71">
         <v>25672</v>
@@ -7115,28 +7115,28 @@
         <v>26142</v>
       </c>
       <c r="M71">
-        <v>7939.790786721243</v>
+        <v>8054.860218412856</v>
       </c>
       <c r="N71">
-        <v>18202.20921327876</v>
+        <v>18087.13978158715</v>
       </c>
       <c r="O71">
-        <v>4550.55230331969</v>
+        <v>4521.784945396786</v>
       </c>
       <c r="P71">
-        <v>13651.65690995907</v>
+        <v>13565.35483619036</v>
       </c>
       <c r="Q71">
-        <v>25899.65690995907</v>
+        <v>25813.35483619036</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1738349381633438</v>
+        <v>0.1777030631833844</v>
       </c>
       <c r="T71">
-        <v>2.495639256108654</v>
+        <v>2.571036212486558</v>
       </c>
       <c r="U71">
         <v>0.0612366166625341</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.292530080732191</v>
+        <v>3.245493936721731</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08546014270284572</v>
+        <v>0.08534150545219346</v>
       </c>
       <c r="C72">
-        <v>64118.44379184453</v>
+        <v>62483.32930177881</v>
       </c>
       <c r="D72">
-        <v>169983.1069422925</v>
+        <v>170227.0876400903</v>
       </c>
       <c r="E72">
-        <v>69636.64436409375</v>
+        <v>71515.73955195729</v>
       </c>
       <c r="F72">
-        <v>131536.6631504479</v>
+        <v>133415.7583383115</v>
       </c>
       <c r="G72">
         <v>25672</v>
@@ -7197,28 +7197,28 @@
         <v>26142</v>
       </c>
       <c r="M72">
-        <v>8054.860218412856</v>
+        <v>8169.929650104467</v>
       </c>
       <c r="N72">
-        <v>18087.13978158715</v>
+        <v>17972.07034989553</v>
       </c>
       <c r="O72">
-        <v>4521.784945396786</v>
+        <v>4493.017587473883</v>
       </c>
       <c r="P72">
-        <v>13565.35483619036</v>
+        <v>13479.05276242165</v>
       </c>
       <c r="Q72">
-        <v>25813.35483619036</v>
+        <v>25727.05276242165</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1777030631833844</v>
+        <v>0.1818379554461864</v>
       </c>
       <c r="T72">
-        <v>2.571036212486558</v>
+        <v>2.651632958959492</v>
       </c>
       <c r="U72">
         <v>0.0612366166625341</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.245493936721731</v>
+        <v>3.199782754514383</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08534150545219346</v>
+        <v>0.08522286820154121</v>
       </c>
       <c r="C73">
-        <v>62483.32930177881</v>
+        <v>60848.91620074713</v>
       </c>
       <c r="D73">
-        <v>170227.0876400903</v>
+        <v>170471.7697269222</v>
       </c>
       <c r="E73">
-        <v>71515.73955195729</v>
+        <v>73394.83473982083</v>
       </c>
       <c r="F73">
-        <v>133415.7583383115</v>
+        <v>135294.853526175</v>
       </c>
       <c r="G73">
         <v>25672</v>
@@ -7279,28 +7279,28 @@
         <v>26142</v>
       </c>
       <c r="M73">
-        <v>8169.929650104467</v>
+        <v>8284.999081796079</v>
       </c>
       <c r="N73">
-        <v>17972.07034989553</v>
+        <v>17857.00091820392</v>
       </c>
       <c r="O73">
-        <v>4493.017587473883</v>
+        <v>4464.25022955098</v>
       </c>
       <c r="P73">
-        <v>13479.05276242165</v>
+        <v>13392.75068865294</v>
       </c>
       <c r="Q73">
-        <v>25727.05276242165</v>
+        <v>25640.75068865294</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1818379554461864</v>
+        <v>0.1862681971563314</v>
       </c>
       <c r="T73">
-        <v>2.651632958959491</v>
+        <v>2.737986615894776</v>
       </c>
       <c r="U73">
         <v>0.0612366166625341</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.199782754514383</v>
+        <v>3.15534132736835</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08522286820154121</v>
+        <v>0.08510423095088895</v>
       </c>
       <c r="C74">
-        <v>60848.91620074713</v>
+        <v>59215.20751760414</v>
       </c>
       <c r="D74">
-        <v>170471.7697269222</v>
+        <v>170717.1562316427</v>
       </c>
       <c r="E74">
-        <v>73394.83473982083</v>
+        <v>75273.92992768437</v>
       </c>
       <c r="F74">
-        <v>135294.853526175</v>
+        <v>137173.9487140386</v>
       </c>
       <c r="G74">
         <v>25672</v>
@@ -7361,28 +7361,28 @@
         <v>26142</v>
       </c>
       <c r="M74">
-        <v>8284.999081796079</v>
+        <v>8400.068513487691</v>
       </c>
       <c r="N74">
-        <v>17857.00091820392</v>
+        <v>17741.93148651231</v>
       </c>
       <c r="O74">
-        <v>4464.25022955098</v>
+        <v>4435.482871628077</v>
       </c>
       <c r="P74">
-        <v>13392.75068865294</v>
+        <v>13306.44861488423</v>
       </c>
       <c r="Q74">
-        <v>25640.75068865294</v>
+        <v>25554.44861488423</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1862681971563314</v>
+        <v>0.1910266049190798</v>
       </c>
       <c r="T74">
-        <v>2.737986615894776</v>
+        <v>2.830736840010453</v>
       </c>
       <c r="U74">
         <v>0.0612366166625341</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.15534132736835</v>
+        <v>3.112117473568783</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08510423095088895</v>
+        <v>0.0849855937002367</v>
       </c>
       <c r="C75">
-        <v>59215.20751760414</v>
+        <v>57582.20629866922</v>
       </c>
       <c r="D75">
-        <v>170717.1562316427</v>
+        <v>170963.2502005713</v>
       </c>
       <c r="E75">
-        <v>75273.92992768437</v>
+        <v>77153.02511554791</v>
       </c>
       <c r="F75">
-        <v>137173.9487140386</v>
+        <v>139053.0439019021</v>
       </c>
       <c r="G75">
         <v>25672</v>
@@ -7443,28 +7443,28 @@
         <v>26142</v>
       </c>
       <c r="M75">
-        <v>8400.068513487691</v>
+        <v>8515.137945179304</v>
       </c>
       <c r="N75">
-        <v>17741.93148651231</v>
+        <v>17626.8620548207</v>
       </c>
       <c r="O75">
-        <v>4435.482871628077</v>
+        <v>4406.715513705174</v>
       </c>
       <c r="P75">
-        <v>13306.44861488423</v>
+        <v>13220.14654111552</v>
       </c>
       <c r="Q75">
-        <v>25554.44861488423</v>
+        <v>25468.14654111552</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1910266049190798</v>
+        <v>0.1961510440481934</v>
       </c>
       <c r="T75">
-        <v>2.830736840010453</v>
+        <v>2.930621696750412</v>
       </c>
       <c r="U75">
         <v>0.0612366166625341</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.112117473568783</v>
+        <v>3.07006183203407</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0849855937002367</v>
+        <v>0.08486695644958445</v>
       </c>
       <c r="C76">
-        <v>57582.20629866922</v>
+        <v>55949.91560785254</v>
       </c>
       <c r="D76">
-        <v>170963.2502005713</v>
+        <v>171210.0546976182</v>
       </c>
       <c r="E76">
-        <v>77153.02511554791</v>
+        <v>79032.12030341144</v>
       </c>
       <c r="F76">
-        <v>139053.0439019021</v>
+        <v>140932.1390897656</v>
       </c>
       <c r="G76">
         <v>25672</v>
@@ -7525,28 +7525,28 @@
         <v>26142</v>
       </c>
       <c r="M76">
-        <v>8515.137945179304</v>
+        <v>8630.207376870916</v>
       </c>
       <c r="N76">
-        <v>17626.8620548207</v>
+        <v>17511.79262312908</v>
       </c>
       <c r="O76">
-        <v>4406.715513705174</v>
+        <v>4377.948155782271</v>
       </c>
       <c r="P76">
-        <v>13220.14654111552</v>
+        <v>13133.84446734681</v>
       </c>
       <c r="Q76">
-        <v>25468.14654111552</v>
+        <v>25381.84446734681</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1961510440481934</v>
+        <v>0.2016854383076361</v>
       </c>
       <c r="T76">
-        <v>2.930621696750412</v>
+        <v>3.038497342029569</v>
       </c>
       <c r="U76">
         <v>0.0612366166625341</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.07006183203407</v>
+        <v>3.029127674273616</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08486695644958445</v>
+        <v>0.0861733191989322</v>
       </c>
       <c r="C77">
-        <v>55949.91560785254</v>
+        <v>51391.81894660741</v>
       </c>
       <c r="D77">
-        <v>171210.0546976182</v>
+        <v>168531.0532242366</v>
       </c>
       <c r="E77">
-        <v>79032.12030341144</v>
+        <v>80911.21549127498</v>
       </c>
       <c r="F77">
-        <v>140932.1390897656</v>
+        <v>142811.2342776292</v>
       </c>
       <c r="G77">
         <v>25672</v>
@@ -7607,45 +7607,45 @@
         <v>26142</v>
       </c>
       <c r="M77">
-        <v>8630.207376870916</v>
+        <v>9102.3048942566</v>
       </c>
       <c r="N77">
-        <v>17511.79262312908</v>
+        <v>17039.6951057434</v>
       </c>
       <c r="O77">
-        <v>4377.948155782271</v>
+        <v>4259.92377643585</v>
       </c>
       <c r="P77">
-        <v>13133.84446734681</v>
+        <v>12779.77132930755</v>
       </c>
       <c r="Q77">
-        <v>25381.84446734681</v>
+        <v>25027.77132930755</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2016854383076361</v>
+        <v>0.207681032088699</v>
       </c>
       <c r="T77">
-        <v>3.038497342029569</v>
+        <v>3.155362624415321</v>
       </c>
       <c r="U77">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.029127674273616</v>
+        <v>2.872019812970136</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0861733191989322</v>
+        <v>0.08607343194827995</v>
       </c>
       <c r="C78">
-        <v>51391.81894660741</v>
+        <v>49714.60213827415</v>
       </c>
       <c r="D78">
-        <v>168531.0532242366</v>
+        <v>168732.9316037669</v>
       </c>
       <c r="E78">
-        <v>80911.21549127498</v>
+        <v>82790.31067913855</v>
       </c>
       <c r="F78">
-        <v>142811.2342776292</v>
+        <v>144690.3294654927</v>
       </c>
       <c r="G78">
         <v>25672</v>
@@ -7689,28 +7689,28 @@
         <v>26142</v>
       </c>
       <c r="M78">
-        <v>9102.3048942566</v>
+        <v>9222.072063917873</v>
       </c>
       <c r="N78">
-        <v>17039.6951057434</v>
+        <v>16919.92793608213</v>
       </c>
       <c r="O78">
-        <v>4259.92377643585</v>
+        <v>4229.981984020532</v>
       </c>
       <c r="P78">
-        <v>12779.77132930755</v>
+        <v>12689.9459520616</v>
       </c>
       <c r="Q78">
-        <v>25027.77132930755</v>
+        <v>24937.9459520616</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.207681032088699</v>
+        <v>0.2141979818507239</v>
       </c>
       <c r="T78">
-        <v>3.155362624415321</v>
+        <v>3.282390105269401</v>
       </c>
       <c r="U78">
         <v>0.06373661666253409</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.872019812970136</v>
+        <v>2.834720854360135</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08607343194827995</v>
+        <v>0.08597354469762769</v>
       </c>
       <c r="C79">
-        <v>49714.60213827415</v>
+        <v>48037.86955830074</v>
       </c>
       <c r="D79">
-        <v>168732.9316037669</v>
+        <v>168935.294211657</v>
       </c>
       <c r="E79">
-        <v>82790.31067913855</v>
+        <v>84669.40586700209</v>
       </c>
       <c r="F79">
-        <v>144690.3294654927</v>
+        <v>146569.4246533563</v>
       </c>
       <c r="G79">
         <v>25672</v>
@@ -7771,28 +7771,28 @@
         <v>26142</v>
       </c>
       <c r="M79">
-        <v>9222.072063917873</v>
+        <v>9341.839233579143</v>
       </c>
       <c r="N79">
-        <v>16919.92793608213</v>
+        <v>16800.16076642086</v>
       </c>
       <c r="O79">
-        <v>4229.981984020532</v>
+        <v>4200.040191605214</v>
       </c>
       <c r="P79">
-        <v>12689.9459520616</v>
+        <v>12600.12057481564</v>
       </c>
       <c r="Q79">
-        <v>24937.9459520616</v>
+        <v>24848.12057481564</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2141979818507239</v>
+        <v>0.2213073815911148</v>
       </c>
       <c r="T79">
-        <v>3.282390105269401</v>
+        <v>3.420965538928395</v>
       </c>
       <c r="U79">
         <v>0.06373661666253409</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.834720854360135</v>
+        <v>2.798378279304235</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08597354469762769</v>
+        <v>0.08587365744697543</v>
       </c>
       <c r="C80">
-        <v>48037.86955830074</v>
+        <v>46361.62295099461</v>
       </c>
       <c r="D80">
-        <v>168935.294211657</v>
+        <v>169138.1427922144</v>
       </c>
       <c r="E80">
-        <v>84669.40586700209</v>
+        <v>86548.50105486563</v>
       </c>
       <c r="F80">
-        <v>146569.4246533563</v>
+        <v>148448.5198412198</v>
       </c>
       <c r="G80">
         <v>25672</v>
@@ -7853,28 +7853,28 @@
         <v>26142</v>
       </c>
       <c r="M80">
-        <v>9341.839233579143</v>
+        <v>9461.606403240414</v>
       </c>
       <c r="N80">
-        <v>16800.16076642086</v>
+        <v>16680.39359675959</v>
       </c>
       <c r="O80">
-        <v>4200.040191605214</v>
+        <v>4170.098399189897</v>
       </c>
       <c r="P80">
-        <v>12600.12057481564</v>
+        <v>12510.29519756969</v>
       </c>
       <c r="Q80">
-        <v>24848.12057481564</v>
+        <v>24758.29519756969</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2213073815911148</v>
+        <v>0.2290938670210666</v>
       </c>
       <c r="T80">
-        <v>3.420965538928395</v>
+        <v>3.572738632935867</v>
       </c>
       <c r="U80">
         <v>0.06373661666253409</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.798378279304235</v>
+        <v>2.762955769439625</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08587365744697543</v>
+        <v>0.08577377019632318</v>
       </c>
       <c r="C81">
-        <v>46361.62295099461</v>
+        <v>44685.8640690514</v>
       </c>
       <c r="D81">
-        <v>169138.1427922144</v>
+        <v>169341.4790981348</v>
       </c>
       <c r="E81">
-        <v>86548.50105486563</v>
+        <v>88427.59624272917</v>
       </c>
       <c r="F81">
-        <v>148448.5198412198</v>
+        <v>150327.6150290834</v>
       </c>
       <c r="G81">
         <v>25672</v>
@@ -7935,28 +7935,28 @@
         <v>26142</v>
       </c>
       <c r="M81">
-        <v>9461.606403240414</v>
+        <v>9581.373572901684</v>
       </c>
       <c r="N81">
-        <v>16680.39359675959</v>
+        <v>16560.62642709832</v>
       </c>
       <c r="O81">
-        <v>4170.098399189897</v>
+        <v>4140.156606774579</v>
       </c>
       <c r="P81">
-        <v>12510.29519756969</v>
+        <v>12420.46982032374</v>
       </c>
       <c r="Q81">
-        <v>24758.29519756969</v>
+        <v>24668.46982032373</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2290938670210666</v>
+        <v>0.2376590009940137</v>
       </c>
       <c r="T81">
-        <v>3.572738632935867</v>
+        <v>3.739689036344085</v>
       </c>
       <c r="U81">
         <v>0.06373661666253409</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.762955769439625</v>
+        <v>2.72841882232163</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08577377019632318</v>
+        <v>0.08567388294567094</v>
       </c>
       <c r="C82">
-        <v>44685.8640690514</v>
+        <v>43010.59467360488</v>
       </c>
       <c r="D82">
-        <v>169341.4790981348</v>
+        <v>169545.3048905518</v>
       </c>
       <c r="E82">
-        <v>88427.59624272917</v>
+        <v>90306.69143059271</v>
       </c>
       <c r="F82">
-        <v>150327.6150290834</v>
+        <v>152206.7102169469</v>
       </c>
       <c r="G82">
         <v>25672</v>
@@ -8017,28 +8017,28 @@
         <v>26142</v>
       </c>
       <c r="M82">
-        <v>9581.373572901684</v>
+        <v>9701.140742562957</v>
       </c>
       <c r="N82">
-        <v>16560.62642709832</v>
+        <v>16440.85925743704</v>
       </c>
       <c r="O82">
-        <v>4140.156606774579</v>
+        <v>4110.21481435926</v>
       </c>
       <c r="P82">
-        <v>12420.46982032374</v>
+        <v>12330.64444307778</v>
       </c>
       <c r="Q82">
-        <v>24668.46982032373</v>
+        <v>24578.64444307778</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2376590009940137</v>
+        <v>0.2471257280167446</v>
       </c>
       <c r="T82">
-        <v>3.739689036344085</v>
+        <v>3.924213166426853</v>
       </c>
       <c r="U82">
         <v>0.06373661666253409</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.72841882232163</v>
+        <v>2.694734639330004</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08567388294567094</v>
+        <v>0.08557399569501867</v>
       </c>
       <c r="C83">
-        <v>43010.59467360488</v>
+        <v>41335.81653427845</v>
       </c>
       <c r="D83">
-        <v>169545.3048905518</v>
+        <v>169749.6219390889</v>
       </c>
       <c r="E83">
-        <v>90306.69143059271</v>
+        <v>92185.78661845624</v>
       </c>
       <c r="F83">
-        <v>152206.7102169469</v>
+        <v>154085.8054048104</v>
       </c>
       <c r="G83">
         <v>25672</v>
@@ -8099,28 +8099,28 @@
         <v>26142</v>
       </c>
       <c r="M83">
-        <v>9701.140742562957</v>
+        <v>9820.907912224227</v>
       </c>
       <c r="N83">
-        <v>16440.85925743704</v>
+        <v>16321.09208777577</v>
       </c>
       <c r="O83">
-        <v>4110.21481435926</v>
+        <v>4080.273021943943</v>
       </c>
       <c r="P83">
-        <v>12330.64444307778</v>
+        <v>12240.81906583183</v>
       </c>
       <c r="Q83">
-        <v>24578.64444307778</v>
+        <v>24488.81906583183</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2471257280167446</v>
+        <v>0.2576443135975567</v>
       </c>
       <c r="T83">
-        <v>3.924213166426853</v>
+        <v>4.129239977629927</v>
       </c>
       <c r="U83">
         <v>0.06373661666253409</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.694734639330004</v>
+        <v>2.661872021777199</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08557399569501867</v>
+        <v>0.08547410844436643</v>
       </c>
       <c r="C84">
-        <v>41335.81653427845</v>
+        <v>39661.53142923565</v>
       </c>
       <c r="D84">
-        <v>169749.6219390889</v>
+        <v>169954.4320219097</v>
       </c>
       <c r="E84">
-        <v>92185.78661845624</v>
+        <v>94064.88180631981</v>
       </c>
       <c r="F84">
-        <v>154085.8054048104</v>
+        <v>155964.900592674</v>
       </c>
       <c r="G84">
         <v>25672</v>
@@ -8181,28 +8181,28 @@
         <v>26142</v>
       </c>
       <c r="M84">
-        <v>9820.907912224227</v>
+        <v>9940.6750818855</v>
       </c>
       <c r="N84">
-        <v>16321.09208777577</v>
+        <v>16201.3249181145</v>
       </c>
       <c r="O84">
-        <v>4080.273021943943</v>
+        <v>4050.331229528625</v>
       </c>
       <c r="P84">
-        <v>12240.81906583183</v>
+        <v>12150.99368858588</v>
       </c>
       <c r="Q84">
-        <v>24488.81906583183</v>
+        <v>24398.99368858588</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2576443135975567</v>
+        <v>0.2694003798349351</v>
       </c>
       <c r="T84">
-        <v>4.129239977629927</v>
+        <v>4.358387590151012</v>
       </c>
       <c r="U84">
         <v>0.06373661666253409</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.661872021777199</v>
+        <v>2.629801274526872</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08547410844436643</v>
+        <v>0.08537422119371418</v>
       </c>
       <c r="C85">
-        <v>39661.53142923565</v>
+        <v>37987.7411452324</v>
       </c>
       <c r="D85">
-        <v>169954.4320219097</v>
+        <v>170159.7369257699</v>
       </c>
       <c r="E85">
-        <v>94064.88180631981</v>
+        <v>95943.97699418335</v>
       </c>
       <c r="F85">
-        <v>155964.900592674</v>
+        <v>157843.9957805375</v>
       </c>
       <c r="G85">
         <v>25672</v>
@@ -8263,28 +8263,28 @@
         <v>26142</v>
       </c>
       <c r="M85">
-        <v>9940.6750818855</v>
+        <v>10060.44225154677</v>
       </c>
       <c r="N85">
-        <v>16201.3249181145</v>
+        <v>16081.55774845323</v>
       </c>
       <c r="O85">
-        <v>4050.331229528625</v>
+        <v>4020.389437113307</v>
       </c>
       <c r="P85">
-        <v>12150.99368858588</v>
+        <v>12061.16831133992</v>
       </c>
       <c r="Q85">
-        <v>24398.99368858588</v>
+        <v>24309.16831133992</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2694003798349351</v>
+        <v>0.2826259543519857</v>
       </c>
       <c r="T85">
-        <v>4.358387590151012</v>
+        <v>4.616178654237232</v>
       </c>
       <c r="U85">
         <v>0.06373661666253409</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.629801274526872</v>
+        <v>2.59849411649679</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08537422119371416</v>
+        <v>0.08527433394306191</v>
       </c>
       <c r="C86">
-        <v>37987.74114523249</v>
+        <v>36314.44747766864</v>
       </c>
       <c r="D86">
-        <v>170159.73692577</v>
+        <v>170365.5384460697</v>
       </c>
       <c r="E86">
-        <v>95943.97699418332</v>
+        <v>97823.07218204686</v>
       </c>
       <c r="F86">
-        <v>157843.9957805375</v>
+        <v>159723.0909684011</v>
       </c>
       <c r="G86">
         <v>25672</v>
@@ -8345,28 +8345,28 @@
         <v>26142</v>
       </c>
       <c r="M86">
-        <v>10060.44225154677</v>
+        <v>10180.20942120804</v>
       </c>
       <c r="N86">
-        <v>16081.55774845323</v>
+        <v>15961.79057879196</v>
       </c>
       <c r="O86">
-        <v>4020.389437113308</v>
+        <v>3990.44764469799</v>
       </c>
       <c r="P86">
-        <v>12061.16831133992</v>
+        <v>11971.34293409397</v>
       </c>
       <c r="Q86">
-        <v>24309.16831133992</v>
+        <v>24219.34293409397</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2826259543519855</v>
+        <v>0.2976149388046429</v>
       </c>
       <c r="T86">
-        <v>4.616178654237229</v>
+        <v>4.90834186020161</v>
       </c>
       <c r="U86">
         <v>0.06373661666253409</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.598494116496791</v>
+        <v>2.567923597479181</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08527433394306191</v>
+        <v>0.08517444669240966</v>
       </c>
       <c r="C87">
-        <v>36314.44747766864</v>
+        <v>34641.65223064041</v>
       </c>
       <c r="D87">
-        <v>170365.5384460697</v>
+        <v>170571.838386905</v>
       </c>
       <c r="E87">
-        <v>97823.07218204686</v>
+        <v>99702.1673699104</v>
       </c>
       <c r="F87">
-        <v>159723.0909684011</v>
+        <v>161602.1861562646</v>
       </c>
       <c r="G87">
         <v>25672</v>
@@ -8427,28 +8427,28 @@
         <v>26142</v>
       </c>
       <c r="M87">
-        <v>10180.20942120804</v>
+        <v>10299.97659086931</v>
       </c>
       <c r="N87">
-        <v>15961.79057879196</v>
+        <v>15842.02340913069</v>
       </c>
       <c r="O87">
-        <v>3990.44764469799</v>
+        <v>3960.505852282673</v>
       </c>
       <c r="P87">
-        <v>11971.34293409397</v>
+        <v>11881.51755684802</v>
       </c>
       <c r="Q87">
-        <v>24219.34293409397</v>
+        <v>24129.51755684802</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2976149388046429</v>
+        <v>0.3147452067505369</v>
       </c>
       <c r="T87">
-        <v>4.90834186020161</v>
+        <v>5.242242667018046</v>
       </c>
       <c r="U87">
         <v>0.06373661666253409</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.567923597479181</v>
+        <v>2.538064020764307</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08517444669240966</v>
+        <v>0.0850745594417574</v>
       </c>
       <c r="C88">
-        <v>34641.65223064041</v>
+        <v>32969.35721699314</v>
       </c>
       <c r="D88">
-        <v>170571.838386905</v>
+        <v>170778.6385611213</v>
       </c>
       <c r="E88">
-        <v>99702.1673699104</v>
+        <v>101581.262557774</v>
       </c>
       <c r="F88">
-        <v>161602.1861562646</v>
+        <v>163481.2813441282</v>
       </c>
       <c r="G88">
         <v>25672</v>
@@ -8509,28 +8509,28 @@
         <v>26142</v>
       </c>
       <c r="M88">
-        <v>10299.97659086931</v>
+        <v>10419.74376053058</v>
       </c>
       <c r="N88">
-        <v>15842.02340913069</v>
+        <v>15722.25623946942</v>
       </c>
       <c r="O88">
-        <v>3960.505852282673</v>
+        <v>3930.564059867354</v>
       </c>
       <c r="P88">
-        <v>11881.51755684802</v>
+        <v>11791.69217960206</v>
       </c>
       <c r="Q88">
-        <v>24129.51755684802</v>
+        <v>24039.69217960206</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3147452067505369</v>
+        <v>0.3345109005342609</v>
       </c>
       <c r="T88">
-        <v>5.242242667018046</v>
+        <v>5.627512828729318</v>
       </c>
       <c r="U88">
         <v>0.06373661666253409</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.538064020764307</v>
+        <v>2.508890871100349</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0850745594417574</v>
+        <v>0.08728467219110517</v>
       </c>
       <c r="C89">
-        <v>32969.35721699314</v>
+        <v>26628.72153483439</v>
       </c>
       <c r="D89">
-        <v>170778.6385611213</v>
+        <v>166317.0980668261</v>
       </c>
       <c r="E89">
-        <v>101581.262557774</v>
+        <v>103460.3577456375</v>
       </c>
       <c r="F89">
-        <v>163481.2813441282</v>
+        <v>165360.3765319917</v>
       </c>
       <c r="G89">
         <v>25672</v>
@@ -8591,45 +8591,45 @@
         <v>26142</v>
       </c>
       <c r="M89">
-        <v>10419.74376053058</v>
+        <v>11118.27224805383</v>
       </c>
       <c r="N89">
-        <v>15722.25623946942</v>
+        <v>15023.72775194617</v>
       </c>
       <c r="O89">
-        <v>3930.564059867354</v>
+        <v>3755.931937986544</v>
       </c>
       <c r="P89">
-        <v>11791.69217960206</v>
+        <v>11267.79581395963</v>
       </c>
       <c r="Q89">
-        <v>24039.69217960206</v>
+        <v>23515.79581395963</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3345109005342609</v>
+        <v>0.3575708766152721</v>
       </c>
       <c r="T89">
-        <v>5.627512828729318</v>
+        <v>6.076994684059137</v>
       </c>
       <c r="U89">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.508890871100349</v>
+        <v>2.351264604496079</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08728467219110517</v>
+        <v>0.0872110349404529</v>
       </c>
       <c r="C90">
-        <v>26628.72153483439</v>
+        <v>24894.52005079415</v>
       </c>
       <c r="D90">
-        <v>166317.0980668261</v>
+        <v>166461.9917706494</v>
       </c>
       <c r="E90">
-        <v>103460.3577456375</v>
+        <v>105339.452933501</v>
       </c>
       <c r="F90">
-        <v>165360.3765319917</v>
+        <v>167239.4717198552</v>
       </c>
       <c r="G90">
         <v>25672</v>
@@ -8673,28 +8673,28 @@
         <v>26142</v>
       </c>
       <c r="M90">
-        <v>11118.27224805383</v>
+        <v>11244.61625087262</v>
       </c>
       <c r="N90">
-        <v>15023.72775194617</v>
+        <v>14897.38374912738</v>
       </c>
       <c r="O90">
-        <v>3755.931937986544</v>
+        <v>3724.345937281845</v>
       </c>
       <c r="P90">
-        <v>11267.79581395963</v>
+        <v>11173.03781184554</v>
       </c>
       <c r="Q90">
-        <v>23515.79581395963</v>
+        <v>23421.03781184553</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3575708766152721</v>
+        <v>0.3848235756201037</v>
       </c>
       <c r="T90">
-        <v>6.076994684059137</v>
+        <v>6.608200513085285</v>
       </c>
       <c r="U90">
         <v>0.0672366166625341</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.351264604496079</v>
+        <v>2.324845901074774</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0872110349404529</v>
+        <v>0.08713739768980065</v>
       </c>
       <c r="C91">
-        <v>24894.52005079415</v>
+        <v>23160.57124662277</v>
       </c>
       <c r="D91">
-        <v>166461.9917706494</v>
+        <v>166607.1381543415</v>
       </c>
       <c r="E91">
-        <v>105339.452933501</v>
+        <v>107218.5481213646</v>
       </c>
       <c r="F91">
-        <v>167239.4717198552</v>
+        <v>169118.5669077188</v>
       </c>
       <c r="G91">
         <v>25672</v>
@@ -8755,28 +8755,28 @@
         <v>26142</v>
       </c>
       <c r="M91">
-        <v>11244.61625087262</v>
+        <v>11370.96025369141</v>
       </c>
       <c r="N91">
-        <v>14897.38374912738</v>
+        <v>14771.03974630859</v>
       </c>
       <c r="O91">
-        <v>3724.345937281845</v>
+        <v>3692.759936577147</v>
       </c>
       <c r="P91">
-        <v>11173.03781184554</v>
+        <v>11078.27980973144</v>
       </c>
       <c r="Q91">
-        <v>23421.03781184553</v>
+        <v>23326.27980973144</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3848235756201037</v>
+        <v>0.4175268144259015</v>
       </c>
       <c r="T91">
-        <v>6.608200513085285</v>
+        <v>7.245647507916665</v>
       </c>
       <c r="U91">
         <v>0.0672366166625341</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.324845901074774</v>
+        <v>2.299014279951721</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08713739768980065</v>
+        <v>0.0870637604391484</v>
       </c>
       <c r="C92">
-        <v>23160.57124662277</v>
+        <v>21426.87578386909</v>
       </c>
       <c r="D92">
-        <v>166607.1381543415</v>
+        <v>166752.5378794514</v>
       </c>
       <c r="E92">
-        <v>107218.5481213646</v>
+        <v>109097.6433092281</v>
       </c>
       <c r="F92">
-        <v>169118.5669077188</v>
+        <v>170997.6620955823</v>
       </c>
       <c r="G92">
         <v>25672</v>
@@ -8837,28 +8837,28 @@
         <v>26142</v>
       </c>
       <c r="M92">
-        <v>11370.96025369141</v>
+        <v>11497.3042565102</v>
       </c>
       <c r="N92">
-        <v>14771.03974630859</v>
+        <v>14644.6957434898</v>
       </c>
       <c r="O92">
-        <v>3692.759936577147</v>
+        <v>3661.173935872449</v>
       </c>
       <c r="P92">
-        <v>11078.27980973144</v>
+        <v>10983.52180761735</v>
       </c>
       <c r="Q92">
-        <v>23326.27980973144</v>
+        <v>23231.52180761735</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4175268144259015</v>
+        <v>0.4574974396329878</v>
       </c>
       <c r="T92">
-        <v>7.245647507916665</v>
+        <v>8.024749390488351</v>
       </c>
       <c r="U92">
         <v>0.0672366166625341</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.299014279951721</v>
+        <v>2.273750386765439</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0870637604391484</v>
+        <v>0.08892212318849615</v>
       </c>
       <c r="C93">
-        <v>21426.87578386909</v>
+        <v>15954.30979163351</v>
       </c>
       <c r="D93">
-        <v>166752.5378794514</v>
+        <v>163159.0670750794</v>
       </c>
       <c r="E93">
-        <v>109097.6433092281</v>
+        <v>110976.7384970917</v>
       </c>
       <c r="F93">
-        <v>170997.6620955823</v>
+        <v>172876.7572834459</v>
       </c>
       <c r="G93">
         <v>25672</v>
@@ -8919,45 +8919,45 @@
         <v>26142</v>
       </c>
       <c r="M93">
-        <v>11497.3042565102</v>
+        <v>12107.70317972265</v>
       </c>
       <c r="N93">
-        <v>14644.6957434898</v>
+        <v>14034.29682027735</v>
       </c>
       <c r="O93">
-        <v>3661.173935872449</v>
+        <v>3508.574205069338</v>
       </c>
       <c r="P93">
-        <v>10983.52180761735</v>
+        <v>10525.72261520801</v>
       </c>
       <c r="Q93">
-        <v>23231.52180761735</v>
+        <v>22773.72261520801</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4574974396329878</v>
+        <v>0.5074607211418456</v>
       </c>
       <c r="T93">
-        <v>8.024749390488351</v>
+        <v>8.998626743702959</v>
       </c>
       <c r="U93">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V93">
         <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.273750386765439</v>
+        <v>2.159121314088808</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08892212318849615</v>
+        <v>0.0888694859378439</v>
       </c>
       <c r="C94">
-        <v>15954.30979163351</v>
+        <v>14174.86539595074</v>
       </c>
       <c r="D94">
-        <v>163159.0670750794</v>
+        <v>163258.7178672602</v>
       </c>
       <c r="E94">
-        <v>110976.7384970917</v>
+        <v>112855.8336849552</v>
       </c>
       <c r="F94">
-        <v>172876.7572834459</v>
+        <v>174755.8524713094</v>
       </c>
       <c r="G94">
         <v>25672</v>
@@ -9001,28 +9001,28 @@
         <v>26142</v>
       </c>
       <c r="M94">
-        <v>12107.70317972265</v>
+        <v>12239.30864906746</v>
       </c>
       <c r="N94">
-        <v>14034.29682027735</v>
+        <v>13902.69135093254</v>
       </c>
       <c r="O94">
-        <v>3508.574205069338</v>
+        <v>3475.672837733135</v>
       </c>
       <c r="P94">
-        <v>10525.72261520801</v>
+        <v>10427.01851319941</v>
       </c>
       <c r="Q94">
-        <v>22773.72261520801</v>
+        <v>22675.01851319941</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5074607211418456</v>
+        <v>0.5716992259389484</v>
       </c>
       <c r="T94">
-        <v>8.998626743702959</v>
+        <v>10.2507547692646</v>
       </c>
       <c r="U94">
         <v>0.07003661666253409</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.159121314088808</v>
+        <v>2.135904955872799</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0888694859378439</v>
+        <v>0.08881684868719164</v>
       </c>
       <c r="C95">
-        <v>14174.86539595074</v>
+        <v>12395.54279980107</v>
       </c>
       <c r="D95">
-        <v>163258.7178672602</v>
+        <v>163358.490458974</v>
       </c>
       <c r="E95">
-        <v>112855.8336849552</v>
+        <v>114734.9288728188</v>
       </c>
       <c r="F95">
-        <v>174755.8524713094</v>
+        <v>176634.947659173</v>
       </c>
       <c r="G95">
         <v>25672</v>
@@ -9083,28 +9083,28 @@
         <v>26142</v>
       </c>
       <c r="M95">
-        <v>12239.30864906746</v>
+        <v>12370.91411841227</v>
       </c>
       <c r="N95">
-        <v>13902.69135093254</v>
+        <v>13771.08588158773</v>
       </c>
       <c r="O95">
-        <v>3475.672837733135</v>
+        <v>3442.771470396932</v>
       </c>
       <c r="P95">
-        <v>10427.01851319941</v>
+        <v>10328.3144111908</v>
       </c>
       <c r="Q95">
-        <v>22675.01851319941</v>
+        <v>22576.3144111908</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5716992259389484</v>
+        <v>0.657350565668419</v>
       </c>
       <c r="T95">
-        <v>10.2507547692646</v>
+        <v>11.92025880334678</v>
       </c>
       <c r="U95">
         <v>0.07003661666253409</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.135904955872799</v>
+        <v>2.113182562725216</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08881684868719164</v>
+        <v>0.0887642114365394</v>
       </c>
       <c r="C96">
-        <v>12395.54279980107</v>
+        <v>10616.34222662772</v>
       </c>
       <c r="D96">
-        <v>163358.490458974</v>
+        <v>163458.3850736642</v>
       </c>
       <c r="E96">
-        <v>114734.9288728188</v>
+        <v>116614.0240606823</v>
       </c>
       <c r="F96">
-        <v>176634.947659173</v>
+        <v>178514.0428470365</v>
       </c>
       <c r="G96">
         <v>25672</v>
@@ -9165,28 +9165,28 @@
         <v>26142</v>
       </c>
       <c r="M96">
-        <v>12370.91411841227</v>
+        <v>12502.51958775708</v>
       </c>
       <c r="N96">
-        <v>13771.08588158773</v>
+        <v>13639.48041224292</v>
       </c>
       <c r="O96">
-        <v>3442.771470396932</v>
+        <v>3409.870103060729</v>
       </c>
       <c r="P96">
-        <v>10328.3144111908</v>
+        <v>10229.61030918219</v>
       </c>
       <c r="Q96">
-        <v>22576.3144111908</v>
+        <v>22477.61030918219</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.657350565668419</v>
+        <v>0.777262441289678</v>
       </c>
       <c r="T96">
-        <v>11.92025880334678</v>
+        <v>14.25756445106184</v>
       </c>
       <c r="U96">
         <v>0.07003661666253409</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.113182562725216</v>
+        <v>2.090938535749161</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0887642114365394</v>
+        <v>0.08871157418588713</v>
       </c>
       <c r="C97">
-        <v>10616.34222662772</v>
+        <v>8837.263900420803</v>
       </c>
       <c r="D97">
-        <v>163458.3850736642</v>
+        <v>163558.4019353208</v>
       </c>
       <c r="E97">
-        <v>116614.0240606823</v>
+        <v>118493.1192485458</v>
       </c>
       <c r="F97">
-        <v>178514.0428470365</v>
+        <v>180393.1380349</v>
       </c>
       <c r="G97">
         <v>25672</v>
@@ -9247,28 +9247,28 @@
         <v>26142</v>
       </c>
       <c r="M97">
-        <v>12502.51958775708</v>
+        <v>12634.12505710189</v>
       </c>
       <c r="N97">
-        <v>13639.48041224292</v>
+        <v>13507.87494289811</v>
       </c>
       <c r="O97">
-        <v>3409.870103060729</v>
+        <v>3376.968735724527</v>
       </c>
       <c r="P97">
-        <v>10229.61030918219</v>
+        <v>10130.90620717358</v>
       </c>
       <c r="Q97">
-        <v>22477.61030918219</v>
+        <v>22378.90620717358</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.777262441289678</v>
+        <v>0.9571302547215663</v>
       </c>
       <c r="T97">
-        <v>14.25756445106184</v>
+        <v>17.76352292263443</v>
       </c>
       <c r="U97">
         <v>0.07003661666253409</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.090938535749161</v>
+        <v>2.069157926001774</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08871157418588714</v>
+        <v>0.08865893693523488</v>
       </c>
       <c r="C98">
-        <v>8837.263900420832</v>
+        <v>7058.308045719081</v>
       </c>
       <c r="D98">
-        <v>163558.4019353208</v>
+        <v>163658.5412684826</v>
       </c>
       <c r="E98">
-        <v>118493.1192485458</v>
+        <v>120372.2144364094</v>
       </c>
       <c r="F98">
-        <v>180393.1380349</v>
+        <v>182272.2332227635</v>
       </c>
       <c r="G98">
         <v>25672</v>
@@ -9329,28 +9329,28 @@
         <v>26142</v>
       </c>
       <c r="M98">
-        <v>12634.12505710189</v>
+        <v>12765.7305264467</v>
       </c>
       <c r="N98">
-        <v>13507.87494289811</v>
+        <v>13376.2694735533</v>
       </c>
       <c r="O98">
-        <v>3376.968735724528</v>
+        <v>3344.067368388325</v>
       </c>
       <c r="P98">
-        <v>10130.90620717358</v>
+        <v>10032.20210516497</v>
       </c>
       <c r="Q98">
-        <v>22378.90620717358</v>
+        <v>22280.20210516497</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.957130254721564</v>
+        <v>1.25690994377471</v>
       </c>
       <c r="T98">
-        <v>17.76352292263439</v>
+        <v>23.60678704192201</v>
       </c>
       <c r="U98">
         <v>0.07003661666253409</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.069157926001775</v>
+        <v>2.047826400991447</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08865893693523488</v>
+        <v>0.08860629968458264</v>
       </c>
       <c r="C99">
-        <v>7058.308045719081</v>
+        <v>5279.474887611286</v>
       </c>
       <c r="D99">
-        <v>163658.5412684826</v>
+        <v>163758.8032982384</v>
       </c>
       <c r="E99">
-        <v>120372.2144364094</v>
+        <v>122251.3096242729</v>
       </c>
       <c r="F99">
-        <v>182272.2332227635</v>
+        <v>184151.3284106271</v>
       </c>
       <c r="G99">
         <v>25672</v>
@@ -9411,28 +9411,28 @@
         <v>26142</v>
       </c>
       <c r="M99">
-        <v>12765.7305264467</v>
+        <v>12897.33599579151</v>
       </c>
       <c r="N99">
-        <v>13376.2694735533</v>
+        <v>13244.66400420849</v>
       </c>
       <c r="O99">
-        <v>3344.067368388325</v>
+        <v>3311.166001052121</v>
       </c>
       <c r="P99">
-        <v>10032.20210516497</v>
+        <v>9933.498003156365</v>
       </c>
       <c r="Q99">
-        <v>22280.20210516497</v>
+        <v>22181.49800315636</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.25690994377471</v>
+        <v>1.856469321881002</v>
       </c>
       <c r="T99">
-        <v>23.60678704192201</v>
+        <v>35.29331528049727</v>
       </c>
       <c r="U99">
         <v>0.07003661666253409</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.047826400991447</v>
+        <v>2.026930213226228</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08860629968458264</v>
+        <v>0.08855366243393038</v>
       </c>
       <c r="C100">
-        <v>5279.474887611286</v>
+        <v>3500.764651738515</v>
       </c>
       <c r="D100">
-        <v>163758.8032982384</v>
+        <v>163859.1882502292</v>
       </c>
       <c r="E100">
-        <v>122251.3096242729</v>
+        <v>124130.4048121365</v>
       </c>
       <c r="F100">
-        <v>184151.3284106271</v>
+        <v>186030.4235984907</v>
       </c>
       <c r="G100">
         <v>25672</v>
@@ -9493,28 +9493,28 @@
         <v>26142</v>
       </c>
       <c r="M100">
-        <v>12897.33599579151</v>
+        <v>13028.94146513633</v>
       </c>
       <c r="N100">
-        <v>13244.66400420849</v>
+        <v>13113.05853486367</v>
       </c>
       <c r="O100">
-        <v>3311.166001052121</v>
+        <v>3278.264633715919</v>
       </c>
       <c r="P100">
-        <v>9933.498003156365</v>
+        <v>9834.793901147756</v>
       </c>
       <c r="Q100">
-        <v>22181.49800315636</v>
+        <v>22082.79390114776</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.856469321881002</v>
+        <v>3.655147456199878</v>
       </c>
       <c r="T100">
-        <v>35.29331528049727</v>
+        <v>70.35289999622303</v>
       </c>
       <c r="U100">
         <v>0.07003661666253409</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.026930213226228</v>
+        <v>2.006456170668387</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08855366243393038</v>
-      </c>
-      <c r="C101">
-        <v>3500.764651738515</v>
-      </c>
-      <c r="D101">
-        <v>163859.1882502292</v>
-      </c>
-      <c r="E101">
-        <v>124130.4048121365</v>
-      </c>
-      <c r="F101">
-        <v>186030.4235984907</v>
-      </c>
-      <c r="G101">
-        <v>25672</v>
-      </c>
-      <c r="H101">
-        <v>126009.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>38390</v>
-      </c>
-      <c r="K101">
-        <v>12248</v>
-      </c>
-      <c r="L101">
-        <v>26142</v>
-      </c>
-      <c r="M101">
-        <v>13028.94146513633</v>
-      </c>
-      <c r="N101">
-        <v>13113.05853486367</v>
-      </c>
-      <c r="O101">
-        <v>3278.264633715919</v>
-      </c>
-      <c r="P101">
-        <v>9834.793901147756</v>
-      </c>
-      <c r="Q101">
-        <v>22082.79390114776</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.655147456199878</v>
-      </c>
-      <c r="T101">
-        <v>70.35289999622303</v>
-      </c>
-      <c r="U101">
-        <v>0.07003661666253409</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05252746249690057</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.006456170668387</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
